--- a/external_dataset.xlsx
+++ b/external_dataset.xlsx
@@ -33,8 +33,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DP92"/>
+  <dimension ref="A1:DP94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1469,7 +1470,7 @@
         <v>50</v>
       </c>
       <c r="G5" t="str">
-        <v>0.005344</v>
+        <v>0.006849</v>
       </c>
       <c r="H5" t="str">
         <v>54.07</v>
@@ -1484,10 +1485,10 @@
         <v>59.05</v>
       </c>
       <c r="L5" t="str">
-        <v>53.811</v>
+        <v>55.6125</v>
       </c>
       <c r="M5" t="str">
-        <v>48.4351</v>
+        <v>50.0567</v>
       </c>
       <c r="N5" t="str">
         <v>9207.49</v>
@@ -1547,7 +1548,7 @@
         <v>80.55</v>
       </c>
       <c r="AG5" t="str">
-        <v>104.07</v>
+        <v>104.08</v>
       </c>
       <c r="AH5" t="str">
         <v>71.09</v>
@@ -1613,46 +1614,46 @@
         <v>3.12</v>
       </c>
       <c r="BC5" t="str">
-        <v>8.8</v>
+        <v>8.5</v>
       </c>
       <c r="BE5" t="str">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="BF5" t="str">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BG5" t="str">
         <v>259.1</v>
       </c>
       <c r="BH5" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ5" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL5" t="str">
-        <v>81.1617</v>
+        <v>81.2292</v>
       </c>
       <c r="BM5" t="str">
-        <v>82.6346</v>
+        <v>82.6733</v>
       </c>
       <c r="BN5" t="str">
-        <v>80.0869</v>
+        <v>80.078</v>
       </c>
       <c r="BO5" t="str">
-        <v>80.2877</v>
+        <v>80.3187</v>
       </c>
       <c r="BP5" t="str">
-        <v>79.4158</v>
+        <v>79.3819</v>
       </c>
       <c r="BQ5" t="str">
         <v>80.2055</v>
       </c>
       <c r="BR5" t="str">
-        <v>80.0313</v>
+        <v>80.0187</v>
       </c>
       <c r="BS5" t="str">
-        <v>21091.1226</v>
+        <v>21137.3792</v>
       </c>
       <c r="BT5" t="str">
         <v>117408.4302</v>
@@ -1742,37 +1743,49 @@
         <v>0</v>
       </c>
       <c r="CW5" t="str">
-        <v>0.0414</v>
+        <v>0.0518</v>
       </c>
       <c r="CX5" t="str">
         <v>4.134</v>
       </c>
       <c r="CY5" t="str">
-        <v>1.716</v>
+        <v>1.7685</v>
+      </c>
+      <c r="CZ5" t="str">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="str">
+        <v>0.218</v>
+      </c>
+      <c r="DB5" t="str">
+        <v>0.2007</v>
+      </c>
+      <c r="DC5" t="str">
+        <v>0</v>
       </c>
       <c r="DD5" t="str">
-        <v>1478.4014</v>
+        <v>1479.0328</v>
       </c>
       <c r="DE5" t="str">
         <v>0.474</v>
       </c>
       <c r="DF5" t="str">
-        <v>1045.6547</v>
+        <v>1045.2511</v>
       </c>
       <c r="DG5" t="str">
-        <v>695.3236</v>
+        <v>695.4331</v>
       </c>
       <c r="DH5" t="str">
-        <v>1.011922</v>
+        <v>1.012763</v>
       </c>
       <c r="DI5" t="str">
-        <v>1.030286</v>
+        <v>1.030768</v>
       </c>
       <c r="DJ5" t="str">
-        <v>0.989231</v>
+        <v>0.988791</v>
       </c>
       <c r="DK5" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL5" t="str">
         <v>0</v>
@@ -1810,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="G6" t="str">
-        <v>0.005310</v>
+        <v>0.006849</v>
       </c>
       <c r="H6" t="str">
         <v>54.18</v>
@@ -1825,10 +1838,10 @@
         <v>59.53</v>
       </c>
       <c r="L6" t="str">
-        <v>53.525</v>
+        <v>55.3265</v>
       </c>
       <c r="M6" t="str">
-        <v>48.1777</v>
+        <v>49.7992</v>
       </c>
       <c r="N6" t="str">
         <v>9009.83</v>
@@ -1888,7 +1901,7 @@
         <v>80.55</v>
       </c>
       <c r="AG6" t="str">
-        <v>104.07</v>
+        <v>104.08</v>
       </c>
       <c r="AH6" t="str">
         <v>71.71</v>
@@ -1945,7 +1958,7 @@
         <v>127.5</v>
       </c>
       <c r="AZ6" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA6" t="str">
         <v>27.44</v>
@@ -1954,46 +1967,46 @@
         <v>3.12</v>
       </c>
       <c r="BC6" t="str">
-        <v>8.8</v>
+        <v>8.5</v>
       </c>
       <c r="BE6" t="str">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="BF6" t="str">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BG6" t="str">
         <v>259.1</v>
       </c>
       <c r="BH6" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ6" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL6" t="str">
-        <v>81.5878</v>
+        <v>81.6557</v>
       </c>
       <c r="BM6" t="str">
-        <v>83.0685</v>
+        <v>83.1073</v>
       </c>
       <c r="BN6" t="str">
-        <v>80.5074</v>
+        <v>80.4984</v>
       </c>
       <c r="BO6" t="str">
-        <v>80.7093</v>
+        <v>80.7404</v>
       </c>
       <c r="BP6" t="str">
-        <v>79.8328</v>
+        <v>79.7987</v>
       </c>
       <c r="BQ6" t="str">
         <v>80.6266</v>
       </c>
       <c r="BR6" t="str">
-        <v>80.4515</v>
+        <v>80.4388</v>
       </c>
       <c r="BS6" t="str">
-        <v>21201.8513</v>
+        <v>21248.3626</v>
       </c>
       <c r="BT6" t="str">
         <v>118024.8554</v>
@@ -2083,13 +2096,13 @@
         <v>0</v>
       </c>
       <c r="CW6" t="str">
-        <v>0.2141</v>
+        <v>0.2274</v>
       </c>
       <c r="CX6" t="str">
         <v>4.53</v>
       </c>
       <c r="CY6" t="str">
-        <v>1.6922</v>
+        <v>1.7447</v>
       </c>
       <c r="CZ6" t="str">
         <v>-2.1467</v>
@@ -2104,28 +2117,28 @@
         <v>-0.3564</v>
       </c>
       <c r="DD6" t="str">
-        <v>1478.4005</v>
+        <v>1479.0323</v>
       </c>
       <c r="DE6" t="str">
         <v>0.474</v>
       </c>
       <c r="DF6" t="str">
-        <v>1045.6538</v>
+        <v>1045.2511</v>
       </c>
       <c r="DG6" t="str">
-        <v>695.3235</v>
+        <v>695.4333</v>
       </c>
       <c r="DH6" t="str">
-        <v>1.011922</v>
+        <v>1.012764</v>
       </c>
       <c r="DI6" t="str">
-        <v>1.030287</v>
+        <v>1.030768</v>
       </c>
       <c r="DJ6" t="str">
-        <v>0.989232</v>
+        <v>0.988791</v>
       </c>
       <c r="DK6" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL6" t="str">
         <v>0</v>
@@ -2163,7 +2176,7 @@
         <v>50</v>
       </c>
       <c r="G7" t="str">
-        <v>0.005201</v>
+        <v>0.006849</v>
       </c>
       <c r="H7" t="str">
         <v>53.81</v>
@@ -2178,10 +2191,10 @@
         <v>59.24</v>
       </c>
       <c r="L7" t="str">
-        <v>52.551</v>
+        <v>54.3525</v>
       </c>
       <c r="M7" t="str">
-        <v>47.301</v>
+        <v>48.9225</v>
       </c>
       <c r="N7" t="str">
         <v>8862.29</v>
@@ -2241,7 +2254,7 @@
         <v>80.55</v>
       </c>
       <c r="AG7" t="str">
-        <v>104.07</v>
+        <v>104.08</v>
       </c>
       <c r="AH7" t="str">
         <v>71.08</v>
@@ -2298,7 +2311,7 @@
         <v>127.5</v>
       </c>
       <c r="AZ7" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA7" t="str">
         <v>27.44</v>
@@ -2307,46 +2320,46 @@
         <v>3.12</v>
       </c>
       <c r="BC7" t="str">
-        <v>8.8</v>
+        <v>8.5</v>
       </c>
       <c r="BE7" t="str">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="BF7" t="str">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BG7" t="str">
         <v>259.1</v>
       </c>
       <c r="BH7" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ7" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL7" t="str">
-        <v>82.0162</v>
+        <v>82.0844</v>
       </c>
       <c r="BM7" t="str">
-        <v>83.5046</v>
+        <v>83.5437</v>
       </c>
       <c r="BN7" t="str">
-        <v>80.9301</v>
+        <v>80.921</v>
       </c>
       <c r="BO7" t="str">
-        <v>81.133</v>
+        <v>81.1643</v>
       </c>
       <c r="BP7" t="str">
-        <v>80.2519</v>
+        <v>80.2176</v>
       </c>
       <c r="BQ7" t="str">
         <v>81.0499</v>
       </c>
       <c r="BR7" t="str">
-        <v>80.8739</v>
+        <v>80.8611</v>
       </c>
       <c r="BS7" t="str">
-        <v>21313.1777</v>
+        <v>21359.9185</v>
       </c>
       <c r="BT7" t="str">
         <v>118644.501</v>
@@ -2436,13 +2449,13 @@
         <v>0</v>
       </c>
       <c r="CW7" t="str">
-        <v>0.0536</v>
+        <v>0.0641</v>
       </c>
       <c r="CX7" t="str">
         <v>5.134</v>
       </c>
       <c r="CY7" t="str">
-        <v>1.611</v>
+        <v>1.6635</v>
       </c>
       <c r="CZ7" t="str">
         <v>-1.6375</v>
@@ -2457,28 +2470,28 @@
         <v>-0.4121</v>
       </c>
       <c r="DD7" t="str">
-        <v>1478.4011</v>
+        <v>1479.0333</v>
       </c>
       <c r="DE7" t="str">
         <v>0.474</v>
       </c>
       <c r="DF7" t="str">
-        <v>1045.6543</v>
+        <v>1045.251</v>
       </c>
       <c r="DG7" t="str">
-        <v>695.3233</v>
+        <v>695.4334</v>
       </c>
       <c r="DH7" t="str">
-        <v>1.011922</v>
+        <v>1.012764</v>
       </c>
       <c r="DI7" t="str">
-        <v>1.030286</v>
+        <v>1.030769</v>
       </c>
       <c r="DJ7" t="str">
-        <v>0.989231</v>
+        <v>0.988791</v>
       </c>
       <c r="DK7" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL7" t="str">
         <v>0</v>
@@ -2516,7 +2529,7 @@
         <v>50</v>
       </c>
       <c r="G8" t="str">
-        <v>0.005243</v>
+        <v>0.006849</v>
       </c>
       <c r="H8" t="str">
         <v>53.78</v>
@@ -2531,10 +2544,10 @@
         <v>59.07</v>
       </c>
       <c r="L8" t="str">
-        <v>52.895</v>
+        <v>54.6965</v>
       </c>
       <c r="M8" t="str">
-        <v>47.6106</v>
+        <v>49.2322</v>
       </c>
       <c r="N8" t="str">
         <v>8797.8</v>
@@ -2594,7 +2607,7 @@
         <v>80.55</v>
       </c>
       <c r="AG8" t="str">
-        <v>104.07</v>
+        <v>104.08</v>
       </c>
       <c r="AH8" t="str">
         <v>70.35</v>
@@ -2651,7 +2664,7 @@
         <v>127.5</v>
       </c>
       <c r="AZ8" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA8" t="str">
         <v>27.44</v>
@@ -2660,46 +2673,46 @@
         <v>3.12</v>
       </c>
       <c r="BC8" t="str">
-        <v>8.8</v>
+        <v>8.5</v>
       </c>
       <c r="BE8" t="str">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="BF8" t="str">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BG8" t="str">
         <v>259.1</v>
       </c>
       <c r="BH8" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ8" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL8" t="str">
-        <v>82.4468</v>
+        <v>82.5153</v>
       </c>
       <c r="BM8" t="str">
-        <v>83.943</v>
+        <v>83.9823</v>
       </c>
       <c r="BN8" t="str">
-        <v>81.3549</v>
+        <v>81.3458</v>
       </c>
       <c r="BO8" t="str">
-        <v>81.5589</v>
+        <v>81.5904</v>
       </c>
       <c r="BP8" t="str">
-        <v>80.6732</v>
+        <v>80.6388</v>
       </c>
       <c r="BQ8" t="str">
         <v>81.4754</v>
       </c>
       <c r="BR8" t="str">
-        <v>81.2985</v>
+        <v>81.2856</v>
       </c>
       <c r="BS8" t="str">
-        <v>21425.0757</v>
+        <v>21472.0468</v>
       </c>
       <c r="BT8" t="str">
         <v>119267.3671</v>
@@ -2789,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="CW8" t="str">
-        <v>0.302</v>
+        <v>0.3171</v>
       </c>
       <c r="CX8" t="str">
         <v>4.76</v>
       </c>
       <c r="CY8" t="str">
-        <v>1.6397</v>
+        <v>1.6922</v>
       </c>
       <c r="CZ8" t="str">
         <v>-0.7277</v>
@@ -2810,28 +2823,28 @@
         <v>-0.0736</v>
       </c>
       <c r="DD8" t="str">
-        <v>1478.4013</v>
+        <v>1479.032</v>
       </c>
       <c r="DE8" t="str">
         <v>0.474</v>
       </c>
       <c r="DF8" t="str">
-        <v>1045.6547</v>
+        <v>1045.251</v>
       </c>
       <c r="DG8" t="str">
-        <v>695.3231</v>
+        <v>695.4335</v>
       </c>
       <c r="DH8" t="str">
-        <v>1.011923</v>
+        <v>1.012763</v>
       </c>
       <c r="DI8" t="str">
-        <v>1.030286</v>
+        <v>1.030769</v>
       </c>
       <c r="DJ8" t="str">
-        <v>0.989231</v>
+        <v>0.988791</v>
       </c>
       <c r="DK8" t="str">
-        <v>1.021105</v>
+        <v>1.021766</v>
       </c>
       <c r="DL8" t="str">
         <v>0</v>
@@ -2869,7 +2882,7 @@
         <v>50</v>
       </c>
       <c r="G9" t="str">
-        <v>0.005201</v>
+        <v>0.006849</v>
       </c>
       <c r="H9" t="str">
         <v>53.43</v>
@@ -2884,10 +2897,10 @@
         <v>59.2</v>
       </c>
       <c r="L9" t="str">
-        <v>52.6975</v>
+        <v>54.499</v>
       </c>
       <c r="M9" t="str">
-        <v>47.4329</v>
+        <v>49.0544</v>
       </c>
       <c r="N9" t="str">
         <v>8925.31</v>
@@ -2947,7 +2960,7 @@
         <v>79.77</v>
       </c>
       <c r="AG9" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH9" t="str">
         <v>69.66</v>
@@ -3013,10 +3026,10 @@
         <v>3.07</v>
       </c>
       <c r="BC9" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE9" t="str">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="BF9" t="str">
         <v>64</v>
@@ -3025,34 +3038,34 @@
         <v>259.1</v>
       </c>
       <c r="BH9" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ9" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL9" t="str">
-        <v>82.8797</v>
+        <v>82.9485</v>
       </c>
       <c r="BM9" t="str">
-        <v>84.3837</v>
+        <v>84.4232</v>
       </c>
       <c r="BN9" t="str">
-        <v>81.7821</v>
+        <v>81.773</v>
       </c>
       <c r="BO9" t="str">
-        <v>81.9872</v>
+        <v>82.0188</v>
       </c>
       <c r="BP9" t="str">
-        <v>81.0968</v>
+        <v>81.0622</v>
       </c>
       <c r="BQ9" t="str">
         <v>81.9032</v>
       </c>
       <c r="BR9" t="str">
-        <v>81.7254</v>
+        <v>81.7124</v>
       </c>
       <c r="BS9" t="str">
-        <v>20590.7</v>
+        <v>20593.11</v>
       </c>
       <c r="BT9" t="str">
         <v>119893.6</v>
@@ -3142,13 +3155,13 @@
         <v>0</v>
       </c>
       <c r="CW9" t="str">
-        <v>-0.0552</v>
+        <v>-0.0468</v>
       </c>
       <c r="CX9" t="str">
         <v>4.6075</v>
       </c>
       <c r="CY9" t="str">
-        <v>1.6232</v>
+        <v>1.6757</v>
       </c>
       <c r="CZ9" t="str">
         <v>1.4493</v>
@@ -3163,28 +3176,28 @@
         <v>0.3092</v>
       </c>
       <c r="DD9" t="str">
-        <v>1478.4011</v>
+        <v>1479.0322</v>
       </c>
       <c r="DE9" t="str">
         <v>0.474</v>
       </c>
       <c r="DF9" t="str">
-        <v>1045.654</v>
+        <v>1045.2511</v>
       </c>
       <c r="DG9" t="str">
-        <v>695.3229</v>
+        <v>695.4335</v>
       </c>
       <c r="DH9" t="str">
-        <v>1.011923</v>
+        <v>1.012763</v>
       </c>
       <c r="DI9" t="str">
-        <v>1.030286</v>
+        <v>1.030768</v>
       </c>
       <c r="DJ9" t="str">
-        <v>0.989231</v>
+        <v>0.988792</v>
       </c>
       <c r="DK9" t="str">
-        <v>1.021104</v>
+        <v>1.021765</v>
       </c>
       <c r="DL9" t="str">
         <v>0</v>
@@ -3199,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="DP9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3222,7 +3235,7 @@
         <v>50</v>
       </c>
       <c r="G10" t="str">
-        <v>0.005326</v>
+        <v>0.006849</v>
       </c>
       <c r="H10" t="str">
         <v>53.23</v>
@@ -3237,10 +3250,10 @@
         <v>58.77</v>
       </c>
       <c r="L10" t="str">
-        <v>53.6325</v>
+        <v>55.434</v>
       </c>
       <c r="M10" t="str">
-        <v>48.2745</v>
+        <v>49.896</v>
       </c>
       <c r="N10" t="str">
         <v>8855.14</v>
@@ -3300,7 +3313,7 @@
         <v>79.77</v>
       </c>
       <c r="AG10" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH10" t="str">
         <v>70.46</v>
@@ -3357,7 +3370,7 @@
         <v>138.8</v>
       </c>
       <c r="AZ10" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA10" t="str">
         <v>27.2</v>
@@ -3366,46 +3379,46 @@
         <v>3.07</v>
       </c>
       <c r="BC10" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE10" t="str">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="BF10" t="str">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BG10" t="str">
         <v>259.1</v>
       </c>
       <c r="BH10" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ10" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL10" t="str">
-        <v>83.3148</v>
+        <v>83.384</v>
       </c>
       <c r="BM10" t="str">
-        <v>84.8268</v>
+        <v>84.8665</v>
       </c>
       <c r="BN10" t="str">
-        <v>82.2115</v>
+        <v>82.2023</v>
       </c>
       <c r="BO10" t="str">
-        <v>82.4176</v>
+        <v>82.4494</v>
       </c>
       <c r="BP10" t="str">
-        <v>81.5226</v>
+        <v>81.4878</v>
       </c>
       <c r="BQ10" t="str">
         <v>82.3332</v>
       </c>
       <c r="BR10" t="str">
-        <v>82.1544</v>
+        <v>82.1414</v>
       </c>
       <c r="BS10" t="str">
-        <v>20710.47</v>
+        <v>20748.2</v>
       </c>
       <c r="BT10" t="str">
         <v>120523.0534</v>
@@ -3495,13 +3508,13 @@
         <v>1</v>
       </c>
       <c r="CW10" t="str">
-        <v>0.287</v>
+        <v>0.3018</v>
       </c>
       <c r="CX10" t="str">
         <v>3.4725</v>
       </c>
       <c r="CY10" t="str">
-        <v>1.7012</v>
+        <v>1.7537</v>
       </c>
       <c r="CZ10" t="str">
         <v>-0.7862</v>
@@ -3516,28 +3529,28 @@
         <v>-0.3009</v>
       </c>
       <c r="DD10" t="str">
-        <v>1478.4005</v>
+        <v>1479.0319</v>
       </c>
       <c r="DE10" t="str">
         <v>0.474</v>
       </c>
       <c r="DF10" t="str">
-        <v>1045.6545</v>
+        <v>1045.2512</v>
       </c>
       <c r="DG10" t="str">
-        <v>695.3234</v>
+        <v>695.4335</v>
       </c>
       <c r="DH10" t="str">
-        <v>1.011922</v>
+        <v>1.012763</v>
       </c>
       <c r="DI10" t="str">
-        <v>1.030287</v>
+        <v>1.030769</v>
       </c>
       <c r="DJ10" t="str">
-        <v>0.989231</v>
+        <v>0.988792</v>
       </c>
       <c r="DK10" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL10" t="str">
         <v>0</v>
@@ -3575,7 +3588,7 @@
         <v>50</v>
       </c>
       <c r="G11" t="str">
-        <v>0.005274</v>
+        <v>0.006849</v>
       </c>
       <c r="H11" t="str">
         <v>53.24</v>
@@ -3590,10 +3603,10 @@
         <v>58.78</v>
       </c>
       <c r="L11" t="str">
-        <v>53.055</v>
+        <v>53.063</v>
       </c>
       <c r="M11" t="str">
-        <v>47.7547</v>
+        <v>47.7619</v>
       </c>
       <c r="N11" t="str">
         <v>9322.8</v>
@@ -3653,7 +3666,7 @@
         <v>79.77</v>
       </c>
       <c r="AG11" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH11" t="str">
         <v>70.38</v>
@@ -3710,7 +3723,7 @@
         <v>138.8</v>
       </c>
       <c r="AZ11" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA11" t="str">
         <v>27.2</v>
@@ -3719,46 +3732,46 @@
         <v>3.07</v>
       </c>
       <c r="BC11" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="str">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="BF11" t="str">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="BG11" t="str">
         <v>259.1</v>
       </c>
       <c r="BH11" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ11" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL11" t="str">
-        <v>83.7522</v>
+        <v>83.8219</v>
       </c>
       <c r="BM11" t="str">
-        <v>85.2722</v>
+        <v>85.3121</v>
       </c>
       <c r="BN11" t="str">
-        <v>82.6431</v>
+        <v>82.6339</v>
       </c>
       <c r="BO11" t="str">
-        <v>82.8504</v>
+        <v>82.8824</v>
       </c>
       <c r="BP11" t="str">
-        <v>81.9506</v>
+        <v>81.9156</v>
       </c>
       <c r="BQ11" t="str">
         <v>82.7655</v>
       </c>
       <c r="BR11" t="str">
-        <v>82.5858</v>
+        <v>82.5727</v>
       </c>
       <c r="BS11" t="str">
-        <v>21004.11</v>
+        <v>21065.38</v>
       </c>
       <c r="BT11" t="str">
         <v>121155.8737</v>
@@ -3848,13 +3861,13 @@
         <v>0</v>
       </c>
       <c r="CW11" t="str">
-        <v>-0.2081</v>
+        <v>-0.2021</v>
       </c>
       <c r="CX11" t="str">
         <v>4.06</v>
       </c>
       <c r="CY11" t="str">
-        <v>1.653</v>
+        <v>1.7055</v>
       </c>
       <c r="CZ11" t="str">
         <v>5.2812</v>
@@ -3869,28 +3882,28 @@
         <v>-0.8197</v>
       </c>
       <c r="DD11" t="str">
-        <v>1478.4013</v>
+        <v>1479.033</v>
       </c>
       <c r="DE11" t="str">
         <v>0.474</v>
       </c>
       <c r="DF11" t="str">
-        <v>1045.6538</v>
+        <v>1045.25</v>
       </c>
       <c r="DG11" t="str">
-        <v>695.3231</v>
+        <v>695.4334</v>
       </c>
       <c r="DH11" t="str">
-        <v>1.011922</v>
+        <v>1.012764</v>
       </c>
       <c r="DI11" t="str">
-        <v>1.030287</v>
+        <v>1.030769</v>
       </c>
       <c r="DJ11" t="str">
-        <v>0.989233</v>
+        <v>0.988792</v>
       </c>
       <c r="DK11" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL11" t="str">
         <v>0</v>
@@ -3928,7 +3941,7 @@
         <v>50</v>
       </c>
       <c r="G12" t="str">
-        <v>0.005261</v>
+        <v>0.006849</v>
       </c>
       <c r="H12" t="str">
         <v>53.31</v>
@@ -3943,10 +3956,10 @@
         <v>58.9</v>
       </c>
       <c r="L12" t="str">
-        <v>53.145</v>
+        <v>53.153</v>
       </c>
       <c r="M12" t="str">
-        <v>47.8357</v>
+        <v>47.8429</v>
       </c>
       <c r="N12" t="str">
         <v>9315.55</v>
@@ -4006,7 +4019,7 @@
         <v>79.77</v>
       </c>
       <c r="AG12" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH12" t="str">
         <v>70.69</v>
@@ -4063,7 +4076,7 @@
         <v>138.8</v>
       </c>
       <c r="AZ12" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA12" t="str">
         <v>27.2</v>
@@ -4072,10 +4085,10 @@
         <v>3.07</v>
       </c>
       <c r="BC12" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE12" t="str">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF12" t="str">
         <v>78</v>
@@ -4084,34 +4097,34 @@
         <v>259.1</v>
       </c>
       <c r="BH12" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ12" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL12" t="str">
-        <v>84.1919</v>
+        <v>84.2619</v>
       </c>
       <c r="BM12" t="str">
-        <v>85.7198</v>
+        <v>85.7599</v>
       </c>
       <c r="BN12" t="str">
-        <v>83.077</v>
+        <v>83.0677</v>
       </c>
       <c r="BO12" t="str">
-        <v>83.2853</v>
+        <v>83.3175</v>
       </c>
       <c r="BP12" t="str">
-        <v>82.3808</v>
+        <v>82.3457</v>
       </c>
       <c r="BQ12" t="str">
         <v>83.2</v>
       </c>
       <c r="BR12" t="str">
-        <v>83.0193</v>
+        <v>83.0062</v>
       </c>
       <c r="BS12" t="str">
-        <v>21235.57</v>
+        <v>21274.45</v>
       </c>
       <c r="BT12" t="str">
         <v>121791.9144</v>
@@ -4201,13 +4214,13 @@
         <v>0</v>
       </c>
       <c r="CW12" t="str">
-        <v>0.3234</v>
+        <v>0.3392</v>
       </c>
       <c r="CX12" t="str">
         <v>4.04</v>
       </c>
       <c r="CY12" t="str">
-        <v>1.6605</v>
+        <v>1.713</v>
       </c>
       <c r="CZ12" t="str">
         <v>-0.0778</v>
@@ -4222,28 +4235,28 @@
         <v>-0.2277</v>
       </c>
       <c r="DD12" t="str">
-        <v>1478.4017</v>
+        <v>1479.0319</v>
       </c>
       <c r="DE12" t="str">
         <v>0.474</v>
       </c>
       <c r="DF12" t="str">
-        <v>1045.6543</v>
+        <v>1045.2502</v>
       </c>
       <c r="DG12" t="str">
-        <v>695.3236</v>
+        <v>695.4333</v>
       </c>
       <c r="DH12" t="str">
-        <v>1.011922</v>
+        <v>1.012763</v>
       </c>
       <c r="DI12" t="str">
-        <v>1.030286</v>
+        <v>1.030768</v>
       </c>
       <c r="DJ12" t="str">
-        <v>0.989232</v>
+        <v>0.988792</v>
       </c>
       <c r="DK12" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL12" t="str">
         <v>0</v>
@@ -4281,7 +4294,7 @@
         <v>50</v>
       </c>
       <c r="G13" t="str">
-        <v>0.005277</v>
+        <v>0.006849</v>
       </c>
       <c r="H13" t="str">
         <v>53.36</v>
@@ -4296,10 +4309,10 @@
         <v>59.22</v>
       </c>
       <c r="L13" t="str">
-        <v>53.311</v>
+        <v>53.319</v>
       </c>
       <c r="M13" t="str">
-        <v>47.9851</v>
+        <v>47.9923</v>
       </c>
       <c r="N13" t="str">
         <v>9645.59</v>
@@ -4359,7 +4372,7 @@
         <v>79.77</v>
       </c>
       <c r="AG13" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH13" t="str">
         <v>70.31</v>
@@ -4416,7 +4429,7 @@
         <v>138.8</v>
       </c>
       <c r="AZ13" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA13" t="str">
         <v>27.2</v>
@@ -4425,46 +4438,46 @@
         <v>3.07</v>
       </c>
       <c r="BC13" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="str">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="BF13" t="str">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="BG13" t="str">
         <v>259.1</v>
       </c>
       <c r="BH13" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ13" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL13" t="str">
-        <v>84.6339</v>
+        <v>84.7043</v>
       </c>
       <c r="BM13" t="str">
-        <v>86.1699</v>
+        <v>86.2102</v>
       </c>
       <c r="BN13" t="str">
-        <v>83.5131</v>
+        <v>83.5038</v>
       </c>
       <c r="BO13" t="str">
-        <v>83.7225</v>
+        <v>83.7549</v>
       </c>
       <c r="BP13" t="str">
-        <v>82.8133</v>
+        <v>82.778</v>
       </c>
       <c r="BQ13" t="str">
         <v>83.6368</v>
       </c>
       <c r="BR13" t="str">
-        <v>83.4552</v>
+        <v>83.442</v>
       </c>
       <c r="BS13" t="str">
-        <v>21392.63</v>
+        <v>21438.22</v>
       </c>
       <c r="BT13" t="str">
         <v>122431.3219</v>
@@ -4554,13 +4567,13 @@
         <v>0</v>
       </c>
       <c r="CW13" t="str">
-        <v>0.2</v>
+        <v>0.2136</v>
       </c>
       <c r="CX13" t="str">
         <v>3.924</v>
       </c>
       <c r="CY13" t="str">
-        <v>1.6744</v>
+        <v>1.7269</v>
       </c>
       <c r="CZ13" t="str">
         <v>3.5429</v>
@@ -4575,28 +4588,28 @@
         <v>0.9618</v>
       </c>
       <c r="DD13" t="str">
-        <v>1478.4017</v>
+        <v>1479.0321</v>
       </c>
       <c r="DE13" t="str">
         <v>0.474</v>
       </c>
       <c r="DF13" t="str">
-        <v>1045.6549</v>
+        <v>1045.2504</v>
       </c>
       <c r="DG13" t="str">
-        <v>695.3232</v>
+        <v>695.4332</v>
       </c>
       <c r="DH13" t="str">
-        <v>1.011922</v>
+        <v>1.012764</v>
       </c>
       <c r="DI13" t="str">
-        <v>1.030287</v>
+        <v>1.030769</v>
       </c>
       <c r="DJ13" t="str">
-        <v>0.989231</v>
+        <v>0.988792</v>
       </c>
       <c r="DK13" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL13" t="str">
         <v>0</v>
@@ -4634,7 +4647,7 @@
         <v>50</v>
       </c>
       <c r="G14" t="str">
-        <v>0.005279</v>
+        <v>0.006849</v>
       </c>
       <c r="H14" t="str">
         <v>53.44</v>
@@ -4649,10 +4662,10 @@
         <v>58.99</v>
       </c>
       <c r="L14" t="str">
-        <v>53.505</v>
+        <v>53.513</v>
       </c>
       <c r="M14" t="str">
-        <v>48.1597</v>
+        <v>48.1669</v>
       </c>
       <c r="N14" t="str">
         <v>9882.27</v>
@@ -4712,7 +4725,7 @@
         <v>79.77</v>
       </c>
       <c r="AG14" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH14" t="str">
         <v>69.77</v>
@@ -4769,7 +4782,7 @@
         <v>138.8</v>
       </c>
       <c r="AZ14" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA14" t="str">
         <v>27.2</v>
@@ -4778,46 +4791,46 @@
         <v>3.07</v>
       </c>
       <c r="BC14" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="str">
+        <v>67</v>
+      </c>
+      <c r="BF14" t="str">
         <v>71</v>
-      </c>
-      <c r="BF14" t="str">
-        <v>70</v>
       </c>
       <c r="BG14" t="str">
         <v>259.1</v>
       </c>
       <c r="BH14" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ14" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL14" t="str">
-        <v>85.0783</v>
+        <v>85.149</v>
       </c>
       <c r="BM14" t="str">
-        <v>86.6222</v>
+        <v>86.6628</v>
       </c>
       <c r="BN14" t="str">
-        <v>83.9516</v>
+        <v>83.9422</v>
       </c>
       <c r="BO14" t="str">
-        <v>84.1621</v>
+        <v>84.1946</v>
       </c>
       <c r="BP14" t="str">
-        <v>83.2481</v>
+        <v>83.2126</v>
       </c>
       <c r="BQ14" t="str">
         <v>84.0759</v>
       </c>
       <c r="BR14" t="str">
-        <v>83.8933</v>
+        <v>83.8801</v>
       </c>
       <c r="BS14" t="str">
-        <v>21591.62</v>
+        <v>21627.43</v>
       </c>
       <c r="BT14" t="str">
         <v>123074.0963</v>
@@ -4904,16 +4917,16 @@
         <v>0</v>
       </c>
       <c r="CV14" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="str">
-        <v>-0.9521</v>
+        <v>-0.9597</v>
       </c>
       <c r="CX14" t="str">
         <v>3.81</v>
       </c>
       <c r="CY14" t="str">
-        <v>1.6905</v>
+        <v>1.743</v>
       </c>
       <c r="CZ14" t="str">
         <v>2.4538</v>
@@ -4928,28 +4941,28 @@
         <v>0.4097</v>
       </c>
       <c r="DD14" t="str">
-        <v>1478.4013</v>
+        <v>1479.032</v>
       </c>
       <c r="DE14" t="str">
         <v>0.474</v>
       </c>
       <c r="DF14" t="str">
-        <v>1045.6543</v>
+        <v>1045.2507</v>
       </c>
       <c r="DG14" t="str">
-        <v>695.3236</v>
+        <v>695.433</v>
       </c>
       <c r="DH14" t="str">
-        <v>1.011923</v>
+        <v>1.012763</v>
       </c>
       <c r="DI14" t="str">
-        <v>1.030286</v>
+        <v>1.030769</v>
       </c>
       <c r="DJ14" t="str">
-        <v>0.989231</v>
+        <v>0.988791</v>
       </c>
       <c r="DK14" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL14" t="str">
         <v>0</v>
@@ -4987,7 +5000,7 @@
         <v>50</v>
       </c>
       <c r="G15" t="str">
-        <v>0.005337</v>
+        <v>0.006849</v>
       </c>
       <c r="H15" t="str">
         <v>53.87</v>
@@ -5002,10 +5015,10 @@
         <v>59.26</v>
       </c>
       <c r="L15" t="str">
-        <v>53.507</v>
+        <v>53.515</v>
       </c>
       <c r="M15" t="str">
-        <v>48.1615</v>
+        <v>48.1687</v>
       </c>
       <c r="N15" t="str">
         <v>10119.8</v>
@@ -5065,7 +5078,7 @@
         <v>79.77</v>
       </c>
       <c r="AG15" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH15" t="str">
         <v>68.85</v>
@@ -5122,7 +5135,7 @@
         <v>138.8</v>
       </c>
       <c r="AZ15" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA15" t="str">
         <v>27.2</v>
@@ -5131,46 +5144,46 @@
         <v>3.07</v>
       </c>
       <c r="BC15" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="str">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="BF15" t="str">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="BG15" t="str">
         <v>259.1</v>
       </c>
       <c r="BH15" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ15" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL15" t="str">
-        <v>85.5249</v>
+        <v>85.596</v>
       </c>
       <c r="BM15" t="str">
-        <v>87.077</v>
+        <v>87.1178</v>
       </c>
       <c r="BN15" t="str">
-        <v>84.3923</v>
+        <v>84.3829</v>
       </c>
       <c r="BO15" t="str">
-        <v>84.604</v>
+        <v>84.6366</v>
       </c>
       <c r="BP15" t="str">
-        <v>83.6852</v>
+        <v>83.6494</v>
       </c>
       <c r="BQ15" t="str">
         <v>84.5173</v>
       </c>
       <c r="BR15" t="str">
-        <v>84.3338</v>
+        <v>84.3205</v>
       </c>
       <c r="BS15" t="str">
-        <v>21695.49</v>
+        <v>21728.28</v>
       </c>
       <c r="BT15" t="str">
         <v>123720.2375</v>
@@ -5260,13 +5273,13 @@
         <v>0</v>
       </c>
       <c r="CW15" t="str">
-        <v>-0.6614</v>
+        <v>-0.6639</v>
       </c>
       <c r="CX15" t="str">
         <v>4.238</v>
       </c>
       <c r="CY15" t="str">
-        <v>1.6907</v>
+        <v>1.7432</v>
       </c>
       <c r="CZ15" t="str">
         <v>2.4036</v>
@@ -5281,28 +5294,28 @@
         <v>-0.0482</v>
       </c>
       <c r="DD15" t="str">
-        <v>1478.4005</v>
+        <v>1479.0332</v>
       </c>
       <c r="DE15" t="str">
         <v>0.474</v>
       </c>
       <c r="DF15" t="str">
-        <v>1045.6537</v>
+        <v>1045.251</v>
       </c>
       <c r="DG15" t="str">
-        <v>695.3231</v>
+        <v>695.4328</v>
       </c>
       <c r="DH15" t="str">
-        <v>1.011922</v>
+        <v>1.012763</v>
       </c>
       <c r="DI15" t="str">
-        <v>1.030286</v>
+        <v>1.030769</v>
       </c>
       <c r="DJ15" t="str">
-        <v>0.989232</v>
+        <v>0.988792</v>
       </c>
       <c r="DK15" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL15" t="str">
         <v>0</v>
@@ -5340,7 +5353,7 @@
         <v>50</v>
       </c>
       <c r="G16" t="str">
-        <v>0.005286</v>
+        <v>0.006849</v>
       </c>
       <c r="H16" t="str">
         <v>53.84</v>
@@ -5355,10 +5368,10 @@
         <v>58.98</v>
       </c>
       <c r="L16" t="str">
-        <v>53.149</v>
+        <v>53.157</v>
       </c>
       <c r="M16" t="str">
-        <v>47.8393</v>
+        <v>47.8465</v>
       </c>
       <c r="N16" t="str">
         <v>9882.86</v>
@@ -5418,7 +5431,7 @@
         <v>79.77</v>
       </c>
       <c r="AG16" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH16" t="str">
         <v>69.23</v>
@@ -5475,7 +5488,7 @@
         <v>138.8</v>
       </c>
       <c r="AZ16" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA16" t="str">
         <v>27.2</v>
@@ -5484,46 +5497,46 @@
         <v>3.07</v>
       </c>
       <c r="BC16" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE16" t="str">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF16" t="str">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="BG16" t="str">
         <v>259.1</v>
       </c>
       <c r="BH16" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ16" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL16" t="str">
-        <v>85.9739</v>
+        <v>86.0454</v>
       </c>
       <c r="BM16" t="str">
-        <v>87.5342</v>
+        <v>87.5751</v>
       </c>
       <c r="BN16" t="str">
-        <v>84.8354</v>
+        <v>84.8259</v>
       </c>
       <c r="BO16" t="str">
-        <v>85.0481</v>
+        <v>85.081</v>
       </c>
       <c r="BP16" t="str">
-        <v>84.1245</v>
+        <v>84.0886</v>
       </c>
       <c r="BQ16" t="str">
         <v>84.961</v>
       </c>
       <c r="BR16" t="str">
-        <v>84.7765</v>
+        <v>84.7631</v>
       </c>
       <c r="BS16" t="str">
-        <v>21865.11</v>
+        <v>21873.52</v>
       </c>
       <c r="BT16" t="str">
         <v>124369.7456</v>
@@ -5613,13 +5626,13 @@
         <v>0</v>
       </c>
       <c r="CW16" t="str">
-        <v>-0.311</v>
+        <v>-0.307</v>
       </c>
       <c r="CX16" t="str">
         <v>4.566</v>
       </c>
       <c r="CY16" t="str">
-        <v>1.6609</v>
+        <v>1.7134</v>
       </c>
       <c r="CZ16" t="str">
         <v>-2.3414</v>
@@ -5634,28 +5647,28 @@
         <v>0.1322</v>
       </c>
       <c r="DD16" t="str">
-        <v>1478.401</v>
+        <v>1479.0322</v>
       </c>
       <c r="DE16" t="str">
         <v>0.474</v>
       </c>
       <c r="DF16" t="str">
-        <v>1045.6544</v>
+        <v>1045.2501</v>
       </c>
       <c r="DG16" t="str">
-        <v>695.3234</v>
+        <v>695.4333</v>
       </c>
       <c r="DH16" t="str">
-        <v>1.011922</v>
+        <v>1.012764</v>
       </c>
       <c r="DI16" t="str">
-        <v>1.030287</v>
+        <v>1.030768</v>
       </c>
       <c r="DJ16" t="str">
-        <v>0.989232</v>
+        <v>0.988792</v>
       </c>
       <c r="DK16" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL16" t="str">
         <v>0</v>
@@ -5693,7 +5706,7 @@
         <v>49.88</v>
       </c>
       <c r="G17" t="str">
-        <v>0.005297</v>
+        <v>0.006833</v>
       </c>
       <c r="H17" t="str">
         <v>53.49</v>
@@ -5708,10 +5721,10 @@
         <v>59.26</v>
       </c>
       <c r="L17" t="str">
-        <v>52.653</v>
+        <v>52.661</v>
       </c>
       <c r="M17" t="str">
-        <v>47.3928</v>
+        <v>47.4</v>
       </c>
       <c r="N17" t="str">
         <v>9838</v>
@@ -5771,7 +5784,7 @@
         <v>79.77</v>
       </c>
       <c r="AG17" t="str">
-        <v>106.83</v>
+        <v>106.86</v>
       </c>
       <c r="AH17" t="str">
         <v>70.08</v>
@@ -5828,7 +5841,7 @@
         <v>138.8</v>
       </c>
       <c r="AZ17" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA17" t="str">
         <v>27.2</v>
@@ -5837,46 +5850,46 @@
         <v>3.07</v>
       </c>
       <c r="BC17" t="str">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="str">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="BF17" t="str">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="BG17" t="str">
         <v>259.1</v>
       </c>
       <c r="BH17" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ17" t="str">
         <v>2.2733</v>
       </c>
       <c r="BL17" t="str">
-        <v>86.4253</v>
+        <v>86.4972</v>
       </c>
       <c r="BM17" t="str">
-        <v>87.9938</v>
+        <v>88.0349</v>
       </c>
       <c r="BN17" t="str">
-        <v>85.2808</v>
+        <v>85.2713</v>
       </c>
       <c r="BO17" t="str">
-        <v>85.4947</v>
+        <v>85.5277</v>
       </c>
       <c r="BP17" t="str">
-        <v>84.5662</v>
+        <v>84.5301</v>
       </c>
       <c r="BQ17" t="str">
         <v>85.4071</v>
       </c>
       <c r="BR17" t="str">
-        <v>85.2217</v>
+        <v>85.2082</v>
       </c>
       <c r="BS17" t="str">
-        <v>21916.42</v>
+        <v>21967.33</v>
       </c>
       <c r="BT17" t="str">
         <v>125022.7669</v>
@@ -5966,13 +5979,13 @@
         <v>0</v>
       </c>
       <c r="CW17" t="str">
-        <v>0.0065</v>
+        <v>0.0169</v>
       </c>
       <c r="CX17" t="str">
         <v>4.712</v>
       </c>
       <c r="CY17" t="str">
-        <v>1.6195</v>
+        <v>1.672</v>
       </c>
       <c r="CZ17" t="str">
         <v>-0.4539</v>
@@ -5987,28 +6000,28 @@
         <v>0.3807</v>
       </c>
       <c r="DD17" t="str">
-        <v>1478.4011</v>
+        <v>1479.0325</v>
       </c>
       <c r="DE17" t="str">
         <v>0.474</v>
       </c>
       <c r="DF17" t="str">
-        <v>1045.6539</v>
+        <v>1045.2504</v>
       </c>
       <c r="DG17" t="str">
-        <v>695.3228</v>
+        <v>695.433</v>
       </c>
       <c r="DH17" t="str">
-        <v>1.011922</v>
+        <v>1.012764</v>
       </c>
       <c r="DI17" t="str">
-        <v>1.030287</v>
+        <v>1.030768</v>
       </c>
       <c r="DJ17" t="str">
-        <v>0.989232</v>
+        <v>0.988792</v>
       </c>
       <c r="DK17" t="str">
-        <v>1.021104</v>
+        <v>1.021766</v>
       </c>
       <c r="DL17" t="str">
         <v>0</v>
@@ -6023,12 +6036,12 @@
         <v>0</v>
       </c>
       <c r="DP17" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B18" t="str">
         <v>Hafta 1</v>
@@ -6046,7 +6059,7 @@
         <v>48.22</v>
       </c>
       <c r="G18" t="str">
-        <v>0.005161</v>
+        <v>0.006605</v>
       </c>
       <c r="H18" t="str">
         <v>52.83</v>
@@ -6124,7 +6137,7 @@
         <v>80.96</v>
       </c>
       <c r="AG18" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH18" t="str">
         <v>72.5</v>
@@ -6190,19 +6203,19 @@
         <v>3.06</v>
       </c>
       <c r="BC18" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE18" t="str">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="BF18" t="str">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="BG18" t="str">
         <v>259.1</v>
       </c>
       <c r="BH18" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ18" t="str">
         <v>2.2733</v>
@@ -6229,7 +6242,7 @@
         <v>84.3232</v>
       </c>
       <c r="BS18" t="str">
-        <v>22147.86</v>
+        <v>22185.11</v>
       </c>
       <c r="BT18" t="str">
         <v>104504.93</v>
@@ -6319,13 +6332,13 @@
         <v>0</v>
       </c>
       <c r="CW18" t="str">
-        <v>0.5582</v>
+        <v>0.5786</v>
       </c>
       <c r="CX18" t="str">
         <v>5.52</v>
       </c>
       <c r="CY18" t="str">
-        <v>1.4972</v>
+        <v>1.5497</v>
       </c>
       <c r="CZ18" t="str">
         <v>1.0287</v>
@@ -6399,7 +6412,7 @@
         <v>47.7</v>
       </c>
       <c r="G19" t="str">
-        <v>0.005235</v>
+        <v>0.006534</v>
       </c>
       <c r="H19" t="str">
         <v>52.46</v>
@@ -6477,7 +6490,7 @@
         <v>80.96</v>
       </c>
       <c r="AG19" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH19" t="str">
         <v>69.98</v>
@@ -6534,7 +6547,7 @@
         <v>168.8</v>
       </c>
       <c r="AZ19" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA19" t="str">
         <v>25.38</v>
@@ -6543,19 +6556,19 @@
         <v>3.06</v>
       </c>
       <c r="BC19" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE19" t="str">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="BF19" t="str">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="BG19" t="str">
         <v>260.67</v>
       </c>
       <c r="BH19" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ19" t="str">
         <v>2.2733</v>
@@ -6582,7 +6595,7 @@
         <v>84.3863</v>
       </c>
       <c r="BS19" t="str">
-        <v>22355.51</v>
+        <v>22460.34</v>
       </c>
       <c r="BT19" t="str">
         <v>105967.0532</v>
@@ -6672,13 +6685,13 @@
         <v>0</v>
       </c>
       <c r="CW19" t="str">
-        <v>-0.0527</v>
+        <v>-0.0438</v>
       </c>
       <c r="CX19" t="str">
         <v>5.712</v>
       </c>
       <c r="CY19" t="str">
-        <v>1.4504</v>
+        <v>1.5029</v>
       </c>
       <c r="CZ19" t="str">
         <v>0.3292</v>
@@ -6752,7 +6765,7 @@
         <v>47.5</v>
       </c>
       <c r="G20" t="str">
-        <v>0.005134</v>
+        <v>0.006507</v>
       </c>
       <c r="H20" t="str">
         <v>52.25</v>
@@ -6830,7 +6843,7 @@
         <v>80.96</v>
       </c>
       <c r="AG20" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH20" t="str">
         <v>68.3</v>
@@ -6887,7 +6900,7 @@
         <v>168.8</v>
       </c>
       <c r="AZ20" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA20" t="str">
         <v>25.38</v>
@@ -6896,19 +6909,19 @@
         <v>3.06</v>
       </c>
       <c r="BC20" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="str">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="BF20" t="str">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BG20" t="str">
         <v>269.49</v>
       </c>
       <c r="BH20" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ20" t="str">
         <v>2.2733</v>
@@ -6935,7 +6948,7 @@
         <v>84.6836</v>
       </c>
       <c r="BS20" t="str">
-        <v>22822.38</v>
+        <v>22850.97</v>
       </c>
       <c r="BT20" t="str">
         <v>106720.7551</v>
@@ -7025,13 +7038,13 @@
         <v>0</v>
       </c>
       <c r="CW20" t="str">
-        <v>-0.2966</v>
+        <v>-0.2923</v>
       </c>
       <c r="CX20" t="str">
         <v>5.642</v>
       </c>
       <c r="CY20" t="str">
-        <v>1.4387</v>
+        <v>1.4912</v>
       </c>
       <c r="CZ20" t="str">
         <v>-1.6571</v>
@@ -7105,7 +7118,7 @@
         <v>47</v>
       </c>
       <c r="G21" t="str">
-        <v>0.005134</v>
+        <v>0.006438</v>
       </c>
       <c r="H21" t="str">
         <v>51.41</v>
@@ -7183,7 +7196,7 @@
         <v>80.96</v>
       </c>
       <c r="AG21" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH21" t="str">
         <v>67.09</v>
@@ -7240,7 +7253,7 @@
         <v>168.8</v>
       </c>
       <c r="AZ21" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA21" t="str">
         <v>25.38</v>
@@ -7249,19 +7262,19 @@
         <v>3.06</v>
       </c>
       <c r="BC21" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE21" t="str">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="BF21" t="str">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="BG21" t="str">
         <v>264.84</v>
       </c>
       <c r="BH21" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ21" t="str">
         <v>2.2733</v>
@@ -7288,7 +7301,7 @@
         <v>85.306</v>
       </c>
       <c r="BS21" t="str">
-        <v>22928.94</v>
+        <v>22930.73</v>
       </c>
       <c r="BT21" t="str">
         <v>107308.6718</v>
@@ -7378,13 +7391,13 @@
         <v>0</v>
       </c>
       <c r="CW21" t="str">
-        <v>-0.8057</v>
+        <v>-0.8107</v>
       </c>
       <c r="CX21" t="str">
         <v>4.9567</v>
       </c>
       <c r="CY21" t="str">
-        <v>1.4258</v>
+        <v>1.4783</v>
       </c>
       <c r="CZ21" t="str">
         <v>2.6889</v>
@@ -7458,7 +7471,7 @@
         <v>45</v>
       </c>
       <c r="G22" t="str">
-        <v>0.005814</v>
+        <v>0.006164</v>
       </c>
       <c r="H22" t="str">
         <v>50.7</v>
@@ -7536,7 +7549,7 @@
         <v>80.96</v>
       </c>
       <c r="AG22" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH22" t="str">
         <v>63.84</v>
@@ -7593,7 +7606,7 @@
         <v>168.8</v>
       </c>
       <c r="AZ22" t="str">
-        <v>2.7946</v>
+        <v>2.7346</v>
       </c>
       <c r="BA22" t="str">
         <v>25.38</v>
@@ -7602,10 +7615,10 @@
         <v>3.06</v>
       </c>
       <c r="BC22" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE22" t="str">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="BF22" t="str">
         <v>69</v>
@@ -7614,7 +7627,7 @@
         <v>256.49</v>
       </c>
       <c r="BH22" t="str">
-        <v>2.4453</v>
+        <v>2.3928</v>
       </c>
       <c r="BJ22" t="str">
         <v>2.2733</v>
@@ -7641,7 +7654,7 @@
         <v>85.8956</v>
       </c>
       <c r="BS22" t="str">
-        <v>23073.31</v>
+        <v>23121.66</v>
       </c>
       <c r="BT22" t="str">
         <v>107769.5109</v>
@@ -7731,13 +7744,13 @@
         <v>0</v>
       </c>
       <c r="CW22" t="str">
-        <v>-0.2007</v>
+        <v>-0.1945</v>
       </c>
       <c r="CX22" t="str">
         <v>6.292</v>
       </c>
       <c r="CY22" t="str">
-        <v>1.2554</v>
+        <v>1.3079</v>
       </c>
       <c r="CZ22" t="str">
         <v>-0.1365</v>
@@ -7811,7 +7824,7 @@
         <v>45</v>
       </c>
       <c r="G23" t="str">
-        <v>0.004118</v>
+        <v>0.006164</v>
       </c>
       <c r="H23" t="str">
         <v>49.79</v>
@@ -7889,7 +7902,7 @@
         <v>80.96</v>
       </c>
       <c r="AG23" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH23" t="str">
         <v>64.62</v>
@@ -7955,13 +7968,13 @@
         <v>3.06</v>
       </c>
       <c r="BC23" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE23" t="str">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="BF23" t="str">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BG23" t="str">
         <v>251.3</v>
@@ -7994,7 +8007,7 @@
         <v>87.402</v>
       </c>
       <c r="BS23" t="str">
-        <v>23351.33</v>
+        <v>23400.88</v>
       </c>
       <c r="BT23" t="str">
         <v>108593.4463</v>
@@ -8084,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="CW23" t="str">
-        <v>-0.1488</v>
+        <v>-0.1418</v>
       </c>
       <c r="CX23" t="str">
         <v>5.192</v>
@@ -8164,7 +8177,7 @@
         <v>45</v>
       </c>
       <c r="G24" t="str">
-        <v>0.004352</v>
+        <v>0.006164</v>
       </c>
       <c r="H24" t="str">
         <v>49.46</v>
@@ -8242,7 +8255,7 @@
         <v>80.96</v>
       </c>
       <c r="AG24" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH24" t="str">
         <v>64.13</v>
@@ -8308,13 +8321,13 @@
         <v>3.06</v>
       </c>
       <c r="BC24" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE24" t="str">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF24" t="str">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BG24" t="str">
         <v>249.32</v>
@@ -8347,7 +8360,7 @@
         <v>89.1761</v>
       </c>
       <c r="BS24" t="str">
-        <v>23592.03</v>
+        <v>23641.68</v>
       </c>
       <c r="BT24" t="str">
         <v>109673.8497</v>
@@ -8437,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="CW24" t="str">
-        <v>-0.2662</v>
+        <v>-0.2612</v>
       </c>
       <c r="CX24" t="str">
         <v>4.882</v>
@@ -8517,7 +8530,7 @@
         <v>45</v>
       </c>
       <c r="G25" t="str">
-        <v>0.004668</v>
+        <v>0.006164</v>
       </c>
       <c r="H25" t="str">
         <v>49</v>
@@ -8595,7 +8608,7 @@
         <v>80.96</v>
       </c>
       <c r="AG25" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH25" t="str">
         <v>63.11</v>
@@ -8661,13 +8674,13 @@
         <v>3.06</v>
       </c>
       <c r="BC25" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE25" t="str">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="BF25" t="str">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="BG25" t="str">
         <v>242.98</v>
@@ -8700,7 +8713,7 @@
         <v>90.6629</v>
       </c>
       <c r="BS25" t="str">
-        <v>23983.52</v>
+        <v>24091.89</v>
       </c>
       <c r="BT25" t="str">
         <v>110779.0844</v>
@@ -8790,7 +8803,7 @@
         <v>0</v>
       </c>
       <c r="CW25" t="str">
-        <v>-0.4273</v>
+        <v>-0.4254</v>
       </c>
       <c r="CX25" t="str">
         <v>4.388</v>
@@ -8870,7 +8883,7 @@
         <v>45</v>
       </c>
       <c r="G26" t="str">
-        <v>0.004644</v>
+        <v>0.006164</v>
       </c>
       <c r="H26" t="str">
         <v>48.81</v>
@@ -8948,7 +8961,7 @@
         <v>80.96</v>
       </c>
       <c r="AG26" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH26" t="str">
         <v>64.76</v>
@@ -9014,13 +9027,13 @@
         <v>3.06</v>
       </c>
       <c r="BC26" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE26" t="str">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="BF26" t="str">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BG26" t="str">
         <v>252.25</v>
@@ -9053,7 +9066,7 @@
         <v>92.8936</v>
       </c>
       <c r="BS26" t="str">
-        <v>24527.8</v>
+        <v>24578.15</v>
       </c>
       <c r="BT26" t="str">
         <v>112083.0909</v>
@@ -9110,7 +9123,7 @@
         <v>0</v>
       </c>
       <c r="CL26" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM26" t="str">
         <v>0</v>
@@ -9143,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="CW26" t="str">
-        <v>-0.0788</v>
+        <v>-0.0707</v>
       </c>
       <c r="CX26" t="str">
         <v>4.118</v>
@@ -9223,7 +9236,7 @@
         <v>44.5</v>
       </c>
       <c r="G27" t="str">
-        <v>0.004784</v>
+        <v>0.006096</v>
       </c>
       <c r="H27" t="str">
         <v>47.44</v>
@@ -9301,7 +9314,7 @@
         <v>80.96</v>
       </c>
       <c r="AG27" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH27" t="str">
         <v>64.12</v>
@@ -9367,13 +9380,13 @@
         <v>3.06</v>
       </c>
       <c r="BC27" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE27" t="str">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="BF27" t="str">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="BG27" t="str">
         <v>255.47</v>
@@ -9406,7 +9419,7 @@
         <v>93.0854</v>
       </c>
       <c r="BS27" t="str">
-        <v>24777.4</v>
+        <v>24830.22</v>
       </c>
       <c r="BT27" t="str">
         <v>113174.8145</v>
@@ -9463,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="CL27" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM27" t="str">
         <v>0</v>
@@ -9496,7 +9509,7 @@
         <v>1</v>
       </c>
       <c r="CW27" t="str">
-        <v>0.4261</v>
+        <v>0.4434</v>
       </c>
       <c r="CX27" t="str">
         <v>3.138</v>
@@ -9576,7 +9589,7 @@
         <v>42.5</v>
       </c>
       <c r="G28" t="str">
-        <v>0.004415</v>
+        <v>0.005822</v>
       </c>
       <c r="H28" t="str">
         <v>47.11</v>
@@ -9654,7 +9667,7 @@
         <v>80.96</v>
       </c>
       <c r="AG28" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH28" t="str">
         <v>62.73</v>
@@ -9720,10 +9733,10 @@
         <v>3.06</v>
       </c>
       <c r="BC28" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE28" t="str">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="BF28" t="str">
         <v>61</v>
@@ -9759,7 +9772,7 @@
         <v>93.1183</v>
       </c>
       <c r="BS28" t="str">
-        <v>25142.66</v>
+        <v>25220.56</v>
       </c>
       <c r="BT28" t="str">
         <v>113623.4813</v>
@@ -9816,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="CL28" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM28" t="str">
         <v>0</v>
@@ -9849,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="CW28" t="str">
-        <v>0.4222</v>
+        <v>0.4394</v>
       </c>
       <c r="CX28" t="str">
         <v>4.788</v>
@@ -9929,7 +9942,7 @@
         <v>42.5</v>
       </c>
       <c r="G29" t="str">
-        <v>0.003691</v>
+        <v>0.005822</v>
       </c>
       <c r="H29" t="str">
         <v>47.1</v>
@@ -10007,7 +10020,7 @@
         <v>80.96</v>
       </c>
       <c r="AG29" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH29" t="str">
         <v>63.74</v>
@@ -10073,10 +10086,10 @@
         <v>3.06</v>
       </c>
       <c r="BC29" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE29" t="str">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="BF29" t="str">
         <v>61</v>
@@ -10112,7 +10125,7 @@
         <v>94.6574</v>
       </c>
       <c r="BS29" t="str">
-        <v>25303.01</v>
+        <v>25315.9</v>
       </c>
       <c r="BT29" t="str">
         <v>114027.598</v>
@@ -10169,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="CL29" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM29" t="str">
         <v>0</v>
@@ -10202,7 +10215,7 @@
         <v>0</v>
       </c>
       <c r="CW29" t="str">
-        <v>2.2758</v>
+        <v>2.3278</v>
       </c>
       <c r="CX29" t="str">
         <v>3.97</v>
@@ -10282,7 +10295,7 @@
         <v>45.27</v>
       </c>
       <c r="G30" t="str">
-        <v>0.001136</v>
+        <v>0.006201</v>
       </c>
       <c r="H30" t="str">
         <v>49.11</v>
@@ -10360,7 +10373,7 @@
         <v>80.96</v>
       </c>
       <c r="AG30" t="str">
-        <v>109.85</v>
+        <v>109.93</v>
       </c>
       <c r="AH30" t="str">
         <v>72.45</v>
@@ -10426,13 +10439,13 @@
         <v>3.06</v>
       </c>
       <c r="BC30" t="str">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE30" t="str">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="BF30" t="str">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="BG30" t="str">
         <v>307.55</v>
@@ -10465,7 +10478,7 @@
         <v>95.8378</v>
       </c>
       <c r="BS30" t="str">
-        <v>25429.3</v>
+        <v>25512</v>
       </c>
       <c r="BT30" t="str">
         <v>114353.4474</v>
@@ -10522,7 +10535,7 @@
         <v>1</v>
       </c>
       <c r="CL30" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM30" t="str">
         <v>0</v>
@@ -10555,7 +10568,7 @@
         <v>1</v>
       </c>
       <c r="CW30" t="str">
-        <v>3.9429</v>
+        <v>4.0258</v>
       </c>
       <c r="CX30" t="str">
         <v>3.125</v>
@@ -10635,7 +10648,7 @@
         <v>46</v>
       </c>
       <c r="G31" t="str">
-        <v>0.004469</v>
+        <v>0.006301</v>
       </c>
       <c r="H31" t="str">
         <v>49.24</v>
@@ -10713,7 +10726,7 @@
         <v>83.86</v>
       </c>
       <c r="AG31" t="str">
-        <v>107.36</v>
+        <v>106.95</v>
       </c>
       <c r="AH31" t="str">
         <v>67.85</v>
@@ -10782,10 +10795,10 @@
         <v>8.5</v>
       </c>
       <c r="BE31" t="str">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="BF31" t="str">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG31" t="str">
         <v>312.94</v>
@@ -10818,7 +10831,7 @@
         <v>95.8967</v>
       </c>
       <c r="BS31" t="str">
-        <v>25796.04</v>
+        <v>25803.81</v>
       </c>
       <c r="BT31" t="str">
         <v>115189.4333</v>
@@ -10908,7 +10921,7 @@
         <v>1</v>
       </c>
       <c r="CW31" t="str">
-        <v>1.1893</v>
+        <v>1.2249</v>
       </c>
       <c r="CX31" t="str">
         <v>3.25</v>
@@ -10988,7 +11001,7 @@
         <v>46</v>
       </c>
       <c r="G32" t="str">
-        <v>0.003662</v>
+        <v>0.006301</v>
       </c>
       <c r="H32" t="str">
         <v>49.8</v>
@@ -11066,7 +11079,7 @@
         <v>83.86</v>
       </c>
       <c r="AG32" t="str">
-        <v>107.36</v>
+        <v>106.95</v>
       </c>
       <c r="AH32" t="str">
         <v>69.67</v>
@@ -11135,10 +11148,10 @@
         <v>8.5</v>
       </c>
       <c r="BE32" t="str">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="BF32" t="str">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BG32" t="str">
         <v>353.68</v>
@@ -11171,7 +11184,7 @@
         <v>96.0944</v>
       </c>
       <c r="BS32" t="str">
-        <v>25710.92</v>
+        <v>25723.22</v>
       </c>
       <c r="BT32" t="str">
         <v>116168.4424</v>
@@ -11261,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="CW32" t="str">
-        <v>1.6151</v>
+        <v>1.6539</v>
       </c>
       <c r="CX32" t="str">
         <v>3.8</v>
@@ -11341,7 +11354,7 @@
         <v>46.39</v>
       </c>
       <c r="G33" t="str">
-        <v>0.004780</v>
+        <v>0.006355</v>
       </c>
       <c r="H33" t="str">
         <v>51.17</v>
@@ -11419,7 +11432,7 @@
         <v>83.86</v>
       </c>
       <c r="AG33" t="str">
-        <v>107.36</v>
+        <v>106.95</v>
       </c>
       <c r="AH33" t="str">
         <v>70.58</v>
@@ -11488,7 +11501,7 @@
         <v>8.5</v>
       </c>
       <c r="BE33" t="str">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="BF33" t="str">
         <v>100</v>
@@ -11524,7 +11537,7 @@
         <v>96.9784</v>
       </c>
       <c r="BS33" t="str">
-        <v>25847.99</v>
+        <v>25897.63</v>
       </c>
       <c r="BT33" t="str">
         <v>116663.9722</v>
@@ -11614,7 +11627,7 @@
         <v>0</v>
       </c>
       <c r="CW33" t="str">
-        <v>0.8229</v>
+        <v>0.8475</v>
       </c>
       <c r="CX33" t="str">
         <v>4.572</v>
@@ -11694,7 +11707,7 @@
         <v>48.23</v>
       </c>
       <c r="G34" t="str">
-        <v>0.005911</v>
+        <v>0.006607</v>
       </c>
       <c r="H34" t="str">
         <v>52.18</v>
@@ -11772,7 +11785,7 @@
         <v>83.86</v>
       </c>
       <c r="AG34" t="str">
-        <v>107.36</v>
+        <v>106.95</v>
       </c>
       <c r="AH34" t="str">
         <v>73.09</v>
@@ -11840,14 +11853,11 @@
       <c r="BC34" t="str">
         <v>8.5</v>
       </c>
-      <c r="BD34" t="str">
-        <v>2.05693E+12</v>
-      </c>
       <c r="BE34" t="str">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BF34" t="str">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BG34" t="str">
         <v>327.57</v>
@@ -11880,7 +11890,7 @@
         <v>96.6513</v>
       </c>
       <c r="BS34" t="str">
-        <v>25733.53</v>
+        <v>25772.19</v>
       </c>
       <c r="BT34" t="str">
         <v>116600.1899</v>
@@ -11970,7 +11980,7 @@
         <v>1</v>
       </c>
       <c r="CW34" t="str">
-        <v>0.901</v>
+        <v>0.9251</v>
       </c>
       <c r="CX34" t="str">
         <v>3.19</v>
@@ -12027,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="DP34" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -12050,7 +12060,7 @@
         <v>48.79</v>
       </c>
       <c r="G35" t="str">
-        <v>0.005056</v>
+        <v>0.006684</v>
       </c>
       <c r="H35" t="str">
         <v>53.94</v>
@@ -12128,7 +12138,7 @@
         <v>84.79</v>
       </c>
       <c r="AG35" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH35" t="str">
         <v>74.03</v>
@@ -12196,14 +12206,11 @@
       <c r="BC35" t="str">
         <v>7.6</v>
       </c>
-      <c r="BD35" t="str">
-        <v>6.07328E+12</v>
-      </c>
       <c r="BE35" t="str">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="BF35" t="str">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="BG35" t="str">
         <v>327.57</v>
@@ -12236,7 +12243,7 @@
         <v>97.0591</v>
       </c>
       <c r="BS35" t="str">
-        <v>25721.95</v>
+        <v>25675.62</v>
       </c>
       <c r="BT35" t="str">
         <v>143144.49</v>
@@ -12326,7 +12333,7 @@
         <v>0</v>
       </c>
       <c r="CW35" t="str">
-        <v>0.5257</v>
+        <v>0.5491</v>
       </c>
       <c r="CX35" t="str">
         <v>4.95</v>
@@ -12406,7 +12413,7 @@
         <v>48.79</v>
       </c>
       <c r="G36" t="str">
-        <v>0.005332</v>
+        <v>0.006684</v>
       </c>
       <c r="H36" t="str">
         <v>54.52</v>
@@ -12484,7 +12491,7 @@
         <v>84.79</v>
       </c>
       <c r="AG36" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH36" t="str">
         <v>74.59</v>
@@ -12552,14 +12559,11 @@
       <c r="BC36" t="str">
         <v>7.6</v>
       </c>
-      <c r="BD36" t="str">
-        <v>5.39498E+12</v>
-      </c>
       <c r="BE36" t="str">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF36" t="str">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BG36" t="str">
         <v>332.69</v>
@@ -12592,7 +12596,7 @@
         <v>97.378</v>
       </c>
       <c r="BS36" t="str">
-        <v>25722.27</v>
+        <v>25708.49</v>
       </c>
       <c r="BT36" t="str">
         <v>144015.8099</v>
@@ -12682,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="CW36" t="str">
-        <v>0.0939</v>
+        <v>0.1051</v>
       </c>
       <c r="CX36" t="str">
         <v>5.53</v>
@@ -12762,7 +12766,7 @@
         <v>48.43</v>
       </c>
       <c r="G37" t="str">
-        <v>0.005079</v>
+        <v>0.006634</v>
       </c>
       <c r="H37" t="str">
         <v>55.13</v>
@@ -12840,7 +12844,7 @@
         <v>84.79</v>
       </c>
       <c r="AG37" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH37" t="str">
         <v>73.52</v>
@@ -12908,14 +12912,11 @@
       <c r="BC37" t="str">
         <v>7.6</v>
       </c>
-      <c r="BD37" t="str">
-        <v>1.39723E+13</v>
-      </c>
       <c r="BE37" t="str">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="BF37" t="str">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="BG37" t="str">
         <v>299.89</v>
@@ -12948,7 +12949,7 @@
         <v>97.8789</v>
       </c>
       <c r="BS37" t="str">
-        <v>25362.99</v>
+        <v>25418.2</v>
       </c>
       <c r="BT37" t="str">
         <v>144304.5118</v>
@@ -13038,7 +13039,7 @@
         <v>0</v>
       </c>
       <c r="CW37" t="str">
-        <v>0.1368</v>
+        <v>0.1489</v>
       </c>
       <c r="CX37" t="str">
         <v>6.142</v>
@@ -13118,7 +13119,7 @@
         <v>47.01</v>
       </c>
       <c r="G38" t="str">
-        <v>0.004183</v>
+        <v>0.006440</v>
       </c>
       <c r="H38" t="str">
         <v>55.32</v>
@@ -13196,7 +13197,7 @@
         <v>84.79</v>
       </c>
       <c r="AG38" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH38" t="str">
         <v>71.23</v>
@@ -13264,14 +13265,11 @@
       <c r="BC38" t="str">
         <v>7.6</v>
       </c>
-      <c r="BD38" t="str">
-        <v>1.55198E+13</v>
-      </c>
       <c r="BE38" t="str">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BF38" t="str">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BG38" t="str">
         <v>294.06</v>
@@ -13304,7 +13302,7 @@
         <v>98.4855</v>
       </c>
       <c r="BS38" t="str">
-        <v>25550.56</v>
+        <v>25570.75</v>
       </c>
       <c r="BT38" t="str">
         <v>144840.9493</v>
@@ -13394,7 +13392,7 @@
         <v>0</v>
       </c>
       <c r="CW38" t="str">
-        <v>0.04</v>
+        <v>0.0546</v>
       </c>
       <c r="CX38" t="str">
         <v>7.27</v>
@@ -13474,7 +13472,7 @@
         <v>48.97</v>
       </c>
       <c r="G39" t="str">
-        <v>0.005660</v>
+        <v>0.006708</v>
       </c>
       <c r="H39" t="str">
         <v>55.5</v>
@@ -13552,7 +13550,7 @@
         <v>84.79</v>
       </c>
       <c r="AG39" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH39" t="str">
         <v>73.39</v>
@@ -13620,11 +13618,8 @@
       <c r="BC39" t="str">
         <v>7.6</v>
       </c>
-      <c r="BD39" t="str">
-        <v>1.01651E+13</v>
-      </c>
       <c r="BE39" t="str">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="BF39" t="str">
         <v>65</v>
@@ -13660,7 +13655,7 @@
         <v>98.9089</v>
       </c>
       <c r="BS39" t="str">
-        <v>25637.84</v>
+        <v>25654.7</v>
       </c>
       <c r="BT39" t="str">
         <v>145067.6802</v>
@@ -13750,7 +13745,7 @@
         <v>0</v>
       </c>
       <c r="CW39" t="str">
-        <v>-0.0778</v>
+        <v>-0.0693</v>
       </c>
       <c r="CX39" t="str">
         <v>6.51</v>
@@ -13830,7 +13825,7 @@
         <v>48.98</v>
       </c>
       <c r="G40" t="str">
-        <v>0.003384</v>
+        <v>0.006710</v>
       </c>
       <c r="H40" t="str">
         <v>55.47</v>
@@ -13908,7 +13903,7 @@
         <v>84.79</v>
       </c>
       <c r="AG40" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH40" t="str">
         <v>72.05</v>
@@ -13976,14 +13971,11 @@
       <c r="BC40" t="str">
         <v>7.6</v>
       </c>
-      <c r="BD40" t="str">
-        <v>7.71989E+12</v>
-      </c>
       <c r="BE40" t="str">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="BF40" t="str">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="BG40" t="str">
         <v>301.56</v>
@@ -14016,7 +14008,7 @@
         <v>99.6384</v>
       </c>
       <c r="BS40" t="str">
-        <v>25542.12</v>
+        <v>25517.76</v>
       </c>
       <c r="BT40" t="str">
         <v>145775.73</v>
@@ -14106,7 +14098,7 @@
         <v>0</v>
       </c>
       <c r="CW40" t="str">
-        <v>0.1648</v>
+        <v>0.1776</v>
       </c>
       <c r="CX40" t="str">
         <v>6.475</v>
@@ -14186,7 +14178,7 @@
         <v>47.16</v>
       </c>
       <c r="G41" t="str">
-        <v>0.003724</v>
+        <v>0.006460</v>
       </c>
       <c r="H41" t="str">
         <v>55.58</v>
@@ -14264,7 +14256,7 @@
         <v>84.79</v>
       </c>
       <c r="AG41" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH41" t="str">
         <v>70.89</v>
@@ -14332,14 +14324,11 @@
       <c r="BC41" t="str">
         <v>7.6</v>
       </c>
-      <c r="BD41" t="str">
-        <v>1.00266E+13</v>
-      </c>
       <c r="BE41" t="str">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="BF41" t="str">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="BG41" t="str">
         <v>293.02</v>
@@ -14372,7 +14361,7 @@
         <v>98.7423</v>
       </c>
       <c r="BS41" t="str">
-        <v>25533.4</v>
+        <v>25593.85</v>
       </c>
       <c r="BT41" t="str">
         <v>145756.513</v>
@@ -14462,7 +14451,7 @@
         <v>0</v>
       </c>
       <c r="CW41" t="str">
-        <v>0.1949</v>
+        <v>0.2127</v>
       </c>
       <c r="CX41" t="str">
         <v>7.1675</v>
@@ -14542,7 +14531,7 @@
         <v>46</v>
       </c>
       <c r="G42" t="str">
-        <v>0.005000</v>
+        <v>0.006301</v>
       </c>
       <c r="H42" t="str">
         <v>55.63</v>
@@ -14620,7 +14609,7 @@
         <v>84.79</v>
       </c>
       <c r="AG42" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH42" t="str">
         <v>70.95</v>
@@ -14689,13 +14678,13 @@
         <v>7.6</v>
       </c>
       <c r="BD42" t="str">
-        <v>6.72732E+12</v>
+        <v>6.20943E+12</v>
       </c>
       <c r="BE42" t="str">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="BF42" t="str">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BG42" t="str">
         <v>300.23</v>
@@ -14728,7 +14717,7 @@
         <v>99.2941</v>
       </c>
       <c r="BS42" t="str">
-        <v>25697.74</v>
+        <v>25693.43</v>
       </c>
       <c r="BT42" t="str">
         <v>146409.7422</v>
@@ -14818,7 +14807,7 @@
         <v>0</v>
       </c>
       <c r="CW42" t="str">
-        <v>0.4015</v>
+        <v>0.4188</v>
       </c>
       <c r="CX42" t="str">
         <v>9.216</v>
@@ -14898,7 +14887,7 @@
         <v>46</v>
       </c>
       <c r="G43" t="str">
-        <v>0.005195</v>
+        <v>0.006301</v>
       </c>
       <c r="H43" t="str">
         <v>55.62</v>
@@ -14976,7 +14965,7 @@
         <v>84.79</v>
       </c>
       <c r="AG43" t="str">
-        <v>110.99</v>
+        <v>110.92</v>
       </c>
       <c r="AH43" t="str">
         <v>69.12</v>
@@ -15048,10 +15037,10 @@
         <v>7.27362E+12</v>
       </c>
       <c r="BE43" t="str">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="BF43" t="str">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BG43" t="str">
         <v>300.17</v>
@@ -15084,7 +15073,7 @@
         <v>100.0479</v>
       </c>
       <c r="BS43" t="str">
-        <v>25489.41</v>
+        <v>25492.17</v>
       </c>
       <c r="BT43" t="str">
         <v>146801.3818</v>
@@ -15174,7 +15163,7 @@
         <v>0</v>
       </c>
       <c r="CW43" t="str">
-        <v>0.2172</v>
+        <v>0.2309</v>
       </c>
       <c r="CX43" t="str">
         <v>8.658</v>
@@ -15254,7 +15243,7 @@
         <v>46</v>
       </c>
       <c r="G44" t="str">
-        <v>0.005361</v>
+        <v>0.006301</v>
       </c>
       <c r="H44" t="str">
         <v>55.66</v>
@@ -15332,7 +15321,7 @@
         <v>83.52</v>
       </c>
       <c r="AG44" t="str">
-        <v>109.59</v>
+        <v>109.55</v>
       </c>
       <c r="AH44" t="str">
         <v>69.43</v>
@@ -15404,10 +15393,10 @@
         <v>5.99987E+12</v>
       </c>
       <c r="BE44" t="str">
+        <v>69</v>
+      </c>
+      <c r="BF44" t="str">
         <v>71</v>
-      </c>
-      <c r="BF44" t="str">
-        <v>69</v>
       </c>
       <c r="BG44" t="str">
         <v>278.85</v>
@@ -15440,7 +15429,7 @@
         <v>100.215</v>
       </c>
       <c r="BS44" t="str">
-        <v>25582.54</v>
+        <v>25636.06</v>
       </c>
       <c r="BT44" t="str">
         <v>133685.4</v>
@@ -15530,7 +15519,7 @@
         <v>0</v>
       </c>
       <c r="CW44" t="str">
-        <v>0.588</v>
+        <v>0.6084</v>
       </c>
       <c r="CX44" t="str">
         <v>9.294</v>
@@ -15610,7 +15599,7 @@
         <v>46</v>
       </c>
       <c r="G45" t="str">
-        <v>0.005178</v>
+        <v>0.006301</v>
       </c>
       <c r="H45" t="str">
         <v>55.02</v>
@@ -15688,7 +15677,7 @@
         <v>83.52</v>
       </c>
       <c r="AG45" t="str">
-        <v>109.59</v>
+        <v>109.55</v>
       </c>
       <c r="AH45" t="str">
         <v>70.57</v>
@@ -15760,10 +15749,10 @@
         <v>1.2122E+13</v>
       </c>
       <c r="BE45" t="str">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="BF45" t="str">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="BG45" t="str">
         <v>282.26</v>
@@ -15796,7 +15785,7 @@
         <v>100.106</v>
       </c>
       <c r="BS45" t="str">
-        <v>25772.05</v>
+        <v>25789.19</v>
       </c>
       <c r="BT45" t="str">
         <v>135054.6637</v>
@@ -15886,7 +15875,7 @@
         <v>0</v>
       </c>
       <c r="CW45" t="str">
-        <v>-0.0652</v>
+        <v>-0.0566</v>
       </c>
       <c r="CX45" t="str">
         <v>9.026</v>
@@ -15966,7 +15955,7 @@
         <v>46</v>
       </c>
       <c r="G46" t="str">
-        <v>0.005116</v>
+        <v>0.006301</v>
       </c>
       <c r="H46" t="str">
         <v>54.51</v>
@@ -16044,7 +16033,7 @@
         <v>83.52</v>
       </c>
       <c r="AG46" t="str">
-        <v>109.59</v>
+        <v>109.55</v>
       </c>
       <c r="AH46" t="str">
         <v>67.57</v>
@@ -16116,10 +16105,10 @@
         <v>2.62956E+13</v>
       </c>
       <c r="BE46" t="str">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="BF46" t="str">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BG46" t="str">
         <v>286.1</v>
@@ -16152,7 +16141,7 @@
         <v>100.3297</v>
       </c>
       <c r="BS46" t="str">
-        <v>25753.37</v>
+        <v>25789.72</v>
       </c>
       <c r="BT46" t="str">
         <v>135246.6781</v>
@@ -16242,7 +16231,7 @@
         <v>0</v>
       </c>
       <c r="CW46" t="str">
-        <v>-0.1988</v>
+        <v>-0.1928</v>
       </c>
       <c r="CX46" t="str">
         <v>8.91</v>
@@ -16322,7 +16311,7 @@
         <v>45.4</v>
       </c>
       <c r="G47" t="str">
-        <v>0.005219</v>
+        <v>0.006219</v>
       </c>
       <c r="H47" t="str">
         <v>52.59</v>
@@ -16400,7 +16389,7 @@
         <v>83.52</v>
       </c>
       <c r="AG47" t="str">
-        <v>109.59</v>
+        <v>109.55</v>
       </c>
       <c r="AH47" t="str">
         <v>65.17</v>
@@ -16472,10 +16461,10 @@
         <v>3.04227E+13</v>
       </c>
       <c r="BE47" t="str">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="BF47" t="str">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="BG47" t="str">
         <v>278.4</v>
@@ -16508,7 +16497,7 @@
         <v>100.6607</v>
       </c>
       <c r="BS47" t="str">
-        <v>25757.73</v>
+        <v>25787.46</v>
       </c>
       <c r="BT47" t="str">
         <v>135712.1148</v>
@@ -16598,7 +16587,7 @@
         <v>0</v>
       </c>
       <c r="CW47" t="str">
-        <v>-0.4096</v>
+        <v>-0.4075</v>
       </c>
       <c r="CX47" t="str">
         <v>7.514</v>
@@ -16678,7 +16667,7 @@
         <v>43</v>
       </c>
       <c r="G48" t="str">
-        <v>0.003628</v>
+        <v>0.005890</v>
       </c>
       <c r="H48" t="str">
         <v>52</v>
@@ -16756,7 +16745,7 @@
         <v>84.25</v>
       </c>
       <c r="AG48" t="str">
-        <v>110.1</v>
+        <v>110.09</v>
       </c>
       <c r="AH48" t="str">
         <v>63.74</v>
@@ -16828,10 +16817,10 @@
         <v>1.83903E+13</v>
       </c>
       <c r="BE48" t="str">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="BF48" t="str">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="BG48" t="str">
         <v>275.62</v>
@@ -16864,7 +16853,7 @@
         <v>101.0212</v>
       </c>
       <c r="BS48" t="str">
-        <v>25683.23</v>
+        <v>25738.66</v>
       </c>
       <c r="BT48" t="str">
         <v>135888.25</v>
@@ -16951,10 +16940,10 @@
         <v>0</v>
       </c>
       <c r="CV48" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW48" t="str">
-        <v>-0.5689</v>
+        <v>-0.5696</v>
       </c>
       <c r="CX48" t="str">
         <v>9.342</v>
@@ -17034,7 +17023,7 @@
         <v>43</v>
       </c>
       <c r="G49" t="str">
-        <v>0.005236</v>
+        <v>0.005890</v>
       </c>
       <c r="H49" t="str">
         <v>51.5</v>
@@ -17112,7 +17101,7 @@
         <v>84.25</v>
       </c>
       <c r="AG49" t="str">
-        <v>110.1</v>
+        <v>110.09</v>
       </c>
       <c r="AH49" t="str">
         <v>65.96</v>
@@ -17184,10 +17173,10 @@
         <v>1.38386E+13</v>
       </c>
       <c r="BE49" t="str">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="BF49" t="str">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="BG49" t="str">
         <v>275.42</v>
@@ -17220,7 +17209,7 @@
         <v>101.712</v>
       </c>
       <c r="BS49" t="str">
-        <v>25986.65</v>
+        <v>26064.75</v>
       </c>
       <c r="BT49" t="str">
         <v>136830.5584</v>
@@ -17310,7 +17299,7 @@
         <v>0</v>
       </c>
       <c r="CW49" t="str">
-        <v>-0.7689</v>
+        <v>-0.7733</v>
       </c>
       <c r="CX49" t="str">
         <v>8.742</v>
@@ -17390,7 +17379,7 @@
         <v>43</v>
       </c>
       <c r="G50" t="str">
-        <v>0.004426</v>
+        <v>0.005890</v>
       </c>
       <c r="H50" t="str">
         <v>51.31</v>
@@ -17468,7 +17457,7 @@
         <v>84.25</v>
       </c>
       <c r="AG50" t="str">
-        <v>110.1</v>
+        <v>110.09</v>
       </c>
       <c r="AH50" t="str">
         <v>64.73</v>
@@ -17540,10 +17529,10 @@
         <v>2.44236E+13</v>
       </c>
       <c r="BE50" t="str">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="BF50" t="str">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="BG50" t="str">
         <v>266.65</v>
@@ -17576,7 +17565,7 @@
         <v>101.6209</v>
       </c>
       <c r="BS50" t="str">
-        <v>26136.94</v>
+        <v>26117.89</v>
       </c>
       <c r="BT50" t="str">
         <v>137278.1717</v>
@@ -17666,7 +17655,7 @@
         <v>0</v>
       </c>
       <c r="CW50" t="str">
-        <v>-0.7672</v>
+        <v>-0.7715</v>
       </c>
       <c r="CX50" t="str">
         <v>8.65</v>
@@ -17746,7 +17735,7 @@
         <v>43</v>
       </c>
       <c r="G51" t="str">
-        <v>0.004912</v>
+        <v>0.005890</v>
       </c>
       <c r="H51" t="str">
         <v>51.05</v>
@@ -17824,7 +17813,7 @@
         <v>84.25</v>
       </c>
       <c r="AG51" t="str">
-        <v>110.1</v>
+        <v>110.09</v>
       </c>
       <c r="AH51" t="str">
         <v>66.23</v>
@@ -17896,10 +17885,10 @@
         <v>1.78698E+13</v>
       </c>
       <c r="BE51" t="str">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="BF51" t="str">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="BG51" t="str">
         <v>265.06</v>
@@ -17932,7 +17921,7 @@
         <v>102.0242</v>
       </c>
       <c r="BS51" t="str">
-        <v>26250.24</v>
+        <v>26202.96</v>
       </c>
       <c r="BT51" t="str">
         <v>137700.9697</v>
@@ -18022,10 +18011,10 @@
         <v>0</v>
       </c>
       <c r="CW51" t="str">
-        <v>-0.7042</v>
+        <v>-0.7073</v>
       </c>
       <c r="CX51" t="str">
-        <v>7.496</v>
+        <v>8.326</v>
       </c>
       <c r="CY51" t="str">
         <v>1.6198</v>
@@ -18102,7 +18091,7 @@
         <v>43</v>
       </c>
       <c r="G52" t="str">
-        <v>0.004707</v>
+        <v>0.005890</v>
       </c>
       <c r="H52" t="str">
         <v>51.1</v>
@@ -18180,7 +18169,7 @@
         <v>84.25</v>
       </c>
       <c r="AG52" t="str">
-        <v>110.1</v>
+        <v>110.09</v>
       </c>
       <c r="AH52" t="str">
         <v>65.83</v>
@@ -18252,10 +18241,10 @@
         <v>1.96531E+13</v>
       </c>
       <c r="BE52" t="str">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="BF52" t="str">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="BG52" t="str">
         <v>261.74</v>
@@ -18288,7 +18277,7 @@
         <v>103.1105</v>
       </c>
       <c r="BS52" t="str">
-        <v>26216.39</v>
+        <v>26308.02</v>
       </c>
       <c r="BT52" t="str">
         <v>138878.5534</v>
@@ -18378,10 +18367,10 @@
         <v>0</v>
       </c>
       <c r="CW52" t="str">
-        <v>-0.6113</v>
+        <v>-0.6127</v>
       </c>
       <c r="CX52" t="str">
-        <v>7.3175</v>
+        <v>8.4075</v>
       </c>
       <c r="CY52" t="str">
         <v>1.6172</v>
@@ -18458,7 +18447,7 @@
         <v>43</v>
       </c>
       <c r="G53" t="str">
-        <v>0.004662</v>
+        <v>0.005890</v>
       </c>
       <c r="H53" t="str">
         <v>50.73</v>
@@ -18536,7 +18525,7 @@
         <v>83.87</v>
       </c>
       <c r="AG53" t="str">
-        <v>108.03</v>
+        <v>108.01</v>
       </c>
       <c r="AH53" t="str">
         <v>65.66</v>
@@ -18608,10 +18597,10 @@
         <v>1.61492E+13</v>
       </c>
       <c r="BE53" t="str">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="BF53" t="str">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="BG53" t="str">
         <v>267.37</v>
@@ -18644,7 +18633,7 @@
         <v>104.0978</v>
       </c>
       <c r="BS53" t="str">
-        <v>26538.74</v>
+        <v>26580.58</v>
       </c>
       <c r="BT53" t="str">
         <v>136437.74</v>
@@ -18734,10 +18723,10 @@
         <v>0</v>
       </c>
       <c r="CW53" t="str">
-        <v>-0.2988</v>
+        <v>-0.2946</v>
       </c>
       <c r="CX53" t="str">
-        <v>7.026</v>
+        <v>7.916</v>
       </c>
       <c r="CY53" t="str">
         <v>0.9557</v>
@@ -18814,7 +18803,7 @@
         <v>42.63</v>
       </c>
       <c r="G54" t="str">
-        <v>0.004577</v>
+        <v>0.005840</v>
       </c>
       <c r="H54" t="str">
         <v>50.25</v>
@@ -18892,7 +18881,7 @@
         <v>83.87</v>
       </c>
       <c r="AG54" t="str">
-        <v>108.03</v>
+        <v>108.01</v>
       </c>
       <c r="AH54" t="str">
         <v>64.85</v>
@@ -18964,10 +18953,10 @@
         <v>1.73867E+13</v>
       </c>
       <c r="BE54" t="str">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="BF54" t="str">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="BG54" t="str">
         <v>266.81</v>
@@ -19000,7 +18989,7 @@
         <v>104.7441</v>
       </c>
       <c r="BS54" t="str">
-        <v>26745.88</v>
+        <v>26833.9</v>
       </c>
       <c r="BT54" t="str">
         <v>136983.3424</v>
@@ -19090,10 +19079,10 @@
         <v>0</v>
       </c>
       <c r="CW54" t="str">
-        <v>-0.318</v>
+        <v>-0.3141</v>
       </c>
       <c r="CX54" t="str">
-        <v>6.232</v>
+        <v>7.972</v>
       </c>
       <c r="CY54" t="str">
         <v>0.9111</v>
@@ -19170,7 +19159,7 @@
         <v>40.5</v>
       </c>
       <c r="G55" t="str">
-        <v>0.004595</v>
+        <v>0.005548</v>
       </c>
       <c r="H55" t="str">
         <v>50.02</v>
@@ -19248,7 +19237,7 @@
         <v>83.87</v>
       </c>
       <c r="AG55" t="str">
-        <v>108.03</v>
+        <v>108.01</v>
       </c>
       <c r="AH55" t="str">
         <v>59.99</v>
@@ -19320,7 +19309,7 @@
         <v>2.02598E+13</v>
       </c>
       <c r="BE55" t="str">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF55" t="str">
         <v>55</v>
@@ -19356,7 +19345,7 @@
         <v>105.5516</v>
       </c>
       <c r="BS55" t="str">
-        <v>27012.52</v>
+        <v>27138.28</v>
       </c>
       <c r="BT55" t="str">
         <v>137922.7149</v>
@@ -19446,10 +19435,10 @@
         <v>0</v>
       </c>
       <c r="CW55" t="str">
-        <v>0.5971</v>
+        <v>0.6175</v>
       </c>
       <c r="CX55" t="str">
-        <v>8.228</v>
+        <v>9.968</v>
       </c>
       <c r="CY55" t="str">
         <v>0.7256</v>
@@ -19497,7 +19486,7 @@
         <v>0</v>
       </c>
       <c r="DN55" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO55" t="str">
         <v>0</v>
@@ -19526,7 +19515,7 @@
         <v>40.5</v>
       </c>
       <c r="G56" t="str">
-        <v>0.004411</v>
+        <v>0.005548</v>
       </c>
       <c r="H56" t="str">
         <v>50.53</v>
@@ -19604,7 +19593,7 @@
         <v>83.87</v>
       </c>
       <c r="AG56" t="str">
-        <v>108.03</v>
+        <v>108.01</v>
       </c>
       <c r="AH56" t="str">
         <v>58.15</v>
@@ -19676,10 +19665,10 @@
         <v>2.31177E+13</v>
       </c>
       <c r="BE56" t="str">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="BF56" t="str">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="BG56" t="str">
         <v>259.04</v>
@@ -19712,7 +19701,7 @@
         <v>106.0004</v>
       </c>
       <c r="BS56" t="str">
-        <v>27147.85</v>
+        <v>27169.88</v>
       </c>
       <c r="BT56" t="str">
         <v>138081.0861</v>
@@ -19802,10 +19791,10 @@
         <v>0</v>
       </c>
       <c r="CW56" t="str">
-        <v>-0.2386</v>
+        <v>-0.2333</v>
       </c>
       <c r="CX56" t="str">
-        <v>8.316</v>
+        <v>10.306</v>
       </c>
       <c r="CY56" t="str">
         <v>0.7399</v>
@@ -19882,7 +19871,7 @@
         <v>40.5</v>
       </c>
       <c r="G57" t="str">
-        <v>0.004608</v>
+        <v>0.005548</v>
       </c>
       <c r="H57" t="str">
         <v>50.17</v>
@@ -19960,7 +19949,7 @@
         <v>83.63</v>
       </c>
       <c r="AG57" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH57" t="str">
         <v>60.46</v>
@@ -20032,10 +20021,10 @@
         <v>2.25786E+13</v>
       </c>
       <c r="BE57" t="str">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="BF57" t="str">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="BG57" t="str">
         <v>255.02</v>
@@ -20068,7 +20057,7 @@
         <v>106.867</v>
       </c>
       <c r="BS57" t="str">
-        <v>27455.89</v>
+        <v>27575.75</v>
       </c>
       <c r="BT57" t="str">
         <v>139699.1921</v>
@@ -20158,10 +20147,10 @@
         <v>0</v>
       </c>
       <c r="CW57" t="str">
-        <v>-0.3638</v>
+        <v>-0.3608</v>
       </c>
       <c r="CX57" t="str">
-        <v>7.76</v>
+        <v>9.94</v>
       </c>
       <c r="CY57" t="str">
         <v>0.263</v>
@@ -20238,7 +20227,7 @@
         <v>40.5</v>
       </c>
       <c r="G58" t="str">
-        <v>0.004588</v>
+        <v>0.005548</v>
       </c>
       <c r="H58" t="str">
         <v>49.99</v>
@@ -20316,7 +20305,7 @@
         <v>83.63</v>
       </c>
       <c r="AG58" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH58" t="str">
         <v>62.62</v>
@@ -20388,10 +20377,10 @@
         <v>2.75031E+13</v>
       </c>
       <c r="BE58" t="str">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="BF58" t="str">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="BG58" t="str">
         <v>258.8</v>
@@ -20424,7 +20413,7 @@
         <v>108.2893</v>
       </c>
       <c r="BS58" t="str">
-        <v>27908.81</v>
+        <v>27900.7</v>
       </c>
       <c r="BT58" t="str">
         <v>141181.5514</v>
@@ -20514,10 +20503,10 @@
         <v>0</v>
       </c>
       <c r="CW58" t="str">
-        <v>-0.3977</v>
+        <v>-0.3954</v>
       </c>
       <c r="CX58" t="str">
-        <v>7.206</v>
+        <v>9.696</v>
       </c>
       <c r="CY58" t="str">
         <v>0.2683</v>
@@ -20594,7 +20583,7 @@
         <v>40.5</v>
       </c>
       <c r="G59" t="str">
-        <v>0.004427</v>
+        <v>0.005548</v>
       </c>
       <c r="H59" t="str">
         <v>50.19</v>
@@ -20672,7 +20661,7 @@
         <v>83.63</v>
       </c>
       <c r="AG59" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH59" t="str">
         <v>62.74</v>
@@ -20744,10 +20733,10 @@
         <v>3.25697E+13</v>
       </c>
       <c r="BE59" t="str">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="BF59" t="str">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="BG59" t="str">
         <v>266.6</v>
@@ -20780,7 +20769,7 @@
         <v>109.1336</v>
       </c>
       <c r="BS59" t="str">
-        <v>27993.96</v>
+        <v>28039.72</v>
       </c>
       <c r="BT59" t="str">
         <v>141670.3965</v>
@@ -20870,10 +20859,10 @@
         <v>0</v>
       </c>
       <c r="CW59" t="str">
-        <v>-0.0129</v>
+        <v>-0.0036</v>
       </c>
       <c r="CX59" t="str">
-        <v>7.596</v>
+        <v>10.066</v>
       </c>
       <c r="CY59" t="str">
         <v>0.2542</v>
@@ -20950,7 +20939,7 @@
         <v>40.3</v>
       </c>
       <c r="G60" t="str">
-        <v>0.004411</v>
+        <v>0.005521</v>
       </c>
       <c r="H60" t="str">
         <v>49.81</v>
@@ -21028,7 +21017,7 @@
         <v>83.63</v>
       </c>
       <c r="AG60" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH60" t="str">
         <v>61.95</v>
@@ -21100,10 +21089,10 @@
         <v>2.48634E+13</v>
       </c>
       <c r="BE60" t="str">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="BF60" t="str">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BG60" t="str">
         <v>265.48</v>
@@ -21136,7 +21125,7 @@
         <v>109.8328</v>
       </c>
       <c r="BS60" t="str">
-        <v>28075.72</v>
+        <v>28115.3</v>
       </c>
       <c r="BT60" t="str">
         <v>142320.0976</v>
@@ -21226,10 +21215,10 @@
         <v>0</v>
       </c>
       <c r="CW60" t="str">
-        <v>-0.1103</v>
+        <v>-0.1028</v>
       </c>
       <c r="CX60" t="str">
-        <v>7.13</v>
+        <v>9.79</v>
       </c>
       <c r="CY60" t="str">
         <v>0.2455</v>
@@ -21306,7 +21295,7 @@
         <v>39.5</v>
       </c>
       <c r="G61" t="str">
-        <v>0.004270</v>
+        <v>0.005411</v>
       </c>
       <c r="H61" t="str">
         <v>49.1</v>
@@ -21384,7 +21373,7 @@
         <v>83.63</v>
       </c>
       <c r="AG61" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH61" t="str">
         <v>61.52</v>
@@ -21456,10 +21445,10 @@
         <v>2.21093E+13</v>
       </c>
       <c r="BE61" t="str">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BF61" t="str">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BG61" t="str">
         <v>246.45</v>
@@ -21492,7 +21481,7 @@
         <v>109.2582</v>
       </c>
       <c r="BS61" t="str">
-        <v>28067.24</v>
+        <v>28141.53</v>
       </c>
       <c r="BT61" t="str">
         <v>142864.9153</v>
@@ -21582,10 +21571,10 @@
         <v>0</v>
       </c>
       <c r="CW61" t="str">
-        <v>-0.1568</v>
+        <v>-0.1501</v>
       </c>
       <c r="CX61" t="str">
-        <v>7.695</v>
+        <v>9.875</v>
       </c>
       <c r="CY61" t="str">
         <v>0.1793</v>
@@ -21662,7 +21651,7 @@
         <v>39.5</v>
       </c>
       <c r="G62" t="str">
-        <v>0.004538</v>
+        <v>0.005411</v>
       </c>
       <c r="H62" t="str">
         <v>48.55</v>
@@ -21740,7 +21729,7 @@
         <v>83.63</v>
       </c>
       <c r="AG62" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH62" t="str">
         <v>62.66</v>
@@ -21812,7 +21801,7 @@
         <v>2.76626E+13</v>
       </c>
       <c r="BE62" t="str">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BF62" t="str">
         <v>50</v>
@@ -21848,7 +21837,7 @@
         <v>108.5421</v>
       </c>
       <c r="BS62" t="str">
-        <v>28624.63</v>
+        <v>28549.16</v>
       </c>
       <c r="BT62" t="str">
         <v>143265.355</v>
@@ -21938,10 +21927,10 @@
         <v>0</v>
       </c>
       <c r="CW62" t="str">
-        <v>-0.1881</v>
+        <v>-0.1819</v>
       </c>
       <c r="CX62" t="str">
-        <v>7.25</v>
+        <v>9.29</v>
       </c>
       <c r="CY62" t="str">
         <v>2.1356</v>
@@ -22018,7 +22007,7 @@
         <v>39.5</v>
       </c>
       <c r="G63" t="str">
-        <v>0.004063</v>
+        <v>0.005411</v>
       </c>
       <c r="H63" t="str">
         <v>48.62</v>
@@ -22096,7 +22085,7 @@
         <v>83.63</v>
       </c>
       <c r="AG63" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH63" t="str">
         <v>61.03</v>
@@ -22168,7 +22157,7 @@
         <v>2.31516E+13</v>
       </c>
       <c r="BE63" t="str">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BF63" t="str">
         <v>42</v>
@@ -22204,7 +22193,7 @@
         <v>108.8062</v>
       </c>
       <c r="BS63" t="str">
-        <v>28243.63</v>
+        <v>28214.37</v>
       </c>
       <c r="BT63" t="str">
         <v>143115.2228</v>
@@ -22294,10 +22283,10 @@
         <v>0</v>
       </c>
       <c r="CW63" t="str">
-        <v>-0.3193</v>
+        <v>-0.3156</v>
       </c>
       <c r="CX63" t="str">
-        <v>7.068</v>
+        <v>9.338</v>
       </c>
       <c r="CY63" t="str">
         <v>2.1374</v>
@@ -22374,7 +22363,7 @@
         <v>39.5</v>
       </c>
       <c r="G64" t="str">
-        <v>0.004063</v>
+        <v>0.005411</v>
       </c>
       <c r="H64" t="str">
         <v>48.7</v>
@@ -22452,7 +22441,7 @@
         <v>83.63</v>
       </c>
       <c r="AG64" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH64" t="str">
         <v>62.92</v>
@@ -22524,10 +22513,10 @@
         <v>2.67926E+13</v>
       </c>
       <c r="BE64" t="str">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BF64" t="str">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="BG64" t="str">
         <v>243.79</v>
@@ -22560,7 +22549,7 @@
         <v>108.9887</v>
       </c>
       <c r="BS64" t="str">
-        <v>27931.04</v>
+        <v>27963.78</v>
       </c>
       <c r="BT64" t="str">
         <v>143066.7045</v>
@@ -22650,10 +22639,10 @@
         <v>0</v>
       </c>
       <c r="CW64" t="str">
-        <v>-0.0688</v>
+        <v>-0.0606</v>
       </c>
       <c r="CX64" t="str">
-        <v>7.238</v>
+        <v>9.378</v>
       </c>
       <c r="CY64" t="str">
         <v>2.1407</v>
@@ -22730,7 +22719,7 @@
         <v>39.5</v>
       </c>
       <c r="G65" t="str">
-        <v>0.004824</v>
+        <v>0.005411</v>
       </c>
       <c r="H65" t="str">
         <v>48.64</v>
@@ -22808,7 +22797,7 @@
         <v>83.63</v>
       </c>
       <c r="AG65" t="str">
-        <v>107.02</v>
+        <v>107.05</v>
       </c>
       <c r="AH65" t="str">
         <v>62.63</v>
@@ -22880,10 +22869,10 @@
         <v>1.79595E+13</v>
       </c>
       <c r="BE65" t="str">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="BF65" t="str">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="BG65" t="str">
         <v>239.99</v>
@@ -22916,7 +22905,7 @@
         <v>108.8635</v>
       </c>
       <c r="BS65" t="str">
-        <v>28234.81</v>
+        <v>28395.87</v>
       </c>
       <c r="BT65" t="str">
         <v>143235.0147</v>
@@ -23006,10 +22995,10 @@
         <v>0</v>
       </c>
       <c r="CW65" t="str">
-        <v>-0.5017</v>
+        <v>-0.5012</v>
       </c>
       <c r="CX65" t="str">
-        <v>7.188</v>
+        <v>9.288</v>
       </c>
       <c r="CY65" t="str">
         <v>2.1432</v>
@@ -23086,7 +23075,7 @@
         <v>39.5</v>
       </c>
       <c r="G66" t="str">
-        <v>0.004299</v>
+        <v>0.005411</v>
       </c>
       <c r="H66" t="str">
         <v>48.52</v>
@@ -23164,7 +23153,7 @@
         <v>83.49</v>
       </c>
       <c r="AG66" t="str">
-        <v>111.04</v>
+        <v>111.11</v>
       </c>
       <c r="AH66" t="str">
         <v>64.57</v>
@@ -23236,7 +23225,7 @@
         <v>1.94445E+13</v>
       </c>
       <c r="BE66" t="str">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="BF66" t="str">
         <v>44</v>
@@ -23272,7 +23261,7 @@
         <v>110.2104</v>
       </c>
       <c r="BS66" t="str">
-        <v>28879.67</v>
+        <v>28853.9</v>
       </c>
       <c r="BT66" t="str">
         <v>158398.14</v>
@@ -23362,10 +23351,10 @@
         <v>0</v>
       </c>
       <c r="CW66" t="str">
-        <v>-0.4665</v>
+        <v>-0.4653</v>
       </c>
       <c r="CX66" t="str">
-        <v>7.188</v>
+        <v>9.138</v>
       </c>
       <c r="CY66" t="str">
         <v>2.2532</v>
@@ -23442,7 +23431,7 @@
         <v>39.2</v>
       </c>
       <c r="G67" t="str">
-        <v>0.004410</v>
+        <v>0.005370</v>
       </c>
       <c r="H67" t="str">
         <v>48.03</v>
@@ -23520,7 +23509,7 @@
         <v>83.49</v>
       </c>
       <c r="AG67" t="str">
-        <v>111.04</v>
+        <v>111.11</v>
       </c>
       <c r="AH67" t="str">
         <v>57.89</v>
@@ -23592,10 +23581,10 @@
         <v>1.75884E+13</v>
       </c>
       <c r="BE67" t="str">
+        <v>47</v>
+      </c>
+      <c r="BF67" t="str">
         <v>50</v>
-      </c>
-      <c r="BF67" t="str">
-        <v>52</v>
       </c>
       <c r="BG67" t="str">
         <v>224.45</v>
@@ -23628,7 +23617,7 @@
         <v>110.4871</v>
       </c>
       <c r="BS67" t="str">
-        <v>28941.63</v>
+        <v>28982.04</v>
       </c>
       <c r="BT67" t="str">
         <v>158963.5188</v>
@@ -23718,10 +23707,10 @@
         <v>0</v>
       </c>
       <c r="CW67" t="str">
-        <v>-0.6031</v>
+        <v>-0.6045</v>
       </c>
       <c r="CX67" t="str">
-        <v>6.524</v>
+        <v>9.014</v>
       </c>
       <c r="CY67" t="str">
         <v>2.2227</v>
@@ -23798,7 +23787,7 @@
         <v>38</v>
       </c>
       <c r="G68" t="str">
-        <v>0.004162</v>
+        <v>0.005205</v>
       </c>
       <c r="H68" t="str">
         <v>47.79</v>
@@ -23876,7 +23865,7 @@
         <v>83.49</v>
       </c>
       <c r="AG68" t="str">
-        <v>111.04</v>
+        <v>111.11</v>
       </c>
       <c r="AH68" t="str">
         <v>56.83</v>
@@ -23948,7 +23937,7 @@
         <v>1.63906E+13</v>
       </c>
       <c r="BE68" t="str">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="BF68" t="str">
         <v>45</v>
@@ -23984,7 +23973,7 @@
         <v>110.8294</v>
       </c>
       <c r="BS68" t="str">
-        <v>28935.04</v>
+        <v>29019.67</v>
       </c>
       <c r="BT68" t="str">
         <v>159366.0455</v>
@@ -24071,13 +24060,13 @@
         <v>0</v>
       </c>
       <c r="CV68" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW68" t="str">
-        <v>-0.6699</v>
+        <v>-0.6725</v>
       </c>
       <c r="CX68" t="str">
-        <v>7.546</v>
+        <v>10.056</v>
       </c>
       <c r="CY68" t="str">
         <v>2.1159</v>
@@ -24154,7 +24143,7 @@
         <v>38</v>
       </c>
       <c r="G69" t="str">
-        <v>0.004271</v>
+        <v>0.005205</v>
       </c>
       <c r="H69" t="str">
         <v>47.71</v>
@@ -24232,7 +24221,7 @@
         <v>83.49</v>
       </c>
       <c r="AG69" t="str">
-        <v>111.04</v>
+        <v>111.11</v>
       </c>
       <c r="AH69" t="str">
         <v>46.37</v>
@@ -24304,7 +24293,7 @@
         <v>1.17882E+13</v>
       </c>
       <c r="BE69" t="str">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BF69" t="str">
         <v>44</v>
@@ -24340,7 +24329,7 @@
         <v>111.5639</v>
       </c>
       <c r="BS69" t="str">
-        <v>29333.41</v>
+        <v>29481.89</v>
       </c>
       <c r="BT69" t="str">
         <v>160841.3533</v>
@@ -24430,10 +24419,10 @@
         <v>0</v>
       </c>
       <c r="CW69" t="str">
-        <v>-1.1416</v>
+        <v>-1.1528</v>
       </c>
       <c r="CX69" t="str">
-        <v>7.444</v>
+        <v>9.914</v>
       </c>
       <c r="CY69" t="str">
         <v>2.1211</v>
@@ -24492,7 +24481,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B70" t="str">
         <v>Hafta 1</v>
@@ -24510,7 +24499,7 @@
         <v>38</v>
       </c>
       <c r="G70" t="str">
-        <v>0.004221</v>
+        <v>0.005205</v>
       </c>
       <c r="H70" t="str">
         <v>47.53</v>
@@ -24588,7 +24577,7 @@
         <v>83.72</v>
       </c>
       <c r="AG70" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH70" t="str">
         <v>54.48</v>
@@ -24660,7 +24649,7 @@
         <v>1.21701E+13</v>
       </c>
       <c r="BE70" t="str">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="BF70" t="str">
         <v>39</v>
@@ -24672,7 +24661,7 @@
         <v>5.0947</v>
       </c>
       <c r="BI70" t="str">
-        <v>33.0578</v>
+        <v>33.0548</v>
       </c>
       <c r="BJ70" t="str">
         <v>4.8403</v>
@@ -24702,7 +24691,7 @@
         <v>112.7263</v>
       </c>
       <c r="BS70" t="str">
-        <v>29780.31</v>
+        <v>29914.44</v>
       </c>
       <c r="BT70" t="str">
         <v>144226.18</v>
@@ -24792,10 +24781,10 @@
         <v>0</v>
       </c>
       <c r="CW70" t="str">
-        <v>-0.8369</v>
+        <v>-0.8425</v>
       </c>
       <c r="CX70" t="str">
-        <v>7.325</v>
+        <v>9.675</v>
       </c>
       <c r="CY70" t="str">
         <v>-1.9401</v>
@@ -24872,7 +24861,7 @@
         <v>38</v>
       </c>
       <c r="G71" t="str">
-        <v>0.004387</v>
+        <v>0.005205</v>
       </c>
       <c r="H71" t="str">
         <v>47.34</v>
@@ -24950,7 +24939,7 @@
         <v>83.72</v>
       </c>
       <c r="AG71" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH71" t="str">
         <v>63.53</v>
@@ -25022,7 +25011,7 @@
         <v>1.7592E+13</v>
       </c>
       <c r="BE71" t="str">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BF71" t="str">
         <v>45</v>
@@ -25034,7 +25023,7 @@
         <v>5.0947</v>
       </c>
       <c r="BI71" t="str">
-        <v>33.0578</v>
+        <v>33.0548</v>
       </c>
       <c r="BJ71" t="str">
         <v>4.8403</v>
@@ -25064,7 +25053,7 @@
         <v>115.4872</v>
       </c>
       <c r="BS71" t="str">
-        <v>30371.83</v>
+        <v>30454.15</v>
       </c>
       <c r="BT71" t="str">
         <v>146003.189</v>
@@ -25154,10 +25143,10 @@
         <v>0</v>
       </c>
       <c r="CW71" t="str">
-        <v>-0.6281</v>
+        <v>-0.6299</v>
       </c>
       <c r="CX71" t="str">
-        <v>6.85</v>
+        <v>9.49</v>
       </c>
       <c r="CY71" t="str">
         <v>-1.9405</v>
@@ -25234,7 +25223,7 @@
         <v>38</v>
       </c>
       <c r="G72" t="str">
-        <v>0.004107</v>
+        <v>0.005205</v>
       </c>
       <c r="H72" t="str">
         <v>47.21</v>
@@ -25312,7 +25301,7 @@
         <v>83.72</v>
       </c>
       <c r="AG72" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH72" t="str">
         <v>64.04</v>
@@ -25384,10 +25373,10 @@
         <v>1.89267E+13</v>
       </c>
       <c r="BE72" t="str">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="BF72" t="str">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG72" t="str">
         <v>217.51</v>
@@ -25396,7 +25385,7 @@
         <v>5.0947</v>
       </c>
       <c r="BI72" t="str">
-        <v>33.0578</v>
+        <v>33.0548</v>
       </c>
       <c r="BJ72" t="str">
         <v>4.8403</v>
@@ -25426,7 +25415,7 @@
         <v>115.7899</v>
       </c>
       <c r="BS72" t="str">
-        <v>30784.84</v>
+        <v>30878</v>
       </c>
       <c r="BT72" t="str">
         <v>147806.9513</v>
@@ -25516,10 +25505,10 @@
         <v>0</v>
       </c>
       <c r="CW72" t="str">
-        <v>-0.7086</v>
+        <v>-0.7118</v>
       </c>
       <c r="CX72" t="str">
-        <v>6.802</v>
+        <v>9.522</v>
       </c>
       <c r="CY72" t="str">
         <v>-1.954</v>
@@ -25596,7 +25585,7 @@
         <v>37.86</v>
       </c>
       <c r="G73" t="str">
-        <v>0.004308</v>
+        <v>0.005186</v>
       </c>
       <c r="H73" t="str">
         <v>46.02</v>
@@ -25674,7 +25663,7 @@
         <v>83.72</v>
       </c>
       <c r="AG73" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH73" t="str">
         <v>56.37</v>
@@ -25746,10 +25735,10 @@
         <v>1.74395E+13</v>
       </c>
       <c r="BE73" t="str">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="BF73" t="str">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="BG73" t="str">
         <v>215.11</v>
@@ -25758,7 +25747,7 @@
         <v>5.0947</v>
       </c>
       <c r="BI73" t="str">
-        <v>33.0578</v>
+        <v>33.0548</v>
       </c>
       <c r="BJ73" t="str">
         <v>4.8403</v>
@@ -25788,7 +25777,7 @@
         <v>116.6523</v>
       </c>
       <c r="BS73" t="str">
-        <v>30909.71</v>
+        <v>30983.43</v>
       </c>
       <c r="BT73" t="str">
         <v>149195.5922</v>
@@ -25878,10 +25867,10 @@
         <v>0</v>
       </c>
       <c r="CW73" t="str">
-        <v>-0.59</v>
+        <v>-0.5911</v>
       </c>
       <c r="CX73" t="str">
-        <v>6.244</v>
+        <v>8.564</v>
       </c>
       <c r="CY73" t="str">
         <v>-1.9734</v>
@@ -25958,7 +25947,7 @@
         <v>37</v>
       </c>
       <c r="G74" t="str">
-        <v>0.004992</v>
+        <v>0.005068</v>
       </c>
       <c r="H74" t="str">
         <v>45.69</v>
@@ -26036,7 +26025,7 @@
         <v>83.72</v>
       </c>
       <c r="AG74" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH74" t="str">
         <v>60.34</v>
@@ -26108,7 +26097,7 @@
         <v>1.85511E+13</v>
       </c>
       <c r="BE74" t="str">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="BF74" t="str">
         <v>39</v>
@@ -26120,7 +26109,7 @@
         <v>5.0947</v>
       </c>
       <c r="BI74" t="str">
-        <v>33.0578</v>
+        <v>33.0548</v>
       </c>
       <c r="BJ74" t="str">
         <v>4.8403</v>
@@ -26150,7 +26139,7 @@
         <v>117.8978</v>
       </c>
       <c r="BS74" t="str">
-        <v>31619.01</v>
+        <v>31786.06</v>
       </c>
       <c r="BT74" t="str">
         <v>151104.8466</v>
@@ -26240,10 +26229,10 @@
         <v>0</v>
       </c>
       <c r="CW74" t="str">
-        <v>-0.4829</v>
+        <v>-0.4821</v>
       </c>
       <c r="CX74" t="str">
-        <v>6.728</v>
+        <v>8.958</v>
       </c>
       <c r="CY74" t="str">
         <v>-2.0337</v>
@@ -26320,7 +26309,7 @@
         <v>37</v>
       </c>
       <c r="G75" t="str">
-        <v>0.003930</v>
+        <v>0.005068</v>
       </c>
       <c r="H75" t="str">
         <v>45.71</v>
@@ -26398,7 +26387,7 @@
         <v>83.72</v>
       </c>
       <c r="AG75" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH75" t="str">
         <v>60.38</v>
@@ -26470,10 +26459,10 @@
         <v>3.13674E+13</v>
       </c>
       <c r="BE75" t="str">
+        <v>32</v>
+      </c>
+      <c r="BF75" t="str">
         <v>35</v>
-      </c>
-      <c r="BF75" t="str">
-        <v>36</v>
       </c>
       <c r="BG75" t="str">
         <v>217.31</v>
@@ -26482,7 +26471,7 @@
         <v>3.1881</v>
       </c>
       <c r="BI75" t="str">
-        <v>32.9293</v>
+        <v>32.9352</v>
       </c>
       <c r="BJ75" t="str">
         <v>2.9638</v>
@@ -26512,7 +26501,7 @@
         <v>117.9656</v>
       </c>
       <c r="BS75" t="str">
-        <v>32234.82</v>
+        <v>32284.17</v>
       </c>
       <c r="BT75" t="str">
         <v>151243.9389</v>
@@ -26602,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="CW75" t="str">
-        <v>0.0591</v>
+        <v>0.0697</v>
       </c>
       <c r="CX75" t="str">
-        <v>6.786</v>
+        <v>8.776</v>
       </c>
       <c r="CY75" t="str">
         <v>-0.1103</v>
@@ -26682,7 +26671,7 @@
         <v>37</v>
       </c>
       <c r="G76" t="str">
-        <v>0.003936</v>
+        <v>0.005068</v>
       </c>
       <c r="H76" t="str">
         <v>45.55</v>
@@ -26760,7 +26749,7 @@
         <v>83.72</v>
       </c>
       <c r="AG76" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH76" t="str">
         <v>59.67</v>
@@ -26832,10 +26821,10 @@
         <v>1.70402E+13</v>
       </c>
       <c r="BE76" t="str">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="BF76" t="str">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="BG76" t="str">
         <v>214.1</v>
@@ -26844,7 +26833,7 @@
         <v>3.1881</v>
       </c>
       <c r="BI76" t="str">
-        <v>32.9293</v>
+        <v>32.9352</v>
       </c>
       <c r="BJ76" t="str">
         <v>2.9638</v>
@@ -26874,7 +26863,7 @@
         <v>119.9488</v>
       </c>
       <c r="BS76" t="str">
-        <v>32364.19</v>
+        <v>32421.62</v>
       </c>
       <c r="BT76" t="str">
         <v>151754.7894</v>
@@ -26964,10 +26953,10 @@
         <v>0</v>
       </c>
       <c r="CW76" t="str">
-        <v>0.3551</v>
+        <v>0.3713</v>
       </c>
       <c r="CX76" t="str">
-        <v>6.59</v>
+        <v>8.71</v>
       </c>
       <c r="CY76" t="str">
         <v>-0.1181</v>
@@ -27044,7 +27033,7 @@
         <v>37</v>
       </c>
       <c r="G77" t="str">
-        <v>0.004173</v>
+        <v>0.005068</v>
       </c>
       <c r="H77" t="str">
         <v>45.45</v>
@@ -27122,7 +27111,7 @@
         <v>83.72</v>
       </c>
       <c r="AG77" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH77" t="str">
         <v>59.51</v>
@@ -27194,10 +27183,10 @@
         <v>1.45142E+13</v>
       </c>
       <c r="BE77" t="str">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="BF77" t="str">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BG77" t="str">
         <v>218.54</v>
@@ -27206,7 +27195,7 @@
         <v>3.1881</v>
       </c>
       <c r="BI77" t="str">
-        <v>32.9293</v>
+        <v>32.9352</v>
       </c>
       <c r="BJ77" t="str">
         <v>2.9638</v>
@@ -27236,7 +27225,7 @@
         <v>120.2601</v>
       </c>
       <c r="BS77" t="str">
-        <v>32387.1</v>
+        <v>32366.45</v>
       </c>
       <c r="BT77" t="str">
         <v>152552.9536</v>
@@ -27293,7 +27282,7 @@
         <v>0</v>
       </c>
       <c r="CL77" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM77" t="str">
         <v>0</v>
@@ -27326,10 +27315,10 @@
         <v>0</v>
       </c>
       <c r="CW77" t="str">
-        <v>0.0918</v>
+        <v>0.1031</v>
       </c>
       <c r="CX77" t="str">
-        <v>6.554</v>
+        <v>8.714</v>
       </c>
       <c r="CY77" t="str">
         <v>-0.1268</v>
@@ -27406,7 +27395,7 @@
         <v>37</v>
       </c>
       <c r="G78" t="str">
-        <v>0.004184</v>
+        <v>0.005068</v>
       </c>
       <c r="H78" t="str">
         <v>45.17</v>
@@ -27421,10 +27410,10 @@
         <v>45.31</v>
       </c>
       <c r="L78" t="str">
-        <v>40.703</v>
+        <v>40.711</v>
       </c>
       <c r="M78" t="str">
-        <v>36.6367</v>
+        <v>36.6439</v>
       </c>
       <c r="N78" t="str">
         <v>13903.75</v>
@@ -27484,7 +27473,7 @@
         <v>83.72</v>
       </c>
       <c r="AG78" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH78" t="str">
         <v>56.79</v>
@@ -27556,10 +27545,10 @@
         <v>1.60113E+13</v>
       </c>
       <c r="BE78" t="str">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="BF78" t="str">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BG78" t="str">
         <v>226.37</v>
@@ -27568,7 +27557,7 @@
         <v>3.1881</v>
       </c>
       <c r="BI78" t="str">
-        <v>32.9293</v>
+        <v>32.9352</v>
       </c>
       <c r="BJ78" t="str">
         <v>2.9638</v>
@@ -27598,7 +27587,7 @@
         <v>120.7743</v>
       </c>
       <c r="BS78" t="str">
-        <v>32403.27</v>
+        <v>32407.4</v>
       </c>
       <c r="BT78" t="str">
         <v>153060.2538</v>
@@ -27655,7 +27644,7 @@
         <v>0</v>
       </c>
       <c r="CL78" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM78" t="str">
         <v>0</v>
@@ -27688,10 +27677,10 @@
         <v>0</v>
       </c>
       <c r="CW78" t="str">
-        <v>0.0027</v>
+        <v>0.0123</v>
       </c>
       <c r="CX78" t="str">
-        <v>6.142</v>
+        <v>8.342</v>
       </c>
       <c r="CY78" t="str">
         <v>-0.1191</v>
@@ -27768,7 +27757,7 @@
         <v>39.26</v>
       </c>
       <c r="G79" t="str">
-        <v>0.003400</v>
+        <v>0.005378</v>
       </c>
       <c r="H79" t="str">
         <v>45.31</v>
@@ -27783,10 +27772,10 @@
         <v>44.82</v>
       </c>
       <c r="L79" t="str">
-        <v>43.823</v>
+        <v>43.831</v>
       </c>
       <c r="M79" t="str">
-        <v>39.445</v>
+        <v>39.4522</v>
       </c>
       <c r="N79" t="str">
         <v>13018.95</v>
@@ -27846,7 +27835,7 @@
         <v>83.72</v>
       </c>
       <c r="AG79" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH79" t="str">
         <v>58.96</v>
@@ -27918,10 +27907,10 @@
         <v>2.04437E+13</v>
       </c>
       <c r="BE79" t="str">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF79" t="str">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BG79" t="str">
         <v>242.36</v>
@@ -27930,7 +27919,7 @@
         <v>2.4795</v>
       </c>
       <c r="BI79" t="str">
-        <v>31.6826</v>
+        <v>31.678</v>
       </c>
       <c r="BJ79" t="str">
         <v>1.9386</v>
@@ -27960,7 +27949,7 @@
         <v>121.4915</v>
       </c>
       <c r="BS79" t="str">
-        <v>32651.17</v>
+        <v>32682.58</v>
       </c>
       <c r="BT79" t="str">
         <v>154024.7709</v>
@@ -28017,7 +28006,7 @@
         <v>0</v>
       </c>
       <c r="CL79" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM79" t="str">
         <v>0</v>
@@ -28050,10 +28039,10 @@
         <v>0</v>
       </c>
       <c r="CW79" t="str">
-        <v>0.4038</v>
+        <v>0.4207</v>
       </c>
       <c r="CX79" t="str">
-        <v>4.332</v>
+        <v>5.362</v>
       </c>
       <c r="CY79" t="str">
         <v>0.8495</v>
@@ -28130,7 +28119,7 @@
         <v>40</v>
       </c>
       <c r="G80" t="str">
-        <v>0.003738</v>
+        <v>0.005479</v>
       </c>
       <c r="H80" t="str">
         <v>45.38</v>
@@ -28208,7 +28197,7 @@
         <v>83.72</v>
       </c>
       <c r="AG80" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH80" t="str">
         <v>58.66</v>
@@ -28280,10 +28269,10 @@
         <v>1.61545E+13</v>
       </c>
       <c r="BE80" t="str">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BF80" t="str">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BG80" t="str">
         <v>259.28</v>
@@ -28292,7 +28281,7 @@
         <v>2.4795</v>
       </c>
       <c r="BI80" t="str">
-        <v>31.6826</v>
+        <v>31.678</v>
       </c>
       <c r="BJ80" t="str">
         <v>1.9386</v>
@@ -28322,7 +28311,7 @@
         <v>121.4043</v>
       </c>
       <c r="BS80" t="str">
-        <v>33072.81</v>
+        <v>33208.37</v>
       </c>
       <c r="BT80" t="str">
         <v>155676.2544</v>
@@ -28379,7 +28368,7 @@
         <v>0</v>
       </c>
       <c r="CL80" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM80" t="str">
         <v>0</v>
@@ -28412,10 +28401,10 @@
         <v>0</v>
       </c>
       <c r="CW80" t="str">
-        <v>0.8178</v>
+        <v>0.8422</v>
       </c>
       <c r="CX80" t="str">
-        <v>4.33</v>
+        <v>5.39</v>
       </c>
       <c r="CY80" t="str">
         <v>0.853</v>
@@ -28492,7 +28481,7 @@
         <v>40</v>
       </c>
       <c r="G81" t="str">
-        <v>0.003604</v>
+        <v>0.005479</v>
       </c>
       <c r="H81" t="str">
         <v>45.35</v>
@@ -28570,7 +28559,7 @@
         <v>83.72</v>
       </c>
       <c r="AG81" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH81" t="str">
         <v>57.91</v>
@@ -28642,10 +28631,10 @@
         <v>1.74207E+13</v>
       </c>
       <c r="BE81" t="str">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BF81" t="str">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BG81" t="str">
         <v>283.35</v>
@@ -28654,7 +28643,7 @@
         <v>2.4795</v>
       </c>
       <c r="BI81" t="str">
-        <v>31.6826</v>
+        <v>31.678</v>
       </c>
       <c r="BJ81" t="str">
         <v>1.9386</v>
@@ -28684,7 +28673,7 @@
         <v>121.4883</v>
       </c>
       <c r="BS81" t="str">
-        <v>33337.05</v>
+        <v>33435.69</v>
       </c>
       <c r="BT81" t="str">
         <v>156924.7887</v>
@@ -28741,7 +28730,7 @@
         <v>0</v>
       </c>
       <c r="CL81" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM81" t="str">
         <v>0</v>
@@ -28774,10 +28763,10 @@
         <v>0</v>
       </c>
       <c r="CW81" t="str">
-        <v>0.4338</v>
+        <v>0.4513</v>
       </c>
       <c r="CX81" t="str">
-        <v>4.65</v>
+        <v>5.36</v>
       </c>
       <c r="CY81" t="str">
         <v>0.853</v>
@@ -28825,7 +28814,7 @@
         <v>1</v>
       </c>
       <c r="DN81" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO81" t="str">
         <v>0</v>
@@ -28854,7 +28843,7 @@
         <v>40</v>
       </c>
       <c r="G82" t="str">
-        <v>0.003967</v>
+        <v>0.005479</v>
       </c>
       <c r="H82" t="str">
         <v>45.93</v>
@@ -28932,7 +28921,7 @@
         <v>83.72</v>
       </c>
       <c r="AG82" t="str">
-        <v>107.87</v>
+        <v>107.96</v>
       </c>
       <c r="AH82" t="str">
         <v>58.99</v>
@@ -29004,19 +28993,19 @@
         <v>1.56783E+13</v>
       </c>
       <c r="BE82" t="str">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="BF82" t="str">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BG82" t="str">
-        <v>293.25</v>
+        <v>283.35</v>
       </c>
       <c r="BH82" t="str">
         <v>2.4795</v>
       </c>
       <c r="BI82" t="str">
-        <v>31.6826</v>
+        <v>31.678</v>
       </c>
       <c r="BJ82" t="str">
         <v>1.9386</v>
@@ -29028,7 +29017,7 @@
         <v>134.9942</v>
       </c>
       <c r="BM82" t="str">
-        <v>129.2454</v>
+        <v>129.2519</v>
       </c>
       <c r="BN82" t="str">
         <v>124.7591</v>
@@ -29040,22 +29029,22 @@
         <v>102.9421</v>
       </c>
       <c r="BQ82" t="str">
-        <v>124.9387</v>
+        <v>124.9393</v>
       </c>
       <c r="BR82" t="str">
         <v>121.7167</v>
       </c>
       <c r="BS82" t="str">
-        <v>34343.46</v>
+        <v>34560.48</v>
       </c>
       <c r="BT82" t="str">
-        <v>158413.9767</v>
+        <v>158414.7375</v>
       </c>
       <c r="BU82" t="str">
-        <v>153744.117</v>
+        <v>153744.8553</v>
       </c>
       <c r="BV82" t="str">
-        <v>101227.5756</v>
+        <v>101228.0618</v>
       </c>
       <c r="BW82" t="str">
         <v>0</v>
@@ -29136,10 +29125,10 @@
         <v>0</v>
       </c>
       <c r="CW82" t="str">
-        <v>0.8028</v>
+        <v>0.8311</v>
       </c>
       <c r="CX82" t="str">
-        <v>5.142</v>
+        <v>5.932</v>
       </c>
       <c r="CY82" t="str">
         <v>0.8537</v>
@@ -29157,28 +29146,28 @@
         <v>0.265</v>
       </c>
       <c r="DD82" t="str">
-        <v>1538.8648</v>
+        <v>1538.8722</v>
       </c>
       <c r="DE82" t="str">
         <v>0.639</v>
       </c>
       <c r="DF82" t="str">
-        <v>1252.6938</v>
+        <v>1252.6999</v>
       </c>
       <c r="DG82" t="str">
-        <v>831.6655</v>
+        <v>831.6695</v>
       </c>
       <c r="DH82" t="str">
-        <v>1.080483</v>
+        <v>1.080478</v>
       </c>
       <c r="DI82" t="str">
-        <v>1.034471</v>
+        <v>1.034518</v>
       </c>
       <c r="DJ82" t="str">
         <v>0.909156</v>
       </c>
       <c r="DK82" t="str">
-        <v>1.057477</v>
+        <v>1.057498</v>
       </c>
       <c r="DL82" t="str">
         <v>0</v>
@@ -29216,7 +29205,7 @@
         <v>40</v>
       </c>
       <c r="G83" t="str">
-        <v>0.004167</v>
+        <v>0.005479</v>
       </c>
       <c r="H83" t="str">
         <v>47.14</v>
@@ -29294,7 +29283,7 @@
         <v>85.5</v>
       </c>
       <c r="AG83" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH83" t="str">
         <v>60.66</v>
@@ -29351,7 +29340,7 @@
         <v>139.6</v>
       </c>
       <c r="AZ83" t="str">
-        <v>3.806</v>
+        <v>3.8025</v>
       </c>
       <c r="BA83" t="str">
         <v>23.39</v>
@@ -29360,37 +29349,37 @@
         <v>3.45</v>
       </c>
       <c r="BC83" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD83" t="str">
         <v>1.47732E+13</v>
       </c>
       <c r="BE83" t="str">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="BF83" t="str">
         <v>51</v>
       </c>
       <c r="BG83" t="str">
-        <v>292.67</v>
+        <v>283.35</v>
       </c>
       <c r="BH83" t="str">
-        <v>3.3303</v>
+        <v>3.3272</v>
       </c>
       <c r="BI83" t="str">
-        <v>32.9606</v>
+        <v>32.9572</v>
       </c>
       <c r="BJ83" t="str">
-        <v>0</v>
+        <v>4.1821</v>
       </c>
       <c r="BK83" t="str">
-        <v>27.058</v>
+        <v>32.3717</v>
       </c>
       <c r="BL83" t="str">
         <v>135.1768</v>
       </c>
       <c r="BM83" t="str">
-        <v>130.5405</v>
+        <v>130.5512</v>
       </c>
       <c r="BN83" t="str">
         <v>125.0536</v>
@@ -29402,22 +29391,22 @@
         <v>105.9836</v>
       </c>
       <c r="BQ83" t="str">
-        <v>125.9405</v>
+        <v>125.9416</v>
       </c>
       <c r="BR83" t="str">
         <v>122.3821</v>
       </c>
       <c r="BS83" t="str">
-        <v>34678.38</v>
+        <v>34764.77</v>
       </c>
       <c r="BT83" t="str">
-        <v>159684.1926</v>
+        <v>159685.5873</v>
       </c>
       <c r="BU83" t="str">
-        <v>154976.8884</v>
+        <v>154978.242</v>
       </c>
       <c r="BV83" t="str">
-        <v>102039.252</v>
+        <v>102040.1432</v>
       </c>
       <c r="BW83" t="str">
         <v>1</v>
@@ -29498,13 +29487,13 @@
         <v>0</v>
       </c>
       <c r="CW83" t="str">
-        <v>0.2851</v>
+        <v>0.2998</v>
       </c>
       <c r="CX83" t="str">
-        <v>6.292</v>
+        <v>7.142</v>
       </c>
       <c r="CY83" t="str">
-        <v>0.0029</v>
+        <v>0.006</v>
       </c>
       <c r="CZ83" t="str">
         <v>-0.2236</v>
@@ -29519,28 +29508,28 @@
         <v>0.434</v>
       </c>
       <c r="DD83" t="str">
-        <v>1506.6878</v>
+        <v>1506.7009</v>
       </c>
       <c r="DE83" t="str">
         <v>0.639</v>
       </c>
       <c r="DF83" t="str">
-        <v>1242.6035</v>
+        <v>1242.6144</v>
       </c>
       <c r="DG83" t="str">
-        <v>833.776</v>
+        <v>833.7832</v>
       </c>
       <c r="DH83" t="str">
-        <v>1.073339</v>
+        <v>1.073329</v>
       </c>
       <c r="DI83" t="str">
-        <v>1.036525</v>
+        <v>1.036601</v>
       </c>
       <c r="DJ83" t="str">
         <v>0.92264</v>
       </c>
       <c r="DK83" t="str">
-        <v>1.054932</v>
+        <v>1.054965</v>
       </c>
       <c r="DL83" t="str">
         <v>0</v>
@@ -29578,7 +29567,7 @@
         <v>40</v>
       </c>
       <c r="G84" t="str">
-        <v>0.005063</v>
+        <v>0.005479</v>
       </c>
       <c r="H84" t="str">
         <v>47.23</v>
@@ -29656,7 +29645,7 @@
         <v>85.5</v>
       </c>
       <c r="AG84" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH84" t="str">
         <v>63.29</v>
@@ -29713,7 +29702,7 @@
         <v>139.6</v>
       </c>
       <c r="AZ84" t="str">
-        <v>3.806</v>
+        <v>3.8025</v>
       </c>
       <c r="BA84" t="str">
         <v>23.39</v>
@@ -29722,37 +29711,37 @@
         <v>3.45</v>
       </c>
       <c r="BC84" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD84" t="str">
         <v>1.4786E+13</v>
       </c>
       <c r="BE84" t="str">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BF84" t="str">
         <v>42</v>
       </c>
       <c r="BG84" t="str">
-        <v>258.9</v>
+        <v>283.35</v>
       </c>
       <c r="BH84" t="str">
-        <v>3.3303</v>
+        <v>3.3272</v>
       </c>
       <c r="BI84" t="str">
-        <v>32.9606</v>
+        <v>32.9572</v>
       </c>
       <c r="BJ84" t="str">
-        <v>0</v>
+        <v>4.1821</v>
       </c>
       <c r="BK84" t="str">
-        <v>27.058</v>
+        <v>32.3717</v>
       </c>
       <c r="BL84" t="str">
         <v>135.8067</v>
       </c>
       <c r="BM84" t="str">
-        <v>135.3262</v>
+        <v>135.337</v>
       </c>
       <c r="BN84" t="str">
         <v>127.2493</v>
@@ -29764,22 +29753,22 @@
         <v>107.5511</v>
       </c>
       <c r="BQ84" t="str">
-        <v>127.2716</v>
+        <v>127.2727</v>
       </c>
       <c r="BR84" t="str">
         <v>122.2598</v>
       </c>
       <c r="BS84" t="str">
-        <v>35125.21</v>
+        <v>35219.7</v>
       </c>
       <c r="BT84" t="str">
-        <v>161371.939</v>
+        <v>161373.3337</v>
       </c>
       <c r="BU84" t="str">
-        <v>156614.882</v>
+        <v>156616.2356</v>
       </c>
       <c r="BV84" t="str">
-        <v>103117.7331</v>
+        <v>103118.6243</v>
       </c>
       <c r="BW84" t="str">
         <v>0</v>
@@ -29860,13 +29849,13 @@
         <v>0</v>
       </c>
       <c r="CW84" t="str">
-        <v>0.4642</v>
+        <v>0.4822</v>
       </c>
       <c r="CX84" t="str">
-        <v>6.13</v>
+        <v>7.24</v>
       </c>
       <c r="CY84" t="str">
-        <v>0.0022</v>
+        <v>0.0053</v>
       </c>
       <c r="CZ84" t="str">
         <v>4.6473</v>
@@ -29881,28 +29870,28 @@
         <v>0.9119</v>
       </c>
       <c r="DD84" t="str">
-        <v>1500.4211</v>
+        <v>1500.4341</v>
       </c>
       <c r="DE84" t="str">
         <v>0.639</v>
       </c>
       <c r="DF84" t="str">
-        <v>1246.9338</v>
+        <v>1246.9446</v>
       </c>
       <c r="DG84" t="str">
-        <v>843.4312</v>
+        <v>843.4385</v>
       </c>
       <c r="DH84" t="str">
-        <v>1.067062</v>
+        <v>1.067053</v>
       </c>
       <c r="DI84" t="str">
-        <v>1.063287</v>
+        <v>1.063362</v>
       </c>
       <c r="DJ84" t="str">
         <v>0.924844</v>
       </c>
       <c r="DK84" t="str">
-        <v>1.065174</v>
+        <v>1.065208</v>
       </c>
       <c r="DL84" t="str">
         <v>0</v>
@@ -29911,7 +29900,7 @@
         <v>0</v>
       </c>
       <c r="DN84" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO84" t="str">
         <v>0</v>
@@ -29940,7 +29929,7 @@
         <v>40</v>
       </c>
       <c r="G85" t="str">
-        <v>0.005059</v>
+        <v>0.005479</v>
       </c>
       <c r="H85" t="str">
         <v>47.43</v>
@@ -30018,7 +30007,7 @@
         <v>85.5</v>
       </c>
       <c r="AG85" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH85" t="str">
         <v>63.07</v>
@@ -30075,7 +30064,7 @@
         <v>139.6</v>
       </c>
       <c r="AZ85" t="str">
-        <v>3.806</v>
+        <v>3.8025</v>
       </c>
       <c r="BA85" t="str">
         <v>23.39</v>
@@ -30084,37 +30073,37 @@
         <v>3.45</v>
       </c>
       <c r="BC85" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD85" t="str">
         <v>1.64491E+13</v>
       </c>
       <c r="BE85" t="str">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BF85" t="str">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="BG85" t="str">
-        <v>233.91</v>
+        <v>283.35</v>
       </c>
       <c r="BH85" t="str">
-        <v>3.3303</v>
+        <v>3.3272</v>
       </c>
       <c r="BI85" t="str">
-        <v>32.9606</v>
+        <v>32.9572</v>
       </c>
       <c r="BJ85" t="str">
-        <v>0</v>
+        <v>4.1821</v>
       </c>
       <c r="BK85" t="str">
-        <v>27.058</v>
+        <v>32.3717</v>
       </c>
       <c r="BL85" t="str">
         <v>133.8256</v>
       </c>
       <c r="BM85" t="str">
-        <v>135.318</v>
+        <v>135.3288</v>
       </c>
       <c r="BN85" t="str">
         <v>126.6399</v>
@@ -30126,22 +30115,22 @@
         <v>108.0092</v>
       </c>
       <c r="BQ85" t="str">
-        <v>126.8495</v>
+        <v>126.8506</v>
       </c>
       <c r="BR85" t="str">
         <v>122.2043</v>
       </c>
       <c r="BS85" t="str">
-        <v>34943.2</v>
+        <v>34885.37</v>
       </c>
       <c r="BT85" t="str">
-        <v>160836.7442</v>
+        <v>160838.139</v>
       </c>
       <c r="BU85" t="str">
-        <v>156095.4641</v>
+        <v>156096.8177</v>
       </c>
       <c r="BV85" t="str">
-        <v>102775.7401</v>
+        <v>102776.6313</v>
       </c>
       <c r="BW85" t="str">
         <v>1</v>
@@ -30222,13 +30211,13 @@
         <v>0</v>
       </c>
       <c r="CW85" t="str">
-        <v>0.164</v>
+        <v>0.1767</v>
       </c>
       <c r="CX85" t="str">
-        <v>6.352</v>
+        <v>7.512</v>
       </c>
       <c r="CY85" t="str">
-        <v>-0.0038</v>
+        <v>-0.0007</v>
       </c>
       <c r="CZ85" t="str">
         <v>5.8939</v>
@@ -30243,28 +30232,28 @@
         <v>0.8317</v>
       </c>
       <c r="DD85" t="str">
-        <v>1489.1023</v>
+        <v>1489.1152</v>
       </c>
       <c r="DE85" t="str">
         <v>0.639</v>
       </c>
       <c r="DF85" t="str">
-        <v>1230.8446</v>
+        <v>1230.8553</v>
       </c>
       <c r="DG85" t="str">
-        <v>841.0157</v>
+        <v>841.023</v>
       </c>
       <c r="DH85" t="str">
-        <v>1.054995</v>
+        <v>1.054986</v>
       </c>
       <c r="DI85" t="str">
-        <v>1.06676</v>
+        <v>1.066836</v>
       </c>
       <c r="DJ85" t="str">
         <v>0.94765</v>
       </c>
       <c r="DK85" t="str">
-        <v>1.060878</v>
+        <v>1.060911</v>
       </c>
       <c r="DL85" t="str">
         <v>0</v>
@@ -30302,7 +30291,7 @@
         <v>40</v>
       </c>
       <c r="G86" t="str">
-        <v>0.004154</v>
+        <v>0.005479</v>
       </c>
       <c r="H86" t="str">
         <v>47.37</v>
@@ -30380,7 +30369,7 @@
         <v>85.5</v>
       </c>
       <c r="AG86" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH86" t="str">
         <v>62.24</v>
@@ -30437,7 +30426,7 @@
         <v>139.6</v>
       </c>
       <c r="AZ86" t="str">
-        <v>3.807</v>
+        <v>3.8025</v>
       </c>
       <c r="BA86" t="str">
         <v>23.39</v>
@@ -30446,31 +30435,31 @@
         <v>3.45</v>
       </c>
       <c r="BC86" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD86" t="str">
         <v>1.70537E+13</v>
       </c>
       <c r="BE86" t="str">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="BF86" t="str">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="BG86" t="str">
-        <v>232.93</v>
+        <v>283.35</v>
       </c>
       <c r="BH86" t="str">
-        <v>3.3312</v>
+        <v>3.3272</v>
       </c>
       <c r="BI86" t="str">
         <v>32.9572</v>
       </c>
       <c r="BJ86" t="str">
-        <v>0</v>
+        <v>4.1821</v>
       </c>
       <c r="BK86" t="str">
-        <v>27.058</v>
+        <v>32.3717</v>
       </c>
       <c r="BL86" t="str">
         <v>133.3276</v>
@@ -30494,7 +30483,7 @@
         <v>122.301</v>
       </c>
       <c r="BS86" t="str">
-        <v>34837.52</v>
+        <v>34847.16</v>
       </c>
       <c r="BT86" t="str">
         <v>160867.3014</v>
@@ -30584,13 +30573,13 @@
         <v>0</v>
       </c>
       <c r="CW86" t="str">
-        <v>-0.0373</v>
+        <v>-0.0284</v>
       </c>
       <c r="CX86" t="str">
-        <v>6.39</v>
+        <v>7.43</v>
       </c>
       <c r="CY86" t="str">
-        <v>-0.0029</v>
+        <v>0.0011</v>
       </c>
       <c r="CZ86" t="str">
         <v>0.9873</v>
@@ -30742,7 +30731,7 @@
         <v>85.76</v>
       </c>
       <c r="AG87" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH87" t="str">
         <v>61.69</v>
@@ -30799,7 +30788,7 @@
         <v>162.8</v>
       </c>
       <c r="AZ87" t="str">
-        <v>0.8644</v>
+        <v>1.769</v>
       </c>
       <c r="BA87" t="str">
         <v>23.82</v>
@@ -30808,40 +30797,40 @@
         <v>3.34</v>
       </c>
       <c r="BC87" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD87" t="str">
         <v>1.60419E+13</v>
       </c>
       <c r="BE87" t="str">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BF87" t="str">
         <v>36</v>
       </c>
       <c r="BG87" t="str">
-        <v>244.54</v>
+        <v>283.35</v>
       </c>
       <c r="BH87" t="str">
-        <v>0.7564</v>
+        <v>1.5479</v>
       </c>
       <c r="BI87" t="str">
-        <v>32.1275</v>
+        <v>33.1645</v>
       </c>
       <c r="BJ87" t="str">
-        <v>0</v>
+        <v>1.7147</v>
       </c>
       <c r="BK87" t="str">
-        <v>30.3791</v>
+        <v>32.6148</v>
       </c>
       <c r="BL87" t="str">
-        <v>132.7884</v>
+        <v>134.3916</v>
       </c>
       <c r="BM87" t="str">
-        <v>135.7848</v>
+        <v>136.0432</v>
       </c>
       <c r="BN87" t="str">
-        <v>128.0763</v>
+        <v>128.0006</v>
       </c>
       <c r="BO87" t="str">
         <v>128.8091</v>
@@ -30850,22 +30839,22 @@
         <v>109.8719</v>
       </c>
       <c r="BQ87" t="str">
-        <v>127.3601</v>
+        <v>127.7867</v>
       </c>
       <c r="BR87" t="str">
         <v>122.204</v>
       </c>
       <c r="BS87" t="str">
-        <v>34631.14</v>
+        <v>34963.47</v>
       </c>
       <c r="BT87" t="str">
-        <v>161484.1511</v>
+        <v>162025.0516</v>
       </c>
       <c r="BU87" t="str">
-        <v>156723.7862</v>
+        <v>157248.7416</v>
       </c>
       <c r="BV87" t="str">
-        <v>103189.4373</v>
+        <v>103535.0763</v>
       </c>
       <c r="BW87" t="str">
         <v>1</v>
@@ -30946,13 +30935,13 @@
         <v>0</v>
       </c>
       <c r="CW87" t="str">
-        <v>-0.4168</v>
+        <v>-0.4106</v>
       </c>
       <c r="CX87" t="str">
-        <v>6.6875</v>
+        <v>7.3775</v>
       </c>
       <c r="CY87" t="str">
-        <v>2.5755</v>
+        <v>1.784</v>
       </c>
       <c r="CZ87" t="str">
         <v>0.1254</v>
@@ -30967,28 +30956,28 @@
         <v>0.2415</v>
       </c>
       <c r="DD87" t="str">
-        <v>1469.7493</v>
+        <v>1474.6723</v>
       </c>
       <c r="DE87" t="str">
         <v>0.639</v>
       </c>
       <c r="DF87" t="str">
-        <v>1216.7136</v>
+        <v>1220.7891</v>
       </c>
       <c r="DG87" t="str">
-        <v>844.4031</v>
+        <v>847.2315</v>
       </c>
       <c r="DH87" t="str">
-        <v>1.042622</v>
+        <v>1.051687</v>
       </c>
       <c r="DI87" t="str">
-        <v>1.066149</v>
+        <v>1.064612</v>
       </c>
       <c r="DJ87" t="str">
-        <v>0.970033</v>
+        <v>0.958461</v>
       </c>
       <c r="DK87" t="str">
-        <v>1.054385</v>
+        <v>1.058149</v>
       </c>
       <c r="DL87" t="str">
         <v>0</v>
@@ -31026,7 +31015,7 @@
         <v>40</v>
       </c>
       <c r="G88" t="str">
-        <v>0.001096</v>
+        <v>0.005479</v>
       </c>
       <c r="H88" t="str">
         <v>47.45</v>
@@ -31104,7 +31093,7 @@
         <v>85.76</v>
       </c>
       <c r="AG88" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH88" t="str">
         <v>61.55</v>
@@ -31161,7 +31150,7 @@
         <v>162.8</v>
       </c>
       <c r="AZ88" t="str">
-        <v>1.4527</v>
+        <v>1.769</v>
       </c>
       <c r="BA88" t="str">
         <v>23.82</v>
@@ -31170,31 +31159,31 @@
         <v>3.34</v>
       </c>
       <c r="BC88" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD88" t="str">
         <v>1.54695E+13</v>
       </c>
       <c r="BE88" t="str">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BF88" t="str">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="BG88" t="str">
-        <v>235.1</v>
+        <v>283.35</v>
       </c>
       <c r="BH88" t="str">
-        <v>1.2711</v>
+        <v>1.5479</v>
       </c>
       <c r="BI88" t="str">
-        <v>32.8025</v>
+        <v>33.1645</v>
       </c>
       <c r="BJ88" t="str">
-        <v>0</v>
+        <v>1.7147</v>
       </c>
       <c r="BK88" t="str">
-        <v>30.3791</v>
+        <v>32.6148</v>
       </c>
       <c r="BL88" t="str">
         <v>134.1051</v>
@@ -31203,7 +31192,7 @@
         <v>137.161</v>
       </c>
       <c r="BN88" t="str">
-        <v>127.0934</v>
+        <v>126.9797</v>
       </c>
       <c r="BO88" t="str">
         <v>129.7697</v>
@@ -31212,22 +31201,22 @@
         <v>114.8175</v>
       </c>
       <c r="BQ88" t="str">
-        <v>128.3623</v>
+        <v>128.3433</v>
       </c>
       <c r="BR88" t="str">
         <v>122.263</v>
       </c>
       <c r="BS88" t="str">
-        <v>35007.62</v>
+        <v>34951</v>
       </c>
       <c r="BT88" t="str">
-        <v>162754.8742</v>
+        <v>162730.7835</v>
       </c>
       <c r="BU88" t="str">
-        <v>157957.0498</v>
+        <v>157933.6693</v>
       </c>
       <c r="BV88" t="str">
-        <v>104001.4378</v>
+        <v>103986.0436</v>
       </c>
       <c r="BW88" t="str">
         <v>0</v>
@@ -31308,13 +31297,13 @@
         <v>0</v>
       </c>
       <c r="CW88" t="str">
-        <v>-0.3719</v>
+        <v>-0.3648</v>
       </c>
       <c r="CX88" t="str">
-        <v>6.42</v>
+        <v>7.46</v>
       </c>
       <c r="CY88" t="str">
-        <v>2.0614</v>
+        <v>1.7846</v>
       </c>
       <c r="CZ88" t="str">
         <v>2.4818</v>
@@ -31329,28 +31318,28 @@
         <v>0.8046</v>
       </c>
       <c r="DD88" t="str">
-        <v>1417.5093</v>
+        <v>1417.2995</v>
       </c>
       <c r="DE88" t="str">
         <v>0.639</v>
       </c>
       <c r="DF88" t="str">
-        <v>1217.2106</v>
+        <v>1217.0304</v>
       </c>
       <c r="DG88" t="str">
-        <v>850.6371</v>
+        <v>850.5111</v>
       </c>
       <c r="DH88" t="str">
-        <v>1.044739</v>
+        <v>1.044894</v>
       </c>
       <c r="DI88" t="str">
-        <v>1.068546</v>
+        <v>1.068704</v>
       </c>
       <c r="DJ88" t="str">
         <v>0.967672</v>
       </c>
       <c r="DK88" t="str">
-        <v>1.056642</v>
+        <v>1.056799</v>
       </c>
       <c r="DL88" t="str">
         <v>0</v>
@@ -31466,7 +31455,7 @@
         <v>85.76</v>
       </c>
       <c r="AG89" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH89" t="str">
         <v>61.65</v>
@@ -31523,7 +31512,7 @@
         <v>162.8</v>
       </c>
       <c r="AZ89" t="str">
-        <v>1.6737</v>
+        <v>1.769</v>
       </c>
       <c r="BA89" t="str">
         <v>23.82</v>
@@ -31532,37 +31521,37 @@
         <v>3.34</v>
       </c>
       <c r="BC89" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD89" t="str">
         <v>1.4519E+13</v>
       </c>
       <c r="BE89" t="str">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF89" t="str">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG89" t="str">
-        <v>230.94</v>
+        <v>283.35</v>
       </c>
       <c r="BH89" t="str">
-        <v>1.4645</v>
+        <v>1.5479</v>
       </c>
       <c r="BI89" t="str">
-        <v>33.0561</v>
+        <v>33.1645</v>
       </c>
       <c r="BJ89" t="str">
-        <v>0</v>
+        <v>1.7147</v>
       </c>
       <c r="BK89" t="str">
-        <v>30.3791</v>
+        <v>32.6148</v>
       </c>
       <c r="BL89" t="str">
         <v>133.4239</v>
       </c>
       <c r="BM89" t="str">
-        <v>137.9759</v>
+        <v>138.0846</v>
       </c>
       <c r="BN89" t="str">
         <v>128.7032</v>
@@ -31574,7 +31563,7 @@
         <v>115.6724</v>
       </c>
       <c r="BQ89" t="str">
-        <v>128.7768</v>
+        <v>128.7879</v>
       </c>
       <c r="BR89" t="str">
         <v>122.6009</v>
@@ -31583,13 +31572,13 @@
         <v>34803.83</v>
       </c>
       <c r="BT89" t="str">
-        <v>163280.4327</v>
+        <v>163294.5067</v>
       </c>
       <c r="BU89" t="str">
-        <v>158467.1155</v>
+        <v>158480.7747</v>
       </c>
       <c r="BV89" t="str">
-        <v>104337.2731</v>
+        <v>104346.2665</v>
       </c>
       <c r="BW89" t="str">
         <v>1</v>
@@ -31670,13 +31659,13 @@
         <v>0</v>
       </c>
       <c r="CW89" t="str">
-        <v>-0.1112</v>
+        <v>-0.1036</v>
       </c>
       <c r="CX89" t="str">
-        <v>6.34</v>
+        <v>7.51</v>
       </c>
       <c r="CY89" t="str">
-        <v>1.868</v>
+        <v>1.7846</v>
       </c>
       <c r="CZ89" t="str">
         <v>-0.4892</v>
@@ -31691,28 +31680,28 @@
         <v>-0.1296</v>
       </c>
       <c r="DD89" t="str">
-        <v>1411.5764</v>
+        <v>1411.6981</v>
       </c>
       <c r="DE89" t="str">
         <v>0.639</v>
       </c>
       <c r="DF89" t="str">
-        <v>1212.7796</v>
+        <v>1212.8841</v>
       </c>
       <c r="DG89" t="str">
-        <v>851.0319</v>
+        <v>851.1052</v>
       </c>
       <c r="DH89" t="str">
-        <v>1.036086</v>
+        <v>1.035997</v>
       </c>
       <c r="DI89" t="str">
-        <v>1.071434</v>
+        <v>1.072186</v>
       </c>
       <c r="DJ89" t="str">
         <v>0.979318</v>
       </c>
       <c r="DK89" t="str">
-        <v>1.05376</v>
+        <v>1.054092</v>
       </c>
       <c r="DL89" t="str">
         <v>0</v>
@@ -31774,7 +31763,7 @@
         <v>13753.41</v>
       </c>
       <c r="O90" t="str">
-        <v>50.81</v>
+        <v>54.09</v>
       </c>
       <c r="P90" t="str">
         <v>49.20655</v>
@@ -31828,10 +31817,10 @@
         <v>85.76</v>
       </c>
       <c r="AG90" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH90" t="str">
-        <v>61.65</v>
+        <v>61.83</v>
       </c>
       <c r="AI90" t="str">
         <v>-151990.8875</v>
@@ -31885,7 +31874,7 @@
         <v>162.8</v>
       </c>
       <c r="AZ90" t="str">
-        <v>1.7681</v>
+        <v>1.769</v>
       </c>
       <c r="BA90" t="str">
         <v>23.82</v>
@@ -31894,31 +31883,31 @@
         <v>3.34</v>
       </c>
       <c r="BC90" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD90" t="str">
         <v>1.19394E+13</v>
       </c>
       <c r="BE90" t="str">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BF90" t="str">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="BG90" t="str">
-        <v>246.56</v>
+        <v>248.3</v>
       </c>
       <c r="BH90" t="str">
-        <v>1.5471</v>
+        <v>1.5479</v>
       </c>
       <c r="BI90" t="str">
         <v>33.1645</v>
       </c>
       <c r="BJ90" t="str">
-        <v>0</v>
+        <v>1.7147</v>
       </c>
       <c r="BK90" t="str">
-        <v>30.3791</v>
+        <v>32.6148</v>
       </c>
       <c r="BL90" t="str">
         <v>132.9583</v>
@@ -32032,13 +32021,13 @@
         <v>0</v>
       </c>
       <c r="CW90" t="str">
-        <v>-0.2471</v>
+        <v>-0.2419</v>
       </c>
       <c r="CX90" t="str">
-        <v>6.3425</v>
+        <v>7.7125</v>
       </c>
       <c r="CY90" t="str">
-        <v>1.7852</v>
+        <v>1.7844</v>
       </c>
       <c r="CZ90" t="str">
         <v>-6.4702</v>
@@ -32115,13 +32104,13 @@
         <v>0.005479</v>
       </c>
       <c r="H91" t="str">
-        <v>47.72</v>
+        <v>47.71</v>
       </c>
       <c r="I91" t="str">
         <v>47.7</v>
       </c>
       <c r="J91" t="str">
-        <v>48.35</v>
+        <v>48.36</v>
       </c>
       <c r="K91" t="str">
         <v>48.6</v>
@@ -32136,7 +32125,7 @@
         <v>13776.83</v>
       </c>
       <c r="O91" t="str">
-        <v>50.81</v>
+        <v>53.08</v>
       </c>
       <c r="P91" t="str">
         <v>49.3768</v>
@@ -32190,10 +32179,10 @@
         <v>85.76</v>
       </c>
       <c r="AG91" t="str">
-        <v>107.87</v>
+        <v>114.09</v>
       </c>
       <c r="AH91" t="str">
-        <v>61.65</v>
+        <v>63.61</v>
       </c>
       <c r="AI91" t="str">
         <v>281503.3</v>
@@ -32256,7 +32245,7 @@
         <v>3.34</v>
       </c>
       <c r="BC91" t="str">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD91" t="str">
         <v>1.26135E+13</v>
@@ -32265,7 +32254,7 @@
         <v>30</v>
       </c>
       <c r="BF91" t="str">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BG91" t="str">
         <v>246.11</v>
@@ -32277,43 +32266,43 @@
         <v>33.1645</v>
       </c>
       <c r="BJ91" t="str">
-        <v>0</v>
+        <v>1.7147</v>
       </c>
       <c r="BK91" t="str">
-        <v>30.3791</v>
+        <v>32.6148</v>
       </c>
       <c r="BL91" t="str">
-        <v>131.8652</v>
+        <v>131.8922</v>
       </c>
       <c r="BM91" t="str">
-        <v>139.4824</v>
+        <v>139.4964</v>
       </c>
       <c r="BN91" t="str">
-        <v>130.5072</v>
+        <v>129.9822</v>
       </c>
       <c r="BO91" t="str">
-        <v>133.1102</v>
+        <v>133.0819</v>
       </c>
       <c r="BP91" t="str">
-        <v>116.2841</v>
+        <v>116.3458</v>
       </c>
       <c r="BQ91" t="str">
-        <v>129.2053</v>
+        <v>129.1301</v>
       </c>
       <c r="BR91" t="str">
-        <v>123.0687</v>
+        <v>123.1231</v>
       </c>
       <c r="BS91" t="str">
         <v>34320.73</v>
       </c>
       <c r="BT91" t="str">
-        <v>163823.7422</v>
+        <v>163728.3936</v>
       </c>
       <c r="BU91" t="str">
-        <v>158994.4089</v>
+        <v>158901.8711</v>
       </c>
       <c r="BV91" t="str">
-        <v>104684.4515</v>
+        <v>104623.5231</v>
       </c>
       <c r="BW91" t="str">
         <v>1</v>
@@ -32394,10 +32383,10 @@
         <v>0</v>
       </c>
       <c r="CW91" t="str">
-        <v>-0.2499</v>
+        <v>-0.2404</v>
       </c>
       <c r="CX91" t="str">
-        <v>6.33</v>
+        <v>7.71</v>
       </c>
       <c r="CY91" t="str">
         <v>1.7854</v>
@@ -32415,28 +32404,28 @@
         <v>0.346</v>
       </c>
       <c r="DD91" t="str">
-        <v>1408.8232</v>
+        <v>1407.2566</v>
       </c>
       <c r="DE91" t="str">
         <v>0.639</v>
       </c>
       <c r="DF91" t="str">
-        <v>1194.457</v>
+        <v>1194.0156</v>
       </c>
       <c r="DG91" t="str">
-        <v>850.618</v>
+        <v>849.7473</v>
       </c>
       <c r="DH91" t="str">
-        <v>1.020587</v>
+        <v>1.02139</v>
       </c>
       <c r="DI91" t="str">
-        <v>1.079541</v>
+        <v>1.080278</v>
       </c>
       <c r="DJ91" t="str">
-        <v>1.009441</v>
+        <v>1.00902</v>
       </c>
       <c r="DK91" t="str">
-        <v>1.050064</v>
+        <v>1.050834</v>
       </c>
       <c r="DL91" t="str">
         <v>0</v>
@@ -32467,86 +32456,215 @@
       <c r="D92" t="str">
         <v>05.06.2026</v>
       </c>
+      <c r="E92" t="str">
+        <v>39.992</v>
+      </c>
+      <c r="F92" t="str">
+        <v>40</v>
+      </c>
+      <c r="G92" t="str">
+        <v>0.005479</v>
+      </c>
+      <c r="H92" t="str">
+        <v>47.47</v>
+      </c>
+      <c r="I92" t="str">
+        <v>47.71</v>
+      </c>
+      <c r="J92" t="str">
+        <v>48.84</v>
+      </c>
+      <c r="K92" t="str">
+        <v>48.36</v>
+      </c>
       <c r="L92" t="str">
         <v>43.875</v>
       </c>
       <c r="M92" t="str">
         <v>39.04</v>
       </c>
+      <c r="N92" t="str">
+        <v>13887.25</v>
+      </c>
+      <c r="O92" t="str">
+        <v>55.33</v>
+      </c>
+      <c r="P92" t="str">
+        <v>49.662</v>
+      </c>
       <c r="Q92" t="str">
         <v>1</v>
       </c>
       <c r="R92" t="str">
-        <v>4482.7334</v>
+        <v>4442.7801</v>
       </c>
       <c r="S92" t="str">
-        <v>16.0267</v>
+        <v>16.958</v>
       </c>
       <c r="T92" t="str">
-        <v>15969.2337</v>
+        <v>15927.0203</v>
       </c>
       <c r="U92" t="str">
-        <v>1.1631</v>
+        <v>1.1626</v>
       </c>
       <c r="V92" t="str">
-        <v>45.9251</v>
+        <v>45.9613</v>
       </c>
       <c r="W92" t="str">
-        <v>53.4295</v>
+        <v>53.4709</v>
       </c>
       <c r="X92" t="str">
-        <v>6.5762</v>
+        <v>6.4858</v>
       </c>
       <c r="Y92" t="str">
-        <v>74.9027</v>
+        <v>73.3032</v>
       </c>
       <c r="Z92" t="str">
-        <v>96.1167</v>
+        <v>95.382</v>
       </c>
       <c r="AA92" t="str">
-        <v>99.3027</v>
+        <v>99.486</v>
       </c>
       <c r="AB92" t="str">
-        <v>0.000753</v>
+        <v>0.000645</v>
       </c>
       <c r="AC92" t="str">
-        <v>6618.87</v>
+        <v>6564.95</v>
+      </c>
+      <c r="AD92" t="str">
+        <v>0.01113</v>
+      </c>
+      <c r="AE92" t="str">
+        <v>74.2</v>
+      </c>
+      <c r="AF92" t="str">
+        <v>85.76</v>
+      </c>
+      <c r="AG92" t="str">
+        <v>114.09</v>
+      </c>
+      <c r="AH92" t="str">
+        <v>64.13</v>
+      </c>
+      <c r="AI92" t="str">
+        <v>228231.44</v>
+      </c>
+      <c r="AJ92" t="str">
+        <v>154.1</v>
+      </c>
+      <c r="AK92" t="str">
+        <v>146.8</v>
+      </c>
+      <c r="AL92" t="str">
+        <v>151</v>
+      </c>
+      <c r="AM92" t="str">
+        <v>164.5</v>
+      </c>
+      <c r="AN92" t="str">
+        <v>151.8</v>
+      </c>
+      <c r="AO92" t="str">
+        <v>143.5</v>
+      </c>
+      <c r="AP92" t="str">
+        <v>148.4</v>
+      </c>
+      <c r="AQ92" t="str">
+        <v>163.6</v>
+      </c>
+      <c r="AR92" t="str">
+        <v>181.4</v>
+      </c>
+      <c r="AS92" t="str">
+        <v>187.3</v>
+      </c>
+      <c r="AT92" t="str">
+        <v>182.4</v>
+      </c>
+      <c r="AU92" t="str">
+        <v>174.4</v>
+      </c>
+      <c r="AV92" t="str">
+        <v>150.9</v>
+      </c>
+      <c r="AW92" t="str">
+        <v>143.6</v>
+      </c>
+      <c r="AX92" t="str">
+        <v>146.4</v>
+      </c>
+      <c r="AY92" t="str">
+        <v>162.8</v>
+      </c>
+      <c r="AZ92" t="str">
+        <v>0.9783</v>
+      </c>
+      <c r="BA92" t="str">
+        <v>23.81</v>
+      </c>
+      <c r="BB92" t="str">
+        <v>3.17</v>
+      </c>
+      <c r="BC92" t="str">
+        <v>8</v>
       </c>
       <c r="BD92" t="str">
-        <v>1.60677E+13</v>
+        <v>2.93854E+13</v>
+      </c>
+      <c r="BE92" t="str">
+        <v>44</v>
       </c>
       <c r="BF92" t="str">
         <v>43</v>
       </c>
+      <c r="BG92" t="str">
+        <v>239.04</v>
+      </c>
       <c r="BH92" t="str">
-        <v>0.4281</v>
+        <v>0.856</v>
       </c>
       <c r="BI92" t="str">
-        <v>32.013</v>
+        <v>32.5754</v>
+      </c>
+      <c r="BJ92" t="str">
+        <v>1.7147</v>
+      </c>
+      <c r="BK92" t="str">
+        <v>32.6148</v>
       </c>
       <c r="BL92" t="str">
-        <v>135.1526</v>
+        <v>133.3179</v>
       </c>
       <c r="BM92" t="str">
-        <v>140.2461</v>
+        <v>140.6144</v>
       </c>
       <c r="BN92" t="str">
-        <v>126.1685</v>
+        <v>128.8322</v>
       </c>
       <c r="BO92" t="str">
-        <v>133.4877</v>
+        <v>133.3995</v>
       </c>
       <c r="BP92" t="str">
-        <v>117.6506</v>
+        <v>117.1744</v>
       </c>
       <c r="BQ92" t="str">
-        <v>129.8533</v>
+        <v>129.8334</v>
       </c>
       <c r="BR92" t="str">
-        <v>123.7149</v>
+        <v>123.6841</v>
       </c>
       <c r="BS92" t="str">
-        <v>35423.82</v>
+        <v>34832.63</v>
+      </c>
+      <c r="BT92" t="str">
+        <v>164620.1313</v>
+      </c>
+      <c r="BU92" t="str">
+        <v>159767.3214</v>
+      </c>
+      <c r="BV92" t="str">
+        <v>105193.3494</v>
       </c>
       <c r="BW92" t="str">
         <v>1</v>
@@ -32627,31 +32745,49 @@
         <v>0</v>
       </c>
       <c r="CW92" t="str">
-        <v>-0.5653</v>
+        <v>-0.4933</v>
+      </c>
+      <c r="CX92" t="str">
+        <v>7.478</v>
+      </c>
+      <c r="CY92" t="str">
+        <v>2.4767</v>
       </c>
       <c r="CZ92" t="str">
-        <v>1.2721</v>
+        <v>0.8015</v>
       </c>
       <c r="DA92" t="str">
-        <v>-0.3587</v>
+        <v>-1.1705</v>
       </c>
       <c r="DB92" t="str">
-        <v>0.1406</v>
+        <v>0.2196</v>
       </c>
       <c r="DC92" t="str">
-        <v>0.3978</v>
+        <v>0.5776</v>
+      </c>
+      <c r="DD92" t="str">
+        <v>1404.9155</v>
+      </c>
+      <c r="DE92" t="str">
+        <v>0.639</v>
+      </c>
+      <c r="DF92" t="str">
+        <v>1197.6606</v>
+      </c>
+      <c r="DG92" t="str">
+        <v>850.5002</v>
       </c>
       <c r="DH92" t="str">
-        <v>1.04081</v>
+        <v>1.026838</v>
       </c>
       <c r="DI92" t="str">
-        <v>1.080035</v>
+        <v>1.083037</v>
       </c>
       <c r="DJ92" t="str">
-        <v>0.987681</v>
+        <v>1.000612</v>
       </c>
       <c r="DK92" t="str">
-        <v>1.060422</v>
+        <v>1.054938</v>
       </c>
       <c r="DL92" t="str">
         <v>0</v>
@@ -32666,12 +32802,736 @@
         <v>0</v>
       </c>
       <c r="DP92" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2026</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Hafta 24</v>
+      </c>
+      <c r="C93" t="str">
+        <v>08.06.2026</v>
+      </c>
+      <c r="D93" t="str">
+        <v>12.06.2026</v>
+      </c>
+      <c r="E93" t="str">
+        <v>39.996</v>
+      </c>
+      <c r="F93" t="str">
+        <v>40</v>
+      </c>
+      <c r="G93" t="str">
+        <v>0.005479</v>
+      </c>
+      <c r="H93" t="str">
+        <v>47.47</v>
+      </c>
+      <c r="I93" t="str">
+        <v>47.47</v>
+      </c>
+      <c r="J93" t="str">
+        <v>48.84</v>
+      </c>
+      <c r="K93" t="str">
+        <v>48.84</v>
+      </c>
+      <c r="L93" t="str">
+        <v>43.875</v>
+      </c>
+      <c r="M93" t="str">
+        <v>38.9016</v>
+      </c>
+      <c r="N93" t="str">
+        <v>13805.82</v>
+      </c>
+      <c r="O93" t="str">
+        <v>55.33</v>
+      </c>
+      <c r="P93" t="str">
+        <v>49.7138</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>1</v>
+      </c>
+      <c r="R93" t="str">
+        <v>4201.88</v>
+      </c>
+      <c r="S93" t="str">
+        <v>19.626</v>
+      </c>
+      <c r="T93" t="str">
+        <v>16450.1002</v>
+      </c>
+      <c r="U93" t="str">
+        <v>1.154</v>
+      </c>
+      <c r="V93" t="str">
+        <v>46.1419</v>
+      </c>
+      <c r="W93" t="str">
+        <v>53.289</v>
+      </c>
+      <c r="X93" t="str">
+        <v>6.3141</v>
+      </c>
+      <c r="Y93" t="str">
+        <v>65.9724</v>
+      </c>
+      <c r="Z93" t="str">
+        <v>91.302</v>
+      </c>
+      <c r="AA93" t="str">
+        <v>99.904</v>
+      </c>
+      <c r="AB93" t="str">
+        <v>0.000674</v>
+      </c>
+      <c r="AC93" t="str">
+        <v>6233.43</v>
+      </c>
+      <c r="AD93" t="str">
+        <v>0.012357</v>
+      </c>
+      <c r="AE93" t="str">
+        <v>74.2</v>
+      </c>
+      <c r="AF93" t="str">
+        <v>85.76</v>
+      </c>
+      <c r="AG93" t="str">
+        <v>114.09</v>
+      </c>
+      <c r="AH93" t="str">
+        <v>64.13</v>
+      </c>
+      <c r="AI93" t="str">
+        <v>446372.02</v>
+      </c>
+      <c r="AJ93" t="str">
+        <v>154.1</v>
+      </c>
+      <c r="AK93" t="str">
+        <v>146.8</v>
+      </c>
+      <c r="AL93" t="str">
+        <v>151</v>
+      </c>
+      <c r="AM93" t="str">
+        <v>164.5</v>
+      </c>
+      <c r="AN93" t="str">
+        <v>151.8</v>
+      </c>
+      <c r="AO93" t="str">
+        <v>143.5</v>
+      </c>
+      <c r="AP93" t="str">
+        <v>148.4</v>
+      </c>
+      <c r="AQ93" t="str">
+        <v>163.6</v>
+      </c>
+      <c r="AR93" t="str">
+        <v>181.4</v>
+      </c>
+      <c r="AS93" t="str">
+        <v>187.3</v>
+      </c>
+      <c r="AT93" t="str">
+        <v>182.4</v>
+      </c>
+      <c r="AU93" t="str">
+        <v>174.4</v>
+      </c>
+      <c r="AV93" t="str">
+        <v>150.9</v>
+      </c>
+      <c r="AW93" t="str">
+        <v>143.6</v>
+      </c>
+      <c r="AX93" t="str">
+        <v>146.4</v>
+      </c>
+      <c r="AY93" t="str">
+        <v>162.8</v>
+      </c>
+      <c r="AZ93" t="str">
+        <v>0.9783</v>
+      </c>
+      <c r="BA93" t="str">
+        <v>23.81</v>
+      </c>
+      <c r="BB93" t="str">
+        <v>3.17</v>
+      </c>
+      <c r="BC93" t="str">
+        <v>8</v>
+      </c>
+      <c r="BD93" t="str">
+        <v>1.27434E+13</v>
+      </c>
+      <c r="BE93" t="str">
+        <v>45</v>
+      </c>
+      <c r="BF93" t="str">
+        <v>44</v>
+      </c>
+      <c r="BG93" t="str">
+        <v>238.29</v>
+      </c>
+      <c r="BH93" t="str">
+        <v>0.856</v>
+      </c>
+      <c r="BI93" t="str">
+        <v>32.5754</v>
+      </c>
+      <c r="BJ93" t="str">
+        <v>1.7147</v>
+      </c>
+      <c r="BK93" t="str">
+        <v>32.6148</v>
+      </c>
+      <c r="BL93" t="str">
+        <v>132.4855</v>
+      </c>
+      <c r="BM93" t="str">
+        <v>141.3941</v>
+      </c>
+      <c r="BN93" t="str">
+        <v>129.1713</v>
+      </c>
+      <c r="BO93" t="str">
+        <v>133.1168</v>
+      </c>
+      <c r="BP93" t="str">
+        <v>117.3444</v>
+      </c>
+      <c r="BQ93" t="str">
+        <v>129.9536</v>
+      </c>
+      <c r="BR93" t="str">
+        <v>124.6635</v>
+      </c>
+      <c r="BS93" t="str">
+        <v>34474.86</v>
+      </c>
+      <c r="BT93" t="str">
+        <v>164772.5369</v>
+      </c>
+      <c r="BU93" t="str">
+        <v>159915.2342</v>
+      </c>
+      <c r="BV93" t="str">
+        <v>105290.7376</v>
+      </c>
+      <c r="BW93" t="str">
+        <v>0</v>
+      </c>
+      <c r="BX93" t="str">
+        <v>0</v>
+      </c>
+      <c r="BY93" t="str">
+        <v>0</v>
+      </c>
+      <c r="BZ93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CA93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CB93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CC93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="str">
+        <v>3</v>
+      </c>
+      <c r="CF93" t="str">
+        <v>6</v>
+      </c>
+      <c r="CG93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CJ93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CK93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CN93" t="str">
+        <v>1</v>
+      </c>
+      <c r="CO93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="str">
+        <v>1</v>
+      </c>
+      <c r="CQ93" t="str">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="str">
+        <v>1</v>
+      </c>
+      <c r="CS93" t="str">
+        <v>1</v>
+      </c>
+      <c r="CT93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CU93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CV93" t="str">
+        <v>0</v>
+      </c>
+      <c r="CW93" t="str">
+        <v>-0.1678</v>
+      </c>
+      <c r="CX93" t="str">
+        <v>7.474</v>
+      </c>
+      <c r="CY93" t="str">
+        <v>2.477</v>
+      </c>
+      <c r="CZ93" t="str">
+        <v>-0.5864</v>
+      </c>
+      <c r="DA93" t="str">
+        <v>-5.0498</v>
+      </c>
+      <c r="DB93" t="str">
+        <v>0.3929</v>
+      </c>
+      <c r="DC93" t="str">
+        <v>0.1043</v>
+      </c>
+      <c r="DD93" t="str">
+        <v>1404.179</v>
+      </c>
+      <c r="DE93" t="str">
+        <v>0.639</v>
+      </c>
+      <c r="DF93" t="str">
+        <v>1201.3152</v>
+      </c>
+      <c r="DG93" t="str">
+        <v>844.5996</v>
+      </c>
+      <c r="DH93" t="str">
+        <v>1.019483</v>
+      </c>
+      <c r="DI93" t="str">
+        <v>1.088035</v>
+      </c>
+      <c r="DJ93" t="str">
+        <v>1.004765</v>
+      </c>
+      <c r="DK93" t="str">
+        <v>1.053759</v>
+      </c>
+      <c r="DL93" t="str">
+        <v>0</v>
+      </c>
+      <c r="DM93" t="str">
+        <v>1</v>
+      </c>
+      <c r="DN93" t="str">
+        <v>0</v>
+      </c>
+      <c r="DO93" t="str">
+        <v>0</v>
+      </c>
+      <c r="DP93" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2026</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Hafta 24</v>
+      </c>
+      <c r="C94" t="str">
+        <v>15.06.2026</v>
+      </c>
+      <c r="D94" t="str">
+        <v>19.06.2026</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v>47.47</v>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v>48.84</v>
+      </c>
+      <c r="L94" t="str">
+        <v>44</v>
+      </c>
+      <c r="M94" t="str">
+        <v>38.9279</v>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v>1</v>
+      </c>
+      <c r="R94" t="str">
+        <v>4361.1001</v>
+      </c>
+      <c r="S94" t="str">
+        <v>16.84</v>
+      </c>
+      <c r="T94" t="str">
+        <v>18180.7695</v>
+      </c>
+      <c r="U94" t="str">
+        <v>1.1609</v>
+      </c>
+      <c r="V94" t="str">
+        <v>46.2761</v>
+      </c>
+      <c r="W94" t="str">
+        <v>53.7427</v>
+      </c>
+      <c r="X94" t="str">
+        <v>6.496</v>
+      </c>
+      <c r="Y94" t="str">
+        <v>70.86</v>
+      </c>
+      <c r="Z94" t="str">
+        <v>82.88</v>
+      </c>
+      <c r="AA94" t="str">
+        <v>99.519</v>
+      </c>
+      <c r="AB94" t="str">
+        <v>0.000673</v>
+      </c>
+      <c r="AC94" t="str">
+        <v>6488.49</v>
+      </c>
+      <c r="AD94" t="str">
+        <v>0.014958</v>
+      </c>
+      <c r="AE94" t="str">
+        <v/>
+      </c>
+      <c r="AF94" t="str">
+        <v/>
+      </c>
+      <c r="AG94" t="str">
+        <v/>
+      </c>
+      <c r="AH94" t="str">
+        <v/>
+      </c>
+      <c r="AI94" t="str">
+        <v/>
+      </c>
+      <c r="AJ94" t="str">
+        <v/>
+      </c>
+      <c r="AK94" t="str">
+        <v/>
+      </c>
+      <c r="AL94" t="str">
+        <v/>
+      </c>
+      <c r="AM94" t="str">
+        <v/>
+      </c>
+      <c r="AN94" t="str">
+        <v/>
+      </c>
+      <c r="AO94" t="str">
+        <v/>
+      </c>
+      <c r="AP94" t="str">
+        <v/>
+      </c>
+      <c r="AQ94" t="str">
+        <v/>
+      </c>
+      <c r="AR94" t="str">
+        <v/>
+      </c>
+      <c r="AS94" t="str">
+        <v/>
+      </c>
+      <c r="AT94" t="str">
+        <v/>
+      </c>
+      <c r="AU94" t="str">
+        <v/>
+      </c>
+      <c r="AV94" t="str">
+        <v/>
+      </c>
+      <c r="AW94" t="str">
+        <v/>
+      </c>
+      <c r="AX94" t="str">
+        <v/>
+      </c>
+      <c r="AY94" t="str">
+        <v/>
+      </c>
+      <c r="AZ94" t="str">
+        <v/>
+      </c>
+      <c r="BA94" t="str">
+        <v/>
+      </c>
+      <c r="BB94" t="str">
+        <v/>
+      </c>
+      <c r="BC94" t="str">
+        <v/>
+      </c>
+      <c r="BD94" t="str">
+        <v>3.78697E+12</v>
+      </c>
+      <c r="BE94" t="str">
+        <v>33</v>
+      </c>
+      <c r="BF94" t="str">
+        <v>31</v>
+      </c>
+      <c r="BG94" t="str">
+        <v/>
+      </c>
+      <c r="BH94" t="str">
+        <v>0.8414</v>
+      </c>
+      <c r="BI94" t="str">
+        <v>32.5562</v>
+      </c>
+      <c r="BJ94" t="str">
+        <v/>
+      </c>
+      <c r="BK94" t="str">
+        <v/>
+      </c>
+      <c r="BL94" t="str">
+        <v>131.6611</v>
+      </c>
+      <c r="BM94" t="str">
+        <v>141.409</v>
+      </c>
+      <c r="BN94" t="str">
+        <v>129.8607</v>
+      </c>
+      <c r="BO94" t="str">
+        <v>133.5192</v>
+      </c>
+      <c r="BP94" t="str">
+        <v>119.9817</v>
+      </c>
+      <c r="BQ94" t="str">
+        <v>130.0919</v>
+      </c>
+      <c r="BR94" t="str">
+        <v>124.9332</v>
+      </c>
+      <c r="BS94" t="str">
+        <v/>
+      </c>
+      <c r="BT94" t="str">
+        <v/>
+      </c>
+      <c r="BU94" t="str">
+        <v/>
+      </c>
+      <c r="BV94" t="str">
+        <v/>
+      </c>
+      <c r="BW94" t="str">
+        <v>1</v>
+      </c>
+      <c r="BX94" t="str">
+        <v>1</v>
+      </c>
+      <c r="BY94" t="str">
+        <v>0</v>
+      </c>
+      <c r="BZ94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CA94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CB94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CC94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="str">
+        <v>3</v>
+      </c>
+      <c r="CF94" t="str">
+        <v>6</v>
+      </c>
+      <c r="CG94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="str">
+        <v>1</v>
+      </c>
+      <c r="CI94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CJ94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CK94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CL94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CM94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CN94" t="str">
+        <v>1</v>
+      </c>
+      <c r="CO94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CQ94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CR94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CS94" t="str">
+        <v>1</v>
+      </c>
+      <c r="CT94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CU94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CV94" t="str">
+        <v>0</v>
+      </c>
+      <c r="CW94" t="str">
+        <v>-0.2388</v>
+      </c>
+      <c r="CX94" t="str">
+        <v/>
+      </c>
+      <c r="CY94" t="str">
+        <v/>
+      </c>
+      <c r="CZ94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DA94" t="str">
+        <v>4.0918</v>
+      </c>
+      <c r="DB94" t="str">
+        <v>0.2908</v>
+      </c>
+      <c r="DC94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DD94" t="str">
+        <v/>
+      </c>
+      <c r="DE94" t="str">
+        <v/>
+      </c>
+      <c r="DF94" t="str">
+        <v/>
+      </c>
+      <c r="DG94" t="str">
+        <v/>
+      </c>
+      <c r="DH94" t="str">
+        <v>1.012062</v>
+      </c>
+      <c r="DI94" t="str">
+        <v>1.086993</v>
+      </c>
+      <c r="DJ94" t="str">
+        <v>1.014113</v>
+      </c>
+      <c r="DK94" t="str">
+        <v>1.049528</v>
+      </c>
+      <c r="DL94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DM94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DN94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DO94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DP94" t="str">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:DP92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:DP94"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -33605,7 +34465,7 @@
         <v>Aylık yayın, ay içinde değer değişmez — ffill doğal davranış.</v>
       </c>
       <c r="I32" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -33634,7 +34494,7 @@
         <v>Aylık yayın, ay içinde sabit — ffill yayın tarihinden bir sonrakine kadar geçerli.</v>
       </c>
       <c r="I33" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -33663,7 +34523,7 @@
         <v>Aylık yayın, ay içinde sabit.</v>
       </c>
       <c r="I34" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -33750,7 +34610,7 @@
         <v>Aylık FHGE yayını, ay içinde sabit.</v>
       </c>
       <c r="I37" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -33779,7 +34639,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I38" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -33808,7 +34668,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I39" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -33837,7 +34697,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I40" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -33866,7 +34726,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I41" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -33895,7 +34755,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I42" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -33924,7 +34784,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I43" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -33953,7 +34813,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I44" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -33982,7 +34842,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I45" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -34011,7 +34871,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I46" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -34040,7 +34900,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I47" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -34069,7 +34929,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I48" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -34098,7 +34958,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I49" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -34127,7 +34987,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I50" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -34156,7 +35016,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I51" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -34185,7 +35045,7 @@
         <v>Aylık FHGE alt endeks, ay içinde sabit.</v>
       </c>
       <c r="I52" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -34243,7 +35103,7 @@
         <v>Aylık Beklenti Anketi, ay içinde sabit.</v>
       </c>
       <c r="I54" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -34272,7 +35132,7 @@
         <v>Aylık Beklenti Anketi, ay içinde sabit.</v>
       </c>
       <c r="I55" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -34301,7 +35161,7 @@
         <v>İşsizlik güçlü mevsimsel (yaz düşük, kış yüksek); yıldan yıla aynı ay farkı statik ffill'den daha gerçekçi.</v>
       </c>
       <c r="I56" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -34330,7 +35190,7 @@
         <v>CoinGecko free tier 365-gün sınırı; güvenilir alternatif donor yok → ilk 29 hafta gerçek warmup.</v>
       </c>
       <c r="I57" t="str">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58">
@@ -34475,7 +35335,7 @@
         <v>Yıllık değer geriye uydurmak 15 ay'lık bileşik etkiyi taklit eder — çarpık olur, NaN bırakıldı.</v>
       </c>
       <c r="I62" t="str">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63">
@@ -34533,7 +35393,7 @@
         <v>Yıllık bileşik değer 15+ ay geriye bfill edilirse çarpık olur — erken hafta NaN bırakıldı.</v>
       </c>
       <c r="I64" t="str">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65">

--- a/external_dataset.xlsx
+++ b/external_dataset.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DP94"/>
+  <dimension ref="A1:DP95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -33172,7 +33172,7 @@
         <v>2026</v>
       </c>
       <c r="B94" t="str">
-        <v>Hafta 24</v>
+        <v>Hafta 25</v>
       </c>
       <c r="C94" t="str">
         <v>15.06.2026</v>
@@ -33181,214 +33181,214 @@
         <v>19.06.2026</v>
       </c>
       <c r="E94" t="str">
-        <v/>
+        <v>39.99</v>
       </c>
       <c r="F94" t="str">
-        <v/>
+        <v>40</v>
       </c>
       <c r="G94" t="str">
-        <v/>
+        <v>0.005479</v>
       </c>
       <c r="H94" t="str">
-        <v/>
+        <v>47.5</v>
       </c>
       <c r="I94" t="str">
-        <v>47.47</v>
+        <v>47.5</v>
       </c>
       <c r="J94" t="str">
-        <v/>
+        <v>48.85</v>
       </c>
       <c r="K94" t="str">
-        <v>48.84</v>
+        <v>48.85</v>
       </c>
       <c r="L94" t="str">
         <v>44</v>
       </c>
       <c r="M94" t="str">
-        <v>38.9279</v>
+        <v>39.0547</v>
       </c>
       <c r="N94" t="str">
-        <v/>
+        <v>14584.5</v>
       </c>
       <c r="O94" t="str">
-        <v/>
+        <v>55.32</v>
       </c>
       <c r="P94" t="str">
-        <v/>
+        <v>49.641</v>
       </c>
       <c r="Q94" t="str">
         <v>1</v>
       </c>
       <c r="R94" t="str">
-        <v>4361.1001</v>
+        <v>4310.475</v>
       </c>
       <c r="S94" t="str">
-        <v>16.84</v>
+        <v>16.8625</v>
       </c>
       <c r="T94" t="str">
-        <v>18180.7695</v>
+        <v>18510.0801</v>
       </c>
       <c r="U94" t="str">
-        <v>1.1609</v>
+        <v>1.1555</v>
       </c>
       <c r="V94" t="str">
-        <v>46.2761</v>
+        <v>46.3428</v>
       </c>
       <c r="W94" t="str">
-        <v>53.7427</v>
+        <v>53.5978</v>
       </c>
       <c r="X94" t="str">
-        <v>6.496</v>
+        <v>6.4569</v>
       </c>
       <c r="Y94" t="str">
-        <v>70.86</v>
+        <v>69.229</v>
       </c>
       <c r="Z94" t="str">
-        <v>82.88</v>
+        <v>80.3825</v>
       </c>
       <c r="AA94" t="str">
-        <v>99.519</v>
+        <v>100.0275</v>
       </c>
       <c r="AB94" t="str">
-        <v>0.000673</v>
+        <v>0.000878</v>
       </c>
       <c r="AC94" t="str">
-        <v>6488.49</v>
+        <v>6419.64</v>
       </c>
       <c r="AD94" t="str">
-        <v>0.014958</v>
+        <v>0.017285</v>
       </c>
       <c r="AE94" t="str">
-        <v/>
+        <v>74.5</v>
       </c>
       <c r="AF94" t="str">
-        <v/>
+        <v>87.93</v>
       </c>
       <c r="AG94" t="str">
-        <v/>
+        <v>114.09</v>
       </c>
       <c r="AH94" t="str">
-        <v/>
+        <v>63.94</v>
       </c>
       <c r="AI94" t="str">
-        <v/>
+        <v>-261631.356</v>
       </c>
       <c r="AJ94" t="str">
-        <v/>
+        <v>154.1</v>
       </c>
       <c r="AK94" t="str">
-        <v/>
+        <v>146.8</v>
       </c>
       <c r="AL94" t="str">
-        <v/>
+        <v>151</v>
       </c>
       <c r="AM94" t="str">
-        <v/>
+        <v>164.5</v>
       </c>
       <c r="AN94" t="str">
-        <v/>
+        <v>151.8</v>
       </c>
       <c r="AO94" t="str">
-        <v/>
+        <v>143.5</v>
       </c>
       <c r="AP94" t="str">
-        <v/>
+        <v>148.4</v>
       </c>
       <c r="AQ94" t="str">
-        <v/>
+        <v>163.6</v>
       </c>
       <c r="AR94" t="str">
-        <v/>
+        <v>181.4</v>
       </c>
       <c r="AS94" t="str">
-        <v/>
+        <v>187.3</v>
       </c>
       <c r="AT94" t="str">
-        <v/>
+        <v>182.4</v>
       </c>
       <c r="AU94" t="str">
-        <v/>
+        <v>174.4</v>
       </c>
       <c r="AV94" t="str">
-        <v/>
+        <v>150.9</v>
       </c>
       <c r="AW94" t="str">
-        <v/>
+        <v>143.6</v>
       </c>
       <c r="AX94" t="str">
-        <v/>
+        <v>146.4</v>
       </c>
       <c r="AY94" t="str">
-        <v/>
+        <v>162.8</v>
       </c>
       <c r="AZ94" t="str">
-        <v/>
+        <v>0.956</v>
       </c>
       <c r="BA94" t="str">
-        <v/>
+        <v>23.81</v>
       </c>
       <c r="BB94" t="str">
-        <v/>
+        <v>3.17</v>
       </c>
       <c r="BC94" t="str">
-        <v/>
+        <v>8</v>
       </c>
       <c r="BD94" t="str">
-        <v>3.78697E+12</v>
+        <v>1.40119E+13</v>
       </c>
       <c r="BE94" t="str">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="BF94" t="str">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="BG94" t="str">
-        <v/>
+        <v>219.04</v>
       </c>
       <c r="BH94" t="str">
-        <v>0.8414</v>
+        <v>0.8577</v>
       </c>
       <c r="BI94" t="str">
-        <v>32.5562</v>
+        <v>32.5777</v>
       </c>
       <c r="BJ94" t="str">
-        <v/>
+        <v>1.7147</v>
       </c>
       <c r="BK94" t="str">
-        <v/>
+        <v>32.6148</v>
       </c>
       <c r="BL94" t="str">
-        <v>131.6611</v>
+        <v>131.7227</v>
       </c>
       <c r="BM94" t="str">
-        <v>141.409</v>
+        <v>141.4548</v>
       </c>
       <c r="BN94" t="str">
-        <v>129.8607</v>
+        <v>129.5418</v>
       </c>
       <c r="BO94" t="str">
-        <v>133.5192</v>
+        <v>134.2013</v>
       </c>
       <c r="BP94" t="str">
-        <v>119.9817</v>
+        <v>118.0747</v>
       </c>
       <c r="BQ94" t="str">
-        <v>130.0919</v>
+        <v>130.0099</v>
       </c>
       <c r="BR94" t="str">
-        <v>124.9332</v>
+        <v>125.256</v>
       </c>
       <c r="BS94" t="str">
-        <v/>
+        <v>33934.36</v>
       </c>
       <c r="BT94" t="str">
-        <v/>
+        <v>164843.9216</v>
       </c>
       <c r="BU94" t="str">
-        <v/>
+        <v>159984.5146</v>
       </c>
       <c r="BV94" t="str">
-        <v/>
+        <v>105336.3528</v>
       </c>
       <c r="BW94" t="str">
         <v>1</v>
@@ -33469,69 +33469,431 @@
         <v>0</v>
       </c>
       <c r="CW94" t="str">
-        <v>-0.2388</v>
+        <v>-0.0611</v>
       </c>
       <c r="CX94" t="str">
+        <v>7.51</v>
+      </c>
+      <c r="CY94" t="str">
+        <v>2.4748</v>
+      </c>
+      <c r="CZ94" t="str">
+        <v>5.6402</v>
+      </c>
+      <c r="DA94" t="str">
+        <v>2.9873</v>
+      </c>
+      <c r="DB94" t="str">
+        <v>0.4354</v>
+      </c>
+      <c r="DC94" t="str">
+        <v>-0.1464</v>
+      </c>
+      <c r="DD94" t="str">
+        <v>1396.0986</v>
+      </c>
+      <c r="DE94" t="str">
+        <v>0.639</v>
+      </c>
+      <c r="DF94" t="str">
+        <v>1192.1234</v>
+      </c>
+      <c r="DG94" t="str">
+        <v>840.9685</v>
+      </c>
+      <c r="DH94" t="str">
+        <v>1.013174</v>
+      </c>
+      <c r="DI94" t="str">
+        <v>1.088031</v>
+      </c>
+      <c r="DJ94" t="str">
+        <v>1.018817</v>
+      </c>
+      <c r="DK94" t="str">
+        <v>1.050603</v>
+      </c>
+      <c r="DL94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DM94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DN94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DO94" t="str">
+        <v>0</v>
+      </c>
+      <c r="DP94" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2026</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Hafta 26</v>
+      </c>
+      <c r="C95" t="str">
+        <v>22.06.2026</v>
+      </c>
+      <c r="D95" t="str">
+        <v>26.06.2026</v>
+      </c>
+      <c r="E95" t="str">
         <v/>
       </c>
-      <c r="CY94" t="str">
+      <c r="F95" t="str">
         <v/>
       </c>
-      <c r="CZ94" t="str">
-        <v>0</v>
-      </c>
-      <c r="DA94" t="str">
-        <v>4.0918</v>
-      </c>
-      <c r="DB94" t="str">
-        <v>0.2908</v>
-      </c>
-      <c r="DC94" t="str">
-        <v>0</v>
-      </c>
-      <c r="DD94" t="str">
+      <c r="G95" t="str">
         <v/>
       </c>
-      <c r="DE94" t="str">
+      <c r="H95" t="str">
         <v/>
       </c>
-      <c r="DF94" t="str">
+      <c r="I95" t="str">
+        <v>47.5</v>
+      </c>
+      <c r="J95" t="str">
         <v/>
       </c>
-      <c r="DG94" t="str">
+      <c r="K95" t="str">
+        <v>48.85</v>
+      </c>
+      <c r="L95" t="str">
+        <v>44.25</v>
+      </c>
+      <c r="M95" t="str">
+        <v>39.244</v>
+      </c>
+      <c r="N95" t="str">
         <v/>
       </c>
-      <c r="DH94" t="str">
-        <v>1.012062</v>
-      </c>
-      <c r="DI94" t="str">
-        <v>1.086993</v>
-      </c>
-      <c r="DJ94" t="str">
-        <v>1.014113</v>
-      </c>
-      <c r="DK94" t="str">
-        <v>1.049528</v>
-      </c>
-      <c r="DL94" t="str">
-        <v>0</v>
-      </c>
-      <c r="DM94" t="str">
-        <v>0</v>
-      </c>
-      <c r="DN94" t="str">
-        <v>0</v>
-      </c>
-      <c r="DO94" t="str">
-        <v>0</v>
-      </c>
-      <c r="DP94" t="str">
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v>1</v>
+      </c>
+      <c r="R95" t="str">
+        <v>4227.6001</v>
+      </c>
+      <c r="S95" t="str">
+        <v>17.45</v>
+      </c>
+      <c r="T95" t="str">
+        <v>19090.9102</v>
+      </c>
+      <c r="U95" t="str">
+        <v>1.1456</v>
+      </c>
+      <c r="V95" t="str">
+        <v>46.4565</v>
+      </c>
+      <c r="W95" t="str">
+        <v>53.2407</v>
+      </c>
+      <c r="X95" t="str">
+        <v>6.383</v>
+      </c>
+      <c r="Y95" t="str">
+        <v>66.66</v>
+      </c>
+      <c r="Z95" t="str">
+        <v>78.98</v>
+      </c>
+      <c r="AA95" t="str">
+        <v>100.887</v>
+      </c>
+      <c r="AB95" t="str">
+        <v>0.001247</v>
+      </c>
+      <c r="AC95" t="str">
+        <v>6314.39</v>
+      </c>
+      <c r="AD95" t="str">
+        <v>0.013841</v>
+      </c>
+      <c r="AE95" t="str">
+        <v/>
+      </c>
+      <c r="AF95" t="str">
+        <v/>
+      </c>
+      <c r="AG95" t="str">
+        <v/>
+      </c>
+      <c r="AH95" t="str">
+        <v/>
+      </c>
+      <c r="AI95" t="str">
+        <v/>
+      </c>
+      <c r="AJ95" t="str">
+        <v/>
+      </c>
+      <c r="AK95" t="str">
+        <v/>
+      </c>
+      <c r="AL95" t="str">
+        <v/>
+      </c>
+      <c r="AM95" t="str">
+        <v/>
+      </c>
+      <c r="AN95" t="str">
+        <v/>
+      </c>
+      <c r="AO95" t="str">
+        <v/>
+      </c>
+      <c r="AP95" t="str">
+        <v/>
+      </c>
+      <c r="AQ95" t="str">
+        <v/>
+      </c>
+      <c r="AR95" t="str">
+        <v/>
+      </c>
+      <c r="AS95" t="str">
+        <v/>
+      </c>
+      <c r="AT95" t="str">
+        <v/>
+      </c>
+      <c r="AU95" t="str">
+        <v/>
+      </c>
+      <c r="AV95" t="str">
+        <v/>
+      </c>
+      <c r="AW95" t="str">
+        <v/>
+      </c>
+      <c r="AX95" t="str">
+        <v/>
+      </c>
+      <c r="AY95" t="str">
+        <v/>
+      </c>
+      <c r="AZ95" t="str">
+        <v/>
+      </c>
+      <c r="BA95" t="str">
+        <v/>
+      </c>
+      <c r="BB95" t="str">
+        <v/>
+      </c>
+      <c r="BC95" t="str">
+        <v/>
+      </c>
+      <c r="BD95" t="str">
+        <v>3.23827E+12</v>
+      </c>
+      <c r="BE95" t="str">
+        <v>37</v>
+      </c>
+      <c r="BF95" t="str">
+        <v>34</v>
+      </c>
+      <c r="BG95" t="str">
+        <v/>
+      </c>
+      <c r="BH95" t="str">
+        <v>0.8577</v>
+      </c>
+      <c r="BI95" t="str">
+        <v>32.5777</v>
+      </c>
+      <c r="BJ95" t="str">
+        <v/>
+      </c>
+      <c r="BK95" t="str">
+        <v/>
+      </c>
+      <c r="BL95" t="str">
+        <v>131.3623</v>
+      </c>
+      <c r="BM95" t="str">
+        <v>141.493</v>
+      </c>
+      <c r="BN95" t="str">
+        <v>133.2396</v>
+      </c>
+      <c r="BO95" t="str">
+        <v>134.1105</v>
+      </c>
+      <c r="BP95" t="str">
+        <v>118.8442</v>
+      </c>
+      <c r="BQ95" t="str">
+        <v>130.6211</v>
+      </c>
+      <c r="BR95" t="str">
+        <v>125.3663</v>
+      </c>
+      <c r="BS95" t="str">
+        <v/>
+      </c>
+      <c r="BT95" t="str">
+        <v/>
+      </c>
+      <c r="BU95" t="str">
+        <v/>
+      </c>
+      <c r="BV95" t="str">
+        <v/>
+      </c>
+      <c r="BW95" t="str">
+        <v>0</v>
+      </c>
+      <c r="BX95" t="str">
+        <v>1</v>
+      </c>
+      <c r="BY95" t="str">
+        <v>0</v>
+      </c>
+      <c r="BZ95" t="str">
+        <v>1</v>
+      </c>
+      <c r="CA95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CB95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CC95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CD95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CE95" t="str">
+        <v>3</v>
+      </c>
+      <c r="CF95" t="str">
+        <v>6</v>
+      </c>
+      <c r="CG95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CH95" t="str">
+        <v>1</v>
+      </c>
+      <c r="CI95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CJ95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CK95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CL95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CM95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CN95" t="str">
+        <v>1</v>
+      </c>
+      <c r="CO95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CP95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CQ95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CR95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CS95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CT95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CU95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CV95" t="str">
+        <v>0</v>
+      </c>
+      <c r="CW95" t="str">
+        <v>-0.1221</v>
+      </c>
+      <c r="CX95" t="str">
+        <v/>
+      </c>
+      <c r="CY95" t="str">
+        <v/>
+      </c>
+      <c r="CZ95" t="str">
+        <v>0</v>
+      </c>
+      <c r="DA95" t="str">
+        <v>-1.6395</v>
+      </c>
+      <c r="DB95" t="str">
+        <v>0.2453</v>
+      </c>
+      <c r="DC95" t="str">
+        <v>0</v>
+      </c>
+      <c r="DD95" t="str">
+        <v/>
+      </c>
+      <c r="DE95" t="str">
+        <v/>
+      </c>
+      <c r="DF95" t="str">
+        <v/>
+      </c>
+      <c r="DG95" t="str">
+        <v/>
+      </c>
+      <c r="DH95" t="str">
+        <v>1.005674</v>
+      </c>
+      <c r="DI95" t="str">
+        <v>1.083232</v>
+      </c>
+      <c r="DJ95" t="str">
+        <v>1.020921</v>
+      </c>
+      <c r="DK95" t="str">
+        <v>1.044453</v>
+      </c>
+      <c r="DL95" t="str">
+        <v>0</v>
+      </c>
+      <c r="DM95" t="str">
+        <v>0</v>
+      </c>
+      <c r="DN95" t="str">
+        <v>0</v>
+      </c>
+      <c r="DO95" t="str">
+        <v>0</v>
+      </c>
+      <c r="DP95" t="str">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:DP94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:DP95"/>
   </ignoredErrors>
 </worksheet>
 </file>
